--- a/Document/KPI/Digital Appraisal System.xlsx
+++ b/Document/KPI/Digital Appraisal System.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\Claude AI\Claude Code Advanced\project-management-system\Document\KPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479EE94A-BA06-47FF-AB19-5AF35FD8693F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAF079C-31FB-4AD8-97A3-B95B98646EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI &amp; Scoring" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="87">
   <si>
     <t>Category</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Delivery &amp; Execution</t>
-  </si>
-  <si>
     <t>Sprint Reliability - (Story Points Delivered Vs Total Story Points Committed)</t>
   </si>
   <si>
@@ -69,34 +66,13 @@
     <t>Throughput &amp; Complexity Handling - (Valid PRs Vs Total Generated PRs)</t>
   </si>
   <si>
-    <t>Quality &amp; Engineering Excellence</t>
-  </si>
-  <si>
     <t>Internal Rework Ratio - (Reopened Tasks Vs Total Completed Tasks)</t>
-  </si>
-  <si>
-    <t>Ownership &amp; Collaboration</t>
-  </si>
-  <si>
-    <t>Dependency &amp; Agile Management - (Daily Standup Logs)</t>
   </si>
   <si>
     <t>Reporting &amp; Documentation</t>
   </si>
   <si>
-    <t>Growth &amp; Innovation</t>
-  </si>
-  <si>
     <t>Learning Velocity - (Professional Upskilling Path)</t>
-  </si>
-  <si>
-    <t>Automation &amp;/or Innovation - (Tangible Improvements)</t>
-  </si>
-  <si>
-    <t>Behaviour &amp; Reliability</t>
-  </si>
-  <si>
-    <t>Attendance (No Unapproved Absences / No More than 1 Leave per month)</t>
   </si>
   <si>
     <t>Positive Behaviour &amp; Conduct (Flexible, Cooperative, Punctual)</t>
@@ -201,13 +177,6 @@
     <t>Measures code durability by tracking production/post-release bugs linked to the developer.</t>
   </si>
   <si>
-    <t>Scoring: 
-0 Production Bugs = 10 pts
-1 Minor Bug = 7 pts
-2 Minor Bugs = 4 pts
-1 Critical or 3+ Minor Bugs = 0 pts</t>
-  </si>
-  <si>
     <t>Functional Defect Leakage (Avg Bugs = No. of bugs/ no. of estimated hours)</t>
   </si>
   <si>
@@ -296,12 +265,71 @@
   <si>
     <t>Collaboration Manual</t>
   </si>
+  <si>
+    <t>Work Item in Closed Column / Total Assigned Work Item * 10</t>
+  </si>
+  <si>
+    <t>Work Item complete on or before due date / Total assigned work item * 10</t>
+  </si>
+  <si>
+    <t>Work item should be move from in -progress to in -review. If work item is blocked, do not consider it in this calculation.</t>
+  </si>
+  <si>
+    <t>Esimtated hours for work item - Actual hours logged against that work item</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> If work item is blocked, do not consider it in this calculation</t>
+  </si>
+  <si>
+    <t>Work Item in "In QA" Column / Total Assigned Work Item * 10</t>
+  </si>
+  <si>
+    <t>If work item dragged from "In QA" to "In Progress" and time logged against such work item should be treated as rework.</t>
+  </si>
+  <si>
+    <t>Check Leave Type Flag - Planned for &lt;= 1 Approved leave = 5 pts, 1.5 Approved leaves = 3 pts and Check Leave Type Flag - Unplanned for Unapproved or more than 1.5 approved leaves = 0 pts</t>
+  </si>
+  <si>
+    <t>Need to Discussed</t>
+  </si>
+  <si>
+    <t>Provision for PM to add manual entry of 5 points (option 5, 3, 0), with option to add notes and append as many as they want for that specific month.</t>
+  </si>
+  <si>
+    <t>This should be based on Learn &amp; Innovate module. Any assignment approved for specific month for any assignee should be awarded with 5 points. If assignment is decline - 3 points. If assignment not submitted for that month - 0 points.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 -( (Hours spent on Rework + Bugs) / Total Working Hours * 10) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 -( (Hours spent on Code Review) / Total Working Hours * 10) </t>
+  </si>
+  <si>
+    <t>If work item - Bug, Classification = "Code Review"  follow the scoring mentioned in previous column                                   EG: Hours Spend on Code Review - 10, Total Hours worked in month 160, 
+As per formula :
+10 -(10/160*10) = 10 - 0.625 = 9.375</t>
+  </si>
+  <si>
+    <t>If work item - Bug, apart from Classification = "Code Review"  follow the scoring mentioned in previous column
+EG: Hours Spend on Rework + Bug - 20, Total Hours worked in month 160, 
+As per formula :
+10 -(10/160*10) = 10 - 1.25 = 8.75</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Collaboration -Manual</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -328,8 +356,40 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -350,18 +410,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -850,17 +934,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -913,11 +986,66 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1021,157 +1149,200 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="5" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="7" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="8" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="8" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="8" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCCCCFF"/>
+      <color rgb="FF9999FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1384,10 +1555,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G998"/>
+  <dimension ref="A1:G999"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" customWidth="1"/>
+    <col min="1" max="1" width="47" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="54.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1413,18 +1584,18 @@
       <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="83" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>7</v>
-      </c>
       <c r="C2" s="9">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D2" s="10">
         <f t="shared" ref="D2:D3" si="0">IF(OR(E2="",F2=""),"-",(E2/F2)*C2*100)</f>
-        <v>11.249999999999998</v>
+        <v>7.5000000000000009</v>
       </c>
       <c r="E2" s="11">
         <v>15</v>
@@ -1435,16 +1606,16 @@
       <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="63"/>
+      <c r="A3" s="66"/>
       <c r="B3" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="14">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D3" s="15">
         <f t="shared" si="0"/>
-        <v>11.249999999999998</v>
+        <v>7.5000000000000009</v>
       </c>
       <c r="E3" s="16">
         <v>15</v>
@@ -1455,9 +1626,9 @@
       <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="63"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="14">
         <v>0.1</v>
@@ -1475,9 +1646,9 @@
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="64"/>
+      <c r="A5" s="67"/>
       <c r="B5" s="13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="14">
         <v>0.1</v>
@@ -1495,11 +1666,11 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="62" t="s">
-        <v>11</v>
+      <c r="A6" s="83" t="s">
+        <v>61</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" s="9">
         <v>0.05</v>
@@ -1517,9 +1688,9 @@
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="63"/>
+      <c r="A7" s="66"/>
       <c r="B7" s="13" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C7" s="14">
         <v>0.1</v>
@@ -1532,9 +1703,9 @@
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="64"/>
+      <c r="A8" s="67"/>
       <c r="B8" s="13" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C8" s="14">
         <v>0.1</v>
@@ -1546,12 +1717,12 @@
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="62" t="s">
-        <v>13</v>
+    <row r="9" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A9" s="83" t="s">
+        <v>62</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>14</v>
+      <c r="B9" s="87" t="s">
+        <v>50</v>
       </c>
       <c r="C9" s="9">
         <v>0.05</v>
@@ -1563,10 +1734,10 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="64"/>
+    <row r="10" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="67"/>
       <c r="B10" s="22" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="C10" s="23">
         <v>0.05</v>
@@ -1579,11 +1750,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="62" t="s">
-        <v>16</v>
+      <c r="A11" s="83" t="s">
+        <v>86</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>17</v>
+      <c r="B11" s="86" t="s">
+        <v>57</v>
       </c>
       <c r="C11" s="9">
         <v>0.05</v>
@@ -1595,10 +1766,10 @@
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="64"/>
-      <c r="B12" s="22" t="s">
-        <v>18</v>
+    <row r="12" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="67"/>
+      <c r="B12" s="92" t="s">
+        <v>11</v>
       </c>
       <c r="C12" s="23">
         <v>0.05</v>
@@ -1610,12 +1781,12 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="62" t="s">
-        <v>19</v>
+    <row r="13" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="94" t="s">
+        <v>59</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C13" s="9">
         <v>0.05</v>
@@ -1628,42 +1799,50 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="64"/>
-      <c r="B14" s="22" t="s">
-        <v>21</v>
+      <c r="A14" s="99" t="s">
+        <v>67</v>
       </c>
-      <c r="C14" s="23">
+      <c r="B14" s="98" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="9">
         <v>0.05</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="10">
         <v>3</v>
       </c>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
     </row>
-    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="65" t="s">
-        <v>22</v>
+    <row r="15" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="99" t="s">
+        <v>66</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="25">
-        <f t="shared" ref="C15:D15" si="1">SUM(C2:C14)</f>
-        <v>1.0500000000000003</v>
+      <c r="B15" s="97"/>
+      <c r="C15" s="23">
+        <v>0.05</v>
       </c>
-      <c r="D15" s="26">
-        <f t="shared" si="1"/>
-        <v>71.590909090909093</v>
+      <c r="D15" s="24">
+        <v>3</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
+    <row r="16" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="96" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="65"/>
+      <c r="C16" s="25">
+        <f>SUM(C2:C15)</f>
+        <v>1.0000000000000002</v>
+      </c>
+      <c r="D16" s="26">
+        <f>SUM(D2:D15)</f>
+        <v>67.090909090909093</v>
+      </c>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
@@ -1679,12 +1858,8 @@
     </row>
     <row r="18" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A18" s="7"/>
-      <c r="B18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>24</v>
-      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
@@ -1692,11 +1867,11 @@
     </row>
     <row r="19" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A19" s="7"/>
-      <c r="B19" s="28" t="s">
-        <v>25</v>
+      <c r="B19" s="1" t="s">
+        <v>15</v>
       </c>
-      <c r="C19" s="29" t="s">
-        <v>26</v>
+      <c r="C19" s="27" t="s">
+        <v>16</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -1705,11 +1880,11 @@
     </row>
     <row r="20" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A20" s="7"/>
-      <c r="B20" s="30" t="s">
-        <v>27</v>
+      <c r="B20" s="28" t="s">
+        <v>17</v>
       </c>
-      <c r="C20" s="17" t="s">
-        <v>28</v>
+      <c r="C20" s="29" t="s">
+        <v>18</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
@@ -1719,10 +1894,10 @@
     <row r="21" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="30" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -1731,11 +1906,11 @@
     </row>
     <row r="22" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
-      <c r="B22" s="31" t="s">
-        <v>31</v>
+      <c r="B22" s="30" t="s">
+        <v>21</v>
       </c>
-      <c r="C22" s="32" t="s">
-        <v>32</v>
+      <c r="C22" s="17" t="s">
+        <v>22</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -1744,8 +1919,12 @@
     </row>
     <row r="23" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
+      <c r="B23" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>24</v>
+      </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -1769,7 +1948,7 @@
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
     </row>
-    <row r="26" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -10526,21 +10705,29 @@
       <c r="F998" s="7"/>
       <c r="G998" s="7"/>
     </row>
+    <row r="999" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A999" s="7"/>
+      <c r="B999" s="7"/>
+      <c r="C999" s="7"/>
+      <c r="D999" s="7"/>
+      <c r="E999" s="7"/>
+      <c r="F999" s="7"/>
+      <c r="G999" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A15:B15"/>
+  <mergeCells count="5">
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A13:A14"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D8:D14" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"0,3,5"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D7" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"0,4,7,10"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D8:D15" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"0,3,5"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10552,17 +10739,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E999"/>
+  <dimension ref="A1:I999"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.88671875" style="75" customWidth="1"/>
-    <col min="2" max="2" width="26.88671875" customWidth="1"/>
+    <col min="1" max="1" width="26.88671875" style="38" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="54.77734375" customWidth="1"/>
-    <col min="5" max="5" width="67" customWidth="1"/>
+    <col min="5" max="5" width="67" style="38" customWidth="1"/>
+    <col min="6" max="6" width="51.6640625" style="38" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="98.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+    <row r="1" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="33" t="s">
@@ -10572,5142 +10761,5219 @@
         <v>2</v>
       </c>
       <c r="D1" s="34" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
-      <c r="E1" s="27" t="s">
-        <v>34</v>
+      <c r="E1" s="70" t="s">
+        <v>26</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
-        <v>69</v>
+      <c r="F1" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="82" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+    </row>
+    <row r="2" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="60" t="s">
+        <v>60</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C2" s="52">
         <v>0.1</v>
       </c>
       <c r="D2" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="74" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" s="79" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+    </row>
+    <row r="3" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="61"/>
+      <c r="B3" s="54" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="55">
+        <v>0.1</v>
+      </c>
+      <c r="D3" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="69" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="80" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+    </row>
+    <row r="4" spans="1:9" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="61"/>
+      <c r="B4" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="55">
+        <v>0.1</v>
+      </c>
+      <c r="D4" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="69" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="74" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="79"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+    </row>
+    <row r="5" spans="1:9" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="62"/>
+      <c r="B5" s="57" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="C5" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="59" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="73"/>
-      <c r="B3" s="39" t="s">
+      <c r="E5" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="40">
+      <c r="F5" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="79" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+    </row>
+    <row r="6" spans="1:9" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="52">
+        <v>0.05</v>
+      </c>
+      <c r="D6" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="74" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="79"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+    </row>
+    <row r="7" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="61"/>
+      <c r="B7" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="55">
         <v>0.1</v>
       </c>
-      <c r="D3" s="41" t="s">
-        <v>39</v>
+      <c r="D7" s="56" t="s">
+        <v>43</v>
       </c>
-      <c r="E3" s="42" t="s">
-        <v>40</v>
+      <c r="E7" s="69" t="s">
+        <v>81</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="73"/>
-      <c r="B4" s="39" t="s">
-        <v>41</v>
+      <c r="F7" s="74" t="s">
+        <v>82</v>
       </c>
-      <c r="C4" s="40">
+      <c r="G7" s="79"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+    </row>
+    <row r="8" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="61"/>
+      <c r="B8" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="55">
         <v>0.1</v>
       </c>
-      <c r="D4" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="42" t="s">
+      <c r="D8" s="56" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
-      <c r="B5" s="55" t="s">
-        <v>44</v>
+      <c r="E8" s="69" t="s">
+        <v>80</v>
       </c>
-      <c r="C5" s="56">
-        <v>0.1</v>
+      <c r="F8" s="74" t="s">
+        <v>83</v>
       </c>
-      <c r="D5" s="57" t="s">
+    </row>
+    <row r="9" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="84" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="52">
+        <v>0.05</v>
+      </c>
+      <c r="D9" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="71" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="74" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="63"/>
+      <c r="B10" s="88" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="52">
+        <v>0.05</v>
+      </c>
+      <c r="D10" s="53"/>
+      <c r="E10" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="74" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="89" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="90" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="47">
+        <v>0.05</v>
+      </c>
+      <c r="D11" s="48"/>
+      <c r="E11" s="75" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="74" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="64"/>
+      <c r="B12" s="91" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="49">
+        <v>0.05</v>
+      </c>
+      <c r="D12" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="58" t="s">
+      <c r="E12" s="76" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="72" t="s">
-        <v>70</v>
+      <c r="F12" s="74" t="s">
+        <v>78</v>
       </c>
-      <c r="B6" s="35" t="s">
+    </row>
+    <row r="13" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C13" s="43">
         <v>0.05</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="D13" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E13" s="77" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="73"/>
-      <c r="B7" s="41" t="s">
-        <v>50</v>
+      <c r="F13" s="74" t="s">
+        <v>79</v>
       </c>
-      <c r="C7" s="40">
-        <v>0.1</v>
+    </row>
+    <row r="14" spans="1:9" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="95" t="s">
+        <v>67</v>
       </c>
-      <c r="D7" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="73"/>
-      <c r="B8" s="41" t="s">
+      <c r="B14" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="40">
-        <v>0.1</v>
-      </c>
-      <c r="D8" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="42" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="36">
+      <c r="C14" s="40">
         <v>0.05</v>
       </c>
-      <c r="D9" s="37" t="s">
-        <v>60</v>
+      <c r="D14" s="41" t="s">
+        <v>54</v>
       </c>
-      <c r="E9" s="38" t="s">
-        <v>61</v>
+      <c r="E14" s="78" t="s">
+        <v>65</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="77"/>
-      <c r="B10" s="35" t="s">
-        <v>72</v>
+      <c r="F14" s="74" t="s">
+        <v>78</v>
       </c>
-      <c r="C10" s="36">
+    </row>
+    <row r="15" spans="1:9" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="45"/>
+      <c r="C15" s="46">
         <v>0.05</v>
       </c>
-      <c r="D10" s="37"/>
-      <c r="E10" s="79" t="s">
-        <v>73</v>
+      <c r="D15" s="45"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="74" t="s">
+        <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="72" t="s">
-        <v>77</v>
-      </c>
-      <c r="B11" s="67" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="68">
-        <v>0.05</v>
-      </c>
-      <c r="D11" s="69"/>
-      <c r="E11" s="70" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="84"/>
-      <c r="B12" s="43" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="44">
-        <v>0.05</v>
-      </c>
-      <c r="D12" s="45" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="46" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="81" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="82" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="59">
-        <v>0.05</v>
-      </c>
-      <c r="D13" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="61" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="83" t="s">
-        <v>76</v>
-      </c>
-      <c r="B14" s="80" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="47">
-        <v>0.05</v>
-      </c>
-      <c r="D14" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="78" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="81" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="85">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A16" s="50"/>
-      <c r="B16" s="49"/>
-      <c r="D16" s="50"/>
+    <row r="16" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A16" s="36"/>
+      <c r="B16" s="35"/>
+      <c r="D16" s="36"/>
     </row>
     <row r="17" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A17" s="50"/>
-      <c r="B17" s="49"/>
-      <c r="D17" s="50"/>
+      <c r="A17" s="36"/>
+      <c r="B17" s="35"/>
+      <c r="D17" s="36"/>
     </row>
     <row r="18" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A18" s="50"/>
-      <c r="B18" s="49"/>
-      <c r="D18" s="50"/>
+      <c r="A18" s="36"/>
+      <c r="B18" s="35"/>
+      <c r="D18" s="36"/>
     </row>
     <row r="19" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A19" s="50"/>
-      <c r="B19" s="49"/>
-      <c r="D19" s="50"/>
+      <c r="A19" s="36"/>
+      <c r="B19" s="35"/>
+      <c r="D19" s="36"/>
     </row>
     <row r="20" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A20" s="50"/>
-      <c r="B20" s="49"/>
-      <c r="D20" s="50"/>
+      <c r="A20" s="36"/>
+      <c r="B20" s="35"/>
+      <c r="D20" s="36"/>
     </row>
     <row r="21" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A21" s="50"/>
-      <c r="B21" s="49"/>
-      <c r="D21" s="50"/>
+      <c r="A21" s="36"/>
+      <c r="B21" s="35"/>
+      <c r="D21" s="36"/>
     </row>
     <row r="22" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A22" s="50"/>
-      <c r="B22" s="49"/>
-      <c r="D22" s="50"/>
+      <c r="A22" s="36"/>
+      <c r="B22" s="35"/>
+      <c r="D22" s="36"/>
     </row>
     <row r="23" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A23" s="50"/>
-      <c r="B23" s="49"/>
-      <c r="D23" s="50"/>
+      <c r="A23" s="36"/>
+      <c r="B23" s="35"/>
+      <c r="D23" s="36"/>
     </row>
     <row r="24" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A24" s="50"/>
-      <c r="B24" s="49"/>
-      <c r="D24" s="50"/>
+      <c r="A24" s="36"/>
+      <c r="B24" s="35"/>
+      <c r="D24" s="36"/>
     </row>
     <row r="25" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A25" s="50"/>
-      <c r="B25" s="49"/>
-      <c r="D25" s="50"/>
+      <c r="A25" s="36"/>
+      <c r="B25" s="35"/>
+      <c r="D25" s="36"/>
     </row>
     <row r="26" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A26" s="50"/>
-      <c r="B26" s="49"/>
-      <c r="D26" s="50"/>
+      <c r="A26" s="36"/>
+      <c r="B26" s="35"/>
+      <c r="D26" s="36"/>
     </row>
     <row r="27" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A27" s="50"/>
-      <c r="B27" s="49"/>
-      <c r="D27" s="50"/>
+      <c r="A27" s="36"/>
+      <c r="B27" s="35"/>
+      <c r="D27" s="36"/>
     </row>
     <row r="28" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A28" s="50"/>
-      <c r="B28" s="49"/>
-      <c r="D28" s="50"/>
+      <c r="A28" s="36"/>
+      <c r="B28" s="35"/>
+      <c r="D28" s="36"/>
     </row>
     <row r="29" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A29" s="50"/>
-      <c r="B29" s="49"/>
-      <c r="D29" s="50"/>
+      <c r="A29" s="36"/>
+      <c r="B29" s="35"/>
+      <c r="D29" s="36"/>
     </row>
     <row r="30" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A30" s="50"/>
-      <c r="B30" s="49"/>
-      <c r="D30" s="50"/>
+      <c r="A30" s="36"/>
+      <c r="B30" s="35"/>
+      <c r="D30" s="36"/>
     </row>
     <row r="31" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A31" s="50"/>
-      <c r="B31" s="49"/>
-      <c r="D31" s="50"/>
+      <c r="A31" s="36"/>
+      <c r="B31" s="35"/>
+      <c r="D31" s="36"/>
     </row>
     <row r="32" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A32" s="50"/>
-      <c r="B32" s="49"/>
-      <c r="D32" s="50"/>
+      <c r="A32" s="36"/>
+      <c r="B32" s="35"/>
+      <c r="D32" s="36"/>
     </row>
     <row r="33" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A33" s="50"/>
-      <c r="B33" s="49"/>
-      <c r="D33" s="50"/>
+      <c r="A33" s="36"/>
+      <c r="B33" s="35"/>
+      <c r="D33" s="36"/>
     </row>
     <row r="34" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A34" s="50"/>
-      <c r="B34" s="49"/>
-      <c r="D34" s="50"/>
+      <c r="A34" s="36"/>
+      <c r="B34" s="35"/>
+      <c r="D34" s="36"/>
     </row>
     <row r="35" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A35" s="50"/>
-      <c r="B35" s="49"/>
-      <c r="D35" s="50"/>
+      <c r="A35" s="36"/>
+      <c r="B35" s="35"/>
+      <c r="D35" s="36"/>
     </row>
     <row r="36" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A36" s="50"/>
-      <c r="B36" s="49"/>
-      <c r="D36" s="50"/>
+      <c r="A36" s="36"/>
+      <c r="B36" s="35"/>
+      <c r="D36" s="36"/>
     </row>
     <row r="37" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A37" s="50"/>
-      <c r="B37" s="49"/>
-      <c r="D37" s="50"/>
+      <c r="A37" s="36"/>
+      <c r="B37" s="35"/>
+      <c r="D37" s="36"/>
     </row>
     <row r="38" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A38" s="50"/>
-      <c r="B38" s="49"/>
-      <c r="D38" s="50"/>
+      <c r="A38" s="36"/>
+      <c r="B38" s="35"/>
+      <c r="D38" s="36"/>
     </row>
     <row r="39" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A39" s="50"/>
-      <c r="B39" s="49"/>
-      <c r="D39" s="50"/>
+      <c r="A39" s="36"/>
+      <c r="B39" s="35"/>
+      <c r="D39" s="36"/>
     </row>
     <row r="40" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A40" s="50"/>
-      <c r="B40" s="49"/>
-      <c r="D40" s="50"/>
+      <c r="A40" s="36"/>
+      <c r="B40" s="35"/>
+      <c r="D40" s="36"/>
     </row>
     <row r="41" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A41" s="50"/>
-      <c r="B41" s="49"/>
-      <c r="D41" s="50"/>
+      <c r="A41" s="36"/>
+      <c r="B41" s="35"/>
+      <c r="D41" s="36"/>
     </row>
     <row r="42" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A42" s="50"/>
-      <c r="B42" s="49"/>
-      <c r="D42" s="50"/>
+      <c r="A42" s="36"/>
+      <c r="B42" s="35"/>
+      <c r="D42" s="36"/>
     </row>
     <row r="43" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A43" s="50"/>
-      <c r="B43" s="49"/>
-      <c r="D43" s="50"/>
+      <c r="A43" s="36"/>
+      <c r="B43" s="35"/>
+      <c r="D43" s="36"/>
     </row>
     <row r="44" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A44" s="50"/>
-      <c r="B44" s="49"/>
-      <c r="D44" s="50"/>
+      <c r="A44" s="36"/>
+      <c r="B44" s="35"/>
+      <c r="D44" s="36"/>
     </row>
     <row r="45" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A45" s="50"/>
-      <c r="B45" s="49"/>
-      <c r="D45" s="50"/>
+      <c r="A45" s="36"/>
+      <c r="B45" s="35"/>
+      <c r="D45" s="36"/>
     </row>
     <row r="46" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A46" s="50"/>
-      <c r="B46" s="49"/>
-      <c r="D46" s="50"/>
+      <c r="A46" s="36"/>
+      <c r="B46" s="35"/>
+      <c r="D46" s="36"/>
     </row>
     <row r="47" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A47" s="50"/>
-      <c r="B47" s="49"/>
-      <c r="D47" s="50"/>
+      <c r="A47" s="36"/>
+      <c r="B47" s="35"/>
+      <c r="D47" s="36"/>
     </row>
     <row r="48" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A48" s="50"/>
-      <c r="B48" s="49"/>
-      <c r="D48" s="50"/>
+      <c r="A48" s="36"/>
+      <c r="B48" s="35"/>
+      <c r="D48" s="36"/>
     </row>
     <row r="49" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A49" s="50"/>
-      <c r="B49" s="49"/>
-      <c r="D49" s="50"/>
+      <c r="A49" s="36"/>
+      <c r="B49" s="35"/>
+      <c r="D49" s="36"/>
     </row>
     <row r="50" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A50" s="50"/>
-      <c r="B50" s="49"/>
-      <c r="D50" s="50"/>
+      <c r="A50" s="36"/>
+      <c r="B50" s="35"/>
+      <c r="D50" s="36"/>
     </row>
     <row r="51" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A51" s="50"/>
-      <c r="B51" s="49"/>
-      <c r="D51" s="50"/>
+      <c r="A51" s="36"/>
+      <c r="B51" s="35"/>
+      <c r="D51" s="36"/>
     </row>
     <row r="52" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A52" s="50"/>
-      <c r="B52" s="49"/>
-      <c r="D52" s="50"/>
+      <c r="A52" s="36"/>
+      <c r="B52" s="35"/>
+      <c r="D52" s="36"/>
     </row>
     <row r="53" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A53" s="50"/>
-      <c r="B53" s="49"/>
-      <c r="D53" s="50"/>
+      <c r="A53" s="36"/>
+      <c r="B53" s="35"/>
+      <c r="D53" s="36"/>
     </row>
     <row r="54" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A54" s="50"/>
-      <c r="B54" s="49"/>
-      <c r="D54" s="50"/>
+      <c r="A54" s="36"/>
+      <c r="B54" s="35"/>
+      <c r="D54" s="36"/>
     </row>
     <row r="55" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A55" s="50"/>
-      <c r="B55" s="49"/>
-      <c r="D55" s="50"/>
+      <c r="A55" s="36"/>
+      <c r="B55" s="35"/>
+      <c r="D55" s="36"/>
     </row>
     <row r="56" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A56" s="50"/>
-      <c r="B56" s="49"/>
-      <c r="D56" s="50"/>
+      <c r="A56" s="36"/>
+      <c r="B56" s="35"/>
+      <c r="D56" s="36"/>
     </row>
     <row r="57" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A57" s="50"/>
-      <c r="B57" s="49"/>
-      <c r="D57" s="50"/>
+      <c r="A57" s="36"/>
+      <c r="B57" s="35"/>
+      <c r="D57" s="36"/>
     </row>
     <row r="58" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A58" s="50"/>
-      <c r="B58" s="49"/>
-      <c r="D58" s="50"/>
+      <c r="A58" s="36"/>
+      <c r="B58" s="35"/>
+      <c r="D58" s="36"/>
     </row>
     <row r="59" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A59" s="50"/>
-      <c r="B59" s="49"/>
-      <c r="D59" s="50"/>
+      <c r="A59" s="36"/>
+      <c r="B59" s="35"/>
+      <c r="D59" s="36"/>
     </row>
     <row r="60" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A60" s="50"/>
-      <c r="B60" s="49"/>
-      <c r="D60" s="50"/>
+      <c r="A60" s="36"/>
+      <c r="B60" s="35"/>
+      <c r="D60" s="36"/>
     </row>
     <row r="61" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A61" s="50"/>
-      <c r="B61" s="49"/>
-      <c r="D61" s="50"/>
+      <c r="A61" s="36"/>
+      <c r="B61" s="35"/>
+      <c r="D61" s="36"/>
     </row>
     <row r="62" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A62" s="50"/>
-      <c r="B62" s="49"/>
-      <c r="D62" s="50"/>
+      <c r="A62" s="36"/>
+      <c r="B62" s="35"/>
+      <c r="D62" s="36"/>
     </row>
     <row r="63" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A63" s="50"/>
-      <c r="B63" s="49"/>
-      <c r="D63" s="50"/>
+      <c r="A63" s="36"/>
+      <c r="B63" s="35"/>
+      <c r="D63" s="36"/>
     </row>
     <row r="64" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A64" s="50"/>
-      <c r="B64" s="49"/>
-      <c r="D64" s="50"/>
+      <c r="A64" s="36"/>
+      <c r="B64" s="35"/>
+      <c r="D64" s="36"/>
     </row>
     <row r="65" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A65" s="50"/>
-      <c r="B65" s="49"/>
-      <c r="D65" s="50"/>
+      <c r="A65" s="36"/>
+      <c r="B65" s="35"/>
+      <c r="D65" s="36"/>
     </row>
     <row r="66" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A66" s="50"/>
-      <c r="B66" s="49"/>
-      <c r="D66" s="50"/>
+      <c r="A66" s="36"/>
+      <c r="B66" s="35"/>
+      <c r="D66" s="36"/>
     </row>
     <row r="67" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A67" s="50"/>
-      <c r="B67" s="49"/>
-      <c r="D67" s="50"/>
+      <c r="A67" s="36"/>
+      <c r="B67" s="35"/>
+      <c r="D67" s="36"/>
     </row>
     <row r="68" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A68" s="50"/>
-      <c r="B68" s="49"/>
-      <c r="D68" s="50"/>
+      <c r="A68" s="36"/>
+      <c r="B68" s="35"/>
+      <c r="D68" s="36"/>
     </row>
     <row r="69" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A69" s="50"/>
-      <c r="B69" s="49"/>
-      <c r="D69" s="50"/>
+      <c r="A69" s="36"/>
+      <c r="B69" s="35"/>
+      <c r="D69" s="36"/>
     </row>
     <row r="70" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A70" s="50"/>
-      <c r="B70" s="49"/>
-      <c r="D70" s="50"/>
+      <c r="A70" s="36"/>
+      <c r="B70" s="35"/>
+      <c r="D70" s="36"/>
     </row>
     <row r="71" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A71" s="50"/>
-      <c r="B71" s="49"/>
-      <c r="D71" s="50"/>
+      <c r="A71" s="36"/>
+      <c r="B71" s="35"/>
+      <c r="D71" s="36"/>
     </row>
     <row r="72" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A72" s="50"/>
-      <c r="B72" s="49"/>
-      <c r="D72" s="50"/>
+      <c r="A72" s="36"/>
+      <c r="B72" s="35"/>
+      <c r="D72" s="36"/>
     </row>
     <row r="73" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A73" s="50"/>
-      <c r="B73" s="49"/>
-      <c r="D73" s="50"/>
+      <c r="A73" s="36"/>
+      <c r="B73" s="35"/>
+      <c r="D73" s="36"/>
     </row>
     <row r="74" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A74" s="50"/>
-      <c r="B74" s="49"/>
-      <c r="D74" s="50"/>
+      <c r="A74" s="36"/>
+      <c r="B74" s="35"/>
+      <c r="D74" s="36"/>
     </row>
     <row r="75" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A75" s="50"/>
-      <c r="B75" s="49"/>
-      <c r="D75" s="50"/>
+      <c r="A75" s="36"/>
+      <c r="B75" s="35"/>
+      <c r="D75" s="36"/>
     </row>
     <row r="76" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A76" s="50"/>
-      <c r="B76" s="49"/>
-      <c r="D76" s="50"/>
+      <c r="A76" s="36"/>
+      <c r="B76" s="35"/>
+      <c r="D76" s="36"/>
     </row>
     <row r="77" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A77" s="50"/>
-      <c r="B77" s="49"/>
-      <c r="D77" s="50"/>
+      <c r="A77" s="36"/>
+      <c r="B77" s="35"/>
+      <c r="D77" s="36"/>
     </row>
     <row r="78" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A78" s="50"/>
-      <c r="B78" s="49"/>
-      <c r="D78" s="50"/>
+      <c r="A78" s="36"/>
+      <c r="B78" s="35"/>
+      <c r="D78" s="36"/>
     </row>
     <row r="79" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A79" s="50"/>
-      <c r="B79" s="49"/>
-      <c r="D79" s="50"/>
+      <c r="A79" s="36"/>
+      <c r="B79" s="35"/>
+      <c r="D79" s="36"/>
     </row>
     <row r="80" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A80" s="50"/>
-      <c r="B80" s="49"/>
-      <c r="D80" s="50"/>
+      <c r="A80" s="36"/>
+      <c r="B80" s="35"/>
+      <c r="D80" s="36"/>
     </row>
     <row r="81" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A81" s="50"/>
-      <c r="B81" s="49"/>
-      <c r="D81" s="50"/>
+      <c r="A81" s="36"/>
+      <c r="B81" s="35"/>
+      <c r="D81" s="36"/>
     </row>
     <row r="82" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A82" s="50"/>
-      <c r="B82" s="49"/>
-      <c r="D82" s="50"/>
+      <c r="A82" s="36"/>
+      <c r="B82" s="35"/>
+      <c r="D82" s="36"/>
     </row>
     <row r="83" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A83" s="50"/>
-      <c r="B83" s="49"/>
-      <c r="D83" s="50"/>
+      <c r="A83" s="36"/>
+      <c r="B83" s="35"/>
+      <c r="D83" s="36"/>
     </row>
     <row r="84" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A84" s="50"/>
-      <c r="B84" s="49"/>
-      <c r="D84" s="50"/>
+      <c r="A84" s="36"/>
+      <c r="B84" s="35"/>
+      <c r="D84" s="36"/>
     </row>
     <row r="85" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A85" s="50"/>
-      <c r="B85" s="49"/>
-      <c r="D85" s="50"/>
+      <c r="A85" s="36"/>
+      <c r="B85" s="35"/>
+      <c r="D85" s="36"/>
     </row>
     <row r="86" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A86" s="50"/>
-      <c r="B86" s="49"/>
-      <c r="D86" s="50"/>
+      <c r="A86" s="36"/>
+      <c r="B86" s="35"/>
+      <c r="D86" s="36"/>
     </row>
     <row r="87" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A87" s="50"/>
-      <c r="B87" s="49"/>
-      <c r="D87" s="50"/>
+      <c r="A87" s="36"/>
+      <c r="B87" s="35"/>
+      <c r="D87" s="36"/>
     </row>
     <row r="88" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A88" s="50"/>
-      <c r="B88" s="49"/>
-      <c r="D88" s="50"/>
+      <c r="A88" s="36"/>
+      <c r="B88" s="35"/>
+      <c r="D88" s="36"/>
     </row>
     <row r="89" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A89" s="50"/>
-      <c r="B89" s="49"/>
-      <c r="D89" s="50"/>
+      <c r="A89" s="36"/>
+      <c r="B89" s="35"/>
+      <c r="D89" s="36"/>
     </row>
     <row r="90" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A90" s="50"/>
-      <c r="B90" s="49"/>
-      <c r="D90" s="50"/>
+      <c r="A90" s="36"/>
+      <c r="B90" s="35"/>
+      <c r="D90" s="36"/>
     </row>
     <row r="91" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A91" s="50"/>
-      <c r="B91" s="49"/>
-      <c r="D91" s="50"/>
+      <c r="A91" s="36"/>
+      <c r="B91" s="35"/>
+      <c r="D91" s="36"/>
     </row>
     <row r="92" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A92" s="50"/>
-      <c r="B92" s="49"/>
-      <c r="D92" s="50"/>
+      <c r="A92" s="36"/>
+      <c r="B92" s="35"/>
+      <c r="D92" s="36"/>
     </row>
     <row r="93" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A93" s="50"/>
-      <c r="B93" s="49"/>
-      <c r="D93" s="50"/>
+      <c r="A93" s="36"/>
+      <c r="B93" s="35"/>
+      <c r="D93" s="36"/>
     </row>
     <row r="94" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A94" s="50"/>
-      <c r="B94" s="49"/>
-      <c r="D94" s="50"/>
+      <c r="A94" s="36"/>
+      <c r="B94" s="35"/>
+      <c r="D94" s="36"/>
     </row>
     <row r="95" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A95" s="50"/>
-      <c r="B95" s="49"/>
-      <c r="D95" s="50"/>
+      <c r="A95" s="36"/>
+      <c r="B95" s="35"/>
+      <c r="D95" s="36"/>
     </row>
     <row r="96" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A96" s="50"/>
-      <c r="B96" s="49"/>
-      <c r="D96" s="50"/>
+      <c r="A96" s="36"/>
+      <c r="B96" s="35"/>
+      <c r="D96" s="36"/>
     </row>
     <row r="97" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A97" s="50"/>
-      <c r="B97" s="49"/>
-      <c r="D97" s="50"/>
+      <c r="A97" s="36"/>
+      <c r="B97" s="35"/>
+      <c r="D97" s="36"/>
     </row>
     <row r="98" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A98" s="50"/>
-      <c r="B98" s="49"/>
-      <c r="D98" s="50"/>
+      <c r="A98" s="36"/>
+      <c r="B98" s="35"/>
+      <c r="D98" s="36"/>
     </row>
     <row r="99" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A99" s="50"/>
-      <c r="B99" s="49"/>
-      <c r="D99" s="50"/>
+      <c r="A99" s="36"/>
+      <c r="B99" s="35"/>
+      <c r="D99" s="36"/>
     </row>
     <row r="100" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A100" s="50"/>
-      <c r="B100" s="49"/>
-      <c r="D100" s="50"/>
+      <c r="A100" s="36"/>
+      <c r="B100" s="35"/>
+      <c r="D100" s="36"/>
     </row>
     <row r="101" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A101" s="50"/>
-      <c r="B101" s="49"/>
-      <c r="D101" s="50"/>
+      <c r="A101" s="36"/>
+      <c r="B101" s="35"/>
+      <c r="D101" s="36"/>
     </row>
     <row r="102" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A102" s="50"/>
-      <c r="B102" s="49"/>
-      <c r="D102" s="50"/>
+      <c r="A102" s="36"/>
+      <c r="B102" s="35"/>
+      <c r="D102" s="36"/>
     </row>
     <row r="103" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A103" s="50"/>
-      <c r="B103" s="49"/>
-      <c r="D103" s="50"/>
+      <c r="A103" s="36"/>
+      <c r="B103" s="35"/>
+      <c r="D103" s="36"/>
     </row>
     <row r="104" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A104" s="50"/>
-      <c r="B104" s="49"/>
-      <c r="D104" s="50"/>
+      <c r="A104" s="36"/>
+      <c r="B104" s="35"/>
+      <c r="D104" s="36"/>
     </row>
     <row r="105" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A105" s="50"/>
-      <c r="B105" s="49"/>
-      <c r="D105" s="50"/>
+      <c r="A105" s="36"/>
+      <c r="B105" s="35"/>
+      <c r="D105" s="36"/>
     </row>
     <row r="106" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A106" s="50"/>
-      <c r="B106" s="49"/>
-      <c r="D106" s="50"/>
+      <c r="A106" s="36"/>
+      <c r="B106" s="35"/>
+      <c r="D106" s="36"/>
     </row>
     <row r="107" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A107" s="50"/>
-      <c r="B107" s="49"/>
-      <c r="D107" s="50"/>
+      <c r="A107" s="36"/>
+      <c r="B107" s="35"/>
+      <c r="D107" s="36"/>
     </row>
     <row r="108" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A108" s="50"/>
-      <c r="B108" s="49"/>
-      <c r="D108" s="50"/>
+      <c r="A108" s="36"/>
+      <c r="B108" s="35"/>
+      <c r="D108" s="36"/>
     </row>
     <row r="109" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A109" s="50"/>
-      <c r="B109" s="49"/>
-      <c r="D109" s="50"/>
+      <c r="A109" s="36"/>
+      <c r="B109" s="35"/>
+      <c r="D109" s="36"/>
     </row>
     <row r="110" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A110" s="50"/>
-      <c r="B110" s="49"/>
-      <c r="D110" s="50"/>
+      <c r="A110" s="36"/>
+      <c r="B110" s="35"/>
+      <c r="D110" s="36"/>
     </row>
     <row r="111" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A111" s="50"/>
-      <c r="B111" s="49"/>
-      <c r="D111" s="50"/>
+      <c r="A111" s="36"/>
+      <c r="B111" s="35"/>
+      <c r="D111" s="36"/>
     </row>
     <row r="112" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A112" s="50"/>
-      <c r="B112" s="49"/>
-      <c r="D112" s="50"/>
+      <c r="A112" s="36"/>
+      <c r="B112" s="35"/>
+      <c r="D112" s="36"/>
     </row>
     <row r="113" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A113" s="50"/>
-      <c r="B113" s="49"/>
-      <c r="D113" s="50"/>
+      <c r="A113" s="36"/>
+      <c r="B113" s="35"/>
+      <c r="D113" s="36"/>
     </row>
     <row r="114" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A114" s="50"/>
-      <c r="B114" s="49"/>
-      <c r="D114" s="50"/>
+      <c r="A114" s="36"/>
+      <c r="B114" s="35"/>
+      <c r="D114" s="36"/>
     </row>
     <row r="115" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A115" s="50"/>
-      <c r="B115" s="49"/>
-      <c r="D115" s="50"/>
+      <c r="A115" s="36"/>
+      <c r="B115" s="35"/>
+      <c r="D115" s="36"/>
     </row>
     <row r="116" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A116" s="50"/>
-      <c r="B116" s="49"/>
-      <c r="D116" s="50"/>
+      <c r="A116" s="36"/>
+      <c r="B116" s="35"/>
+      <c r="D116" s="36"/>
     </row>
     <row r="117" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A117" s="50"/>
-      <c r="B117" s="49"/>
-      <c r="D117" s="50"/>
+      <c r="A117" s="36"/>
+      <c r="B117" s="35"/>
+      <c r="D117" s="36"/>
     </row>
     <row r="118" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A118" s="50"/>
-      <c r="B118" s="49"/>
-      <c r="D118" s="50"/>
+      <c r="A118" s="36"/>
+      <c r="B118" s="35"/>
+      <c r="D118" s="36"/>
     </row>
     <row r="119" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A119" s="50"/>
-      <c r="B119" s="49"/>
-      <c r="D119" s="50"/>
+      <c r="A119" s="36"/>
+      <c r="B119" s="35"/>
+      <c r="D119" s="36"/>
     </row>
     <row r="120" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A120" s="50"/>
-      <c r="B120" s="49"/>
-      <c r="D120" s="50"/>
+      <c r="A120" s="36"/>
+      <c r="B120" s="35"/>
+      <c r="D120" s="36"/>
     </row>
     <row r="121" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A121" s="50"/>
-      <c r="B121" s="49"/>
-      <c r="D121" s="50"/>
+      <c r="A121" s="36"/>
+      <c r="B121" s="35"/>
+      <c r="D121" s="36"/>
     </row>
     <row r="122" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A122" s="50"/>
-      <c r="B122" s="49"/>
-      <c r="D122" s="50"/>
+      <c r="A122" s="36"/>
+      <c r="B122" s="35"/>
+      <c r="D122" s="36"/>
     </row>
     <row r="123" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A123" s="50"/>
-      <c r="B123" s="49"/>
-      <c r="D123" s="50"/>
+      <c r="A123" s="36"/>
+      <c r="B123" s="35"/>
+      <c r="D123" s="36"/>
     </row>
     <row r="124" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A124" s="50"/>
-      <c r="B124" s="49"/>
-      <c r="D124" s="50"/>
+      <c r="A124" s="36"/>
+      <c r="B124" s="35"/>
+      <c r="D124" s="36"/>
     </row>
     <row r="125" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A125" s="50"/>
-      <c r="B125" s="49"/>
-      <c r="D125" s="50"/>
+      <c r="A125" s="36"/>
+      <c r="B125" s="35"/>
+      <c r="D125" s="36"/>
     </row>
     <row r="126" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A126" s="50"/>
-      <c r="B126" s="49"/>
-      <c r="D126" s="50"/>
+      <c r="A126" s="36"/>
+      <c r="B126" s="35"/>
+      <c r="D126" s="36"/>
     </row>
     <row r="127" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A127" s="50"/>
-      <c r="B127" s="49"/>
-      <c r="D127" s="50"/>
+      <c r="A127" s="36"/>
+      <c r="B127" s="35"/>
+      <c r="D127" s="36"/>
     </row>
     <row r="128" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A128" s="50"/>
-      <c r="B128" s="49"/>
-      <c r="D128" s="50"/>
+      <c r="A128" s="36"/>
+      <c r="B128" s="35"/>
+      <c r="D128" s="36"/>
     </row>
     <row r="129" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A129" s="50"/>
-      <c r="B129" s="49"/>
-      <c r="D129" s="50"/>
+      <c r="A129" s="36"/>
+      <c r="B129" s="35"/>
+      <c r="D129" s="36"/>
     </row>
     <row r="130" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A130" s="50"/>
-      <c r="B130" s="49"/>
-      <c r="D130" s="50"/>
+      <c r="A130" s="36"/>
+      <c r="B130" s="35"/>
+      <c r="D130" s="36"/>
     </row>
     <row r="131" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A131" s="50"/>
-      <c r="B131" s="49"/>
-      <c r="D131" s="50"/>
+      <c r="A131" s="36"/>
+      <c r="B131" s="35"/>
+      <c r="D131" s="36"/>
     </row>
     <row r="132" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A132" s="50"/>
-      <c r="B132" s="49"/>
-      <c r="D132" s="50"/>
+      <c r="A132" s="36"/>
+      <c r="B132" s="35"/>
+      <c r="D132" s="36"/>
     </row>
     <row r="133" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A133" s="50"/>
-      <c r="B133" s="49"/>
-      <c r="D133" s="50"/>
+      <c r="A133" s="36"/>
+      <c r="B133" s="35"/>
+      <c r="D133" s="36"/>
     </row>
     <row r="134" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A134" s="50"/>
-      <c r="B134" s="49"/>
-      <c r="D134" s="50"/>
+      <c r="A134" s="36"/>
+      <c r="B134" s="35"/>
+      <c r="D134" s="36"/>
     </row>
     <row r="135" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A135" s="50"/>
-      <c r="B135" s="49"/>
-      <c r="D135" s="50"/>
+      <c r="A135" s="36"/>
+      <c r="B135" s="35"/>
+      <c r="D135" s="36"/>
     </row>
     <row r="136" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A136" s="50"/>
-      <c r="B136" s="49"/>
-      <c r="D136" s="50"/>
+      <c r="A136" s="36"/>
+      <c r="B136" s="35"/>
+      <c r="D136" s="36"/>
     </row>
     <row r="137" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A137" s="50"/>
-      <c r="B137" s="49"/>
-      <c r="D137" s="50"/>
+      <c r="A137" s="36"/>
+      <c r="B137" s="35"/>
+      <c r="D137" s="36"/>
     </row>
     <row r="138" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A138" s="50"/>
-      <c r="B138" s="49"/>
-      <c r="D138" s="50"/>
+      <c r="A138" s="36"/>
+      <c r="B138" s="35"/>
+      <c r="D138" s="36"/>
     </row>
     <row r="139" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A139" s="50"/>
-      <c r="B139" s="49"/>
-      <c r="D139" s="50"/>
+      <c r="A139" s="36"/>
+      <c r="B139" s="35"/>
+      <c r="D139" s="36"/>
     </row>
     <row r="140" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A140" s="50"/>
-      <c r="B140" s="49"/>
-      <c r="D140" s="50"/>
+      <c r="A140" s="36"/>
+      <c r="B140" s="35"/>
+      <c r="D140" s="36"/>
     </row>
     <row r="141" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A141" s="50"/>
-      <c r="B141" s="49"/>
-      <c r="D141" s="50"/>
+      <c r="A141" s="36"/>
+      <c r="B141" s="35"/>
+      <c r="D141" s="36"/>
     </row>
     <row r="142" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A142" s="50"/>
-      <c r="B142" s="49"/>
-      <c r="D142" s="50"/>
+      <c r="A142" s="36"/>
+      <c r="B142" s="35"/>
+      <c r="D142" s="36"/>
     </row>
     <row r="143" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A143" s="50"/>
-      <c r="B143" s="49"/>
-      <c r="D143" s="50"/>
+      <c r="A143" s="36"/>
+      <c r="B143" s="35"/>
+      <c r="D143" s="36"/>
     </row>
     <row r="144" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A144" s="50"/>
-      <c r="B144" s="49"/>
-      <c r="D144" s="50"/>
+      <c r="A144" s="36"/>
+      <c r="B144" s="35"/>
+      <c r="D144" s="36"/>
     </row>
     <row r="145" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A145" s="50"/>
-      <c r="B145" s="49"/>
-      <c r="D145" s="50"/>
+      <c r="A145" s="36"/>
+      <c r="B145" s="35"/>
+      <c r="D145" s="36"/>
     </row>
     <row r="146" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A146" s="50"/>
-      <c r="B146" s="49"/>
-      <c r="D146" s="50"/>
+      <c r="A146" s="36"/>
+      <c r="B146" s="35"/>
+      <c r="D146" s="36"/>
     </row>
     <row r="147" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A147" s="50"/>
-      <c r="B147" s="49"/>
-      <c r="D147" s="50"/>
+      <c r="A147" s="36"/>
+      <c r="B147" s="35"/>
+      <c r="D147" s="36"/>
     </row>
     <row r="148" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A148" s="50"/>
-      <c r="B148" s="49"/>
-      <c r="D148" s="50"/>
+      <c r="A148" s="36"/>
+      <c r="B148" s="35"/>
+      <c r="D148" s="36"/>
     </row>
     <row r="149" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A149" s="50"/>
-      <c r="B149" s="49"/>
-      <c r="D149" s="50"/>
+      <c r="A149" s="36"/>
+      <c r="B149" s="35"/>
+      <c r="D149" s="36"/>
     </row>
     <row r="150" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A150" s="50"/>
-      <c r="B150" s="49"/>
-      <c r="D150" s="50"/>
+      <c r="A150" s="36"/>
+      <c r="B150" s="35"/>
+      <c r="D150" s="36"/>
     </row>
     <row r="151" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A151" s="50"/>
-      <c r="B151" s="49"/>
-      <c r="D151" s="50"/>
+      <c r="A151" s="36"/>
+      <c r="B151" s="35"/>
+      <c r="D151" s="36"/>
     </row>
     <row r="152" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A152" s="50"/>
-      <c r="B152" s="49"/>
-      <c r="D152" s="50"/>
+      <c r="A152" s="36"/>
+      <c r="B152" s="35"/>
+      <c r="D152" s="36"/>
     </row>
     <row r="153" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A153" s="50"/>
-      <c r="B153" s="49"/>
-      <c r="D153" s="50"/>
+      <c r="A153" s="36"/>
+      <c r="B153" s="35"/>
+      <c r="D153" s="36"/>
     </row>
     <row r="154" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A154" s="50"/>
-      <c r="B154" s="49"/>
-      <c r="D154" s="50"/>
+      <c r="A154" s="36"/>
+      <c r="B154" s="35"/>
+      <c r="D154" s="36"/>
     </row>
     <row r="155" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A155" s="50"/>
-      <c r="B155" s="49"/>
-      <c r="D155" s="50"/>
+      <c r="A155" s="36"/>
+      <c r="B155" s="35"/>
+      <c r="D155" s="36"/>
     </row>
     <row r="156" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A156" s="50"/>
-      <c r="B156" s="49"/>
-      <c r="D156" s="50"/>
+      <c r="A156" s="36"/>
+      <c r="B156" s="35"/>
+      <c r="D156" s="36"/>
     </row>
     <row r="157" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A157" s="50"/>
-      <c r="B157" s="49"/>
-      <c r="D157" s="50"/>
+      <c r="A157" s="36"/>
+      <c r="B157" s="35"/>
+      <c r="D157" s="36"/>
     </row>
     <row r="158" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A158" s="50"/>
-      <c r="B158" s="49"/>
-      <c r="D158" s="50"/>
+      <c r="A158" s="36"/>
+      <c r="B158" s="35"/>
+      <c r="D158" s="36"/>
     </row>
     <row r="159" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A159" s="50"/>
-      <c r="B159" s="49"/>
-      <c r="D159" s="50"/>
+      <c r="A159" s="36"/>
+      <c r="B159" s="35"/>
+      <c r="D159" s="36"/>
     </row>
     <row r="160" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A160" s="50"/>
-      <c r="B160" s="49"/>
-      <c r="D160" s="50"/>
+      <c r="A160" s="36"/>
+      <c r="B160" s="35"/>
+      <c r="D160" s="36"/>
     </row>
     <row r="161" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A161" s="50"/>
-      <c r="B161" s="49"/>
-      <c r="D161" s="50"/>
+      <c r="A161" s="36"/>
+      <c r="B161" s="35"/>
+      <c r="D161" s="36"/>
     </row>
     <row r="162" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A162" s="50"/>
-      <c r="B162" s="49"/>
-      <c r="D162" s="50"/>
+      <c r="A162" s="36"/>
+      <c r="B162" s="35"/>
+      <c r="D162" s="36"/>
     </row>
     <row r="163" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A163" s="50"/>
-      <c r="B163" s="49"/>
-      <c r="D163" s="50"/>
+      <c r="A163" s="36"/>
+      <c r="B163" s="35"/>
+      <c r="D163" s="36"/>
     </row>
     <row r="164" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A164" s="50"/>
-      <c r="B164" s="49"/>
-      <c r="D164" s="50"/>
+      <c r="A164" s="36"/>
+      <c r="B164" s="35"/>
+      <c r="D164" s="36"/>
     </row>
     <row r="165" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A165" s="50"/>
-      <c r="B165" s="49"/>
-      <c r="D165" s="50"/>
+      <c r="A165" s="36"/>
+      <c r="B165" s="35"/>
+      <c r="D165" s="36"/>
     </row>
     <row r="166" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A166" s="50"/>
-      <c r="B166" s="49"/>
-      <c r="D166" s="50"/>
+      <c r="A166" s="36"/>
+      <c r="B166" s="35"/>
+      <c r="D166" s="36"/>
     </row>
     <row r="167" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A167" s="50"/>
-      <c r="B167" s="49"/>
-      <c r="D167" s="50"/>
+      <c r="A167" s="36"/>
+      <c r="B167" s="35"/>
+      <c r="D167" s="36"/>
     </row>
     <row r="168" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A168" s="50"/>
-      <c r="B168" s="49"/>
-      <c r="D168" s="50"/>
+      <c r="A168" s="36"/>
+      <c r="B168" s="35"/>
+      <c r="D168" s="36"/>
     </row>
     <row r="169" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A169" s="50"/>
-      <c r="B169" s="49"/>
-      <c r="D169" s="50"/>
+      <c r="A169" s="36"/>
+      <c r="B169" s="35"/>
+      <c r="D169" s="36"/>
     </row>
     <row r="170" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A170" s="50"/>
-      <c r="B170" s="49"/>
-      <c r="D170" s="50"/>
+      <c r="A170" s="36"/>
+      <c r="B170" s="35"/>
+      <c r="D170" s="36"/>
     </row>
     <row r="171" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A171" s="50"/>
-      <c r="B171" s="49"/>
-      <c r="D171" s="50"/>
+      <c r="A171" s="36"/>
+      <c r="B171" s="35"/>
+      <c r="D171" s="36"/>
     </row>
     <row r="172" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A172" s="50"/>
-      <c r="B172" s="49"/>
-      <c r="D172" s="50"/>
+      <c r="A172" s="36"/>
+      <c r="B172" s="35"/>
+      <c r="D172" s="36"/>
     </row>
     <row r="173" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A173" s="50"/>
-      <c r="B173" s="49"/>
-      <c r="D173" s="50"/>
+      <c r="A173" s="36"/>
+      <c r="B173" s="35"/>
+      <c r="D173" s="36"/>
     </row>
     <row r="174" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A174" s="50"/>
-      <c r="B174" s="49"/>
-      <c r="D174" s="50"/>
+      <c r="A174" s="36"/>
+      <c r="B174" s="35"/>
+      <c r="D174" s="36"/>
     </row>
     <row r="175" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A175" s="50"/>
-      <c r="B175" s="49"/>
-      <c r="D175" s="50"/>
+      <c r="A175" s="36"/>
+      <c r="B175" s="35"/>
+      <c r="D175" s="36"/>
     </row>
     <row r="176" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A176" s="50"/>
-      <c r="B176" s="49"/>
-      <c r="D176" s="50"/>
+      <c r="A176" s="36"/>
+      <c r="B176" s="35"/>
+      <c r="D176" s="36"/>
     </row>
     <row r="177" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A177" s="50"/>
-      <c r="B177" s="49"/>
-      <c r="D177" s="50"/>
+      <c r="A177" s="36"/>
+      <c r="B177" s="35"/>
+      <c r="D177" s="36"/>
     </row>
     <row r="178" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A178" s="50"/>
-      <c r="B178" s="49"/>
-      <c r="D178" s="50"/>
+      <c r="A178" s="36"/>
+      <c r="B178" s="35"/>
+      <c r="D178" s="36"/>
     </row>
     <row r="179" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A179" s="50"/>
-      <c r="B179" s="49"/>
-      <c r="D179" s="50"/>
+      <c r="A179" s="36"/>
+      <c r="B179" s="35"/>
+      <c r="D179" s="36"/>
     </row>
     <row r="180" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A180" s="50"/>
-      <c r="B180" s="49"/>
-      <c r="D180" s="50"/>
+      <c r="A180" s="36"/>
+      <c r="B180" s="35"/>
+      <c r="D180" s="36"/>
     </row>
     <row r="181" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A181" s="50"/>
-      <c r="B181" s="49"/>
-      <c r="D181" s="50"/>
+      <c r="A181" s="36"/>
+      <c r="B181" s="35"/>
+      <c r="D181" s="36"/>
     </row>
     <row r="182" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A182" s="50"/>
-      <c r="B182" s="49"/>
-      <c r="D182" s="50"/>
+      <c r="A182" s="36"/>
+      <c r="B182" s="35"/>
+      <c r="D182" s="36"/>
     </row>
     <row r="183" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A183" s="50"/>
-      <c r="B183" s="49"/>
-      <c r="D183" s="50"/>
+      <c r="A183" s="36"/>
+      <c r="B183" s="35"/>
+      <c r="D183" s="36"/>
     </row>
     <row r="184" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A184" s="50"/>
-      <c r="B184" s="49"/>
-      <c r="D184" s="50"/>
+      <c r="A184" s="36"/>
+      <c r="B184" s="35"/>
+      <c r="D184" s="36"/>
     </row>
     <row r="185" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A185" s="50"/>
-      <c r="B185" s="49"/>
-      <c r="D185" s="50"/>
+      <c r="A185" s="36"/>
+      <c r="B185" s="35"/>
+      <c r="D185" s="36"/>
     </row>
     <row r="186" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A186" s="50"/>
-      <c r="B186" s="49"/>
-      <c r="D186" s="50"/>
+      <c r="A186" s="36"/>
+      <c r="B186" s="35"/>
+      <c r="D186" s="36"/>
     </row>
     <row r="187" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A187" s="50"/>
-      <c r="B187" s="49"/>
-      <c r="D187" s="50"/>
+      <c r="A187" s="36"/>
+      <c r="B187" s="35"/>
+      <c r="D187" s="36"/>
     </row>
     <row r="188" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A188" s="50"/>
-      <c r="B188" s="49"/>
-      <c r="D188" s="50"/>
+      <c r="A188" s="36"/>
+      <c r="B188" s="35"/>
+      <c r="D188" s="36"/>
     </row>
     <row r="189" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A189" s="50"/>
-      <c r="B189" s="49"/>
-      <c r="D189" s="50"/>
+      <c r="A189" s="36"/>
+      <c r="B189" s="35"/>
+      <c r="D189" s="36"/>
     </row>
     <row r="190" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A190" s="50"/>
-      <c r="B190" s="49"/>
-      <c r="D190" s="50"/>
+      <c r="A190" s="36"/>
+      <c r="B190" s="35"/>
+      <c r="D190" s="36"/>
     </row>
     <row r="191" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A191" s="50"/>
-      <c r="B191" s="49"/>
-      <c r="D191" s="50"/>
+      <c r="A191" s="36"/>
+      <c r="B191" s="35"/>
+      <c r="D191" s="36"/>
     </row>
     <row r="192" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A192" s="50"/>
-      <c r="B192" s="49"/>
-      <c r="D192" s="50"/>
+      <c r="A192" s="36"/>
+      <c r="B192" s="35"/>
+      <c r="D192" s="36"/>
     </row>
     <row r="193" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A193" s="50"/>
-      <c r="B193" s="49"/>
-      <c r="D193" s="50"/>
+      <c r="A193" s="36"/>
+      <c r="B193" s="35"/>
+      <c r="D193" s="36"/>
     </row>
     <row r="194" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A194" s="50"/>
-      <c r="B194" s="49"/>
-      <c r="D194" s="50"/>
+      <c r="A194" s="36"/>
+      <c r="B194" s="35"/>
+      <c r="D194" s="36"/>
     </row>
     <row r="195" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A195" s="50"/>
-      <c r="B195" s="49"/>
-      <c r="D195" s="50"/>
+      <c r="A195" s="36"/>
+      <c r="B195" s="35"/>
+      <c r="D195" s="36"/>
     </row>
     <row r="196" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A196" s="50"/>
-      <c r="B196" s="49"/>
-      <c r="D196" s="50"/>
+      <c r="A196" s="36"/>
+      <c r="B196" s="35"/>
+      <c r="D196" s="36"/>
     </row>
     <row r="197" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A197" s="50"/>
-      <c r="B197" s="49"/>
-      <c r="D197" s="50"/>
+      <c r="A197" s="36"/>
+      <c r="B197" s="35"/>
+      <c r="D197" s="36"/>
     </row>
     <row r="198" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A198" s="50"/>
-      <c r="B198" s="49"/>
-      <c r="D198" s="50"/>
+      <c r="A198" s="36"/>
+      <c r="B198" s="35"/>
+      <c r="D198" s="36"/>
     </row>
     <row r="199" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A199" s="50"/>
-      <c r="B199" s="49"/>
-      <c r="D199" s="50"/>
+      <c r="A199" s="36"/>
+      <c r="B199" s="35"/>
+      <c r="D199" s="36"/>
     </row>
     <row r="200" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A200" s="50"/>
-      <c r="B200" s="49"/>
-      <c r="D200" s="50"/>
+      <c r="A200" s="36"/>
+      <c r="B200" s="35"/>
+      <c r="D200" s="36"/>
     </row>
     <row r="201" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A201" s="50"/>
-      <c r="B201" s="49"/>
-      <c r="D201" s="50"/>
+      <c r="A201" s="36"/>
+      <c r="B201" s="35"/>
+      <c r="D201" s="36"/>
     </row>
     <row r="202" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A202" s="50"/>
-      <c r="B202" s="49"/>
-      <c r="D202" s="50"/>
+      <c r="A202" s="36"/>
+      <c r="B202" s="35"/>
+      <c r="D202" s="36"/>
     </row>
     <row r="203" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A203" s="50"/>
-      <c r="B203" s="49"/>
-      <c r="D203" s="50"/>
+      <c r="A203" s="36"/>
+      <c r="B203" s="35"/>
+      <c r="D203" s="36"/>
     </row>
     <row r="204" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A204" s="50"/>
-      <c r="B204" s="49"/>
-      <c r="D204" s="50"/>
+      <c r="A204" s="36"/>
+      <c r="B204" s="35"/>
+      <c r="D204" s="36"/>
     </row>
     <row r="205" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A205" s="50"/>
-      <c r="B205" s="49"/>
-      <c r="D205" s="50"/>
+      <c r="A205" s="36"/>
+      <c r="B205" s="35"/>
+      <c r="D205" s="36"/>
     </row>
     <row r="206" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A206" s="50"/>
-      <c r="B206" s="49"/>
-      <c r="D206" s="50"/>
+      <c r="A206" s="36"/>
+      <c r="B206" s="35"/>
+      <c r="D206" s="36"/>
     </row>
     <row r="207" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A207" s="50"/>
-      <c r="B207" s="49"/>
-      <c r="D207" s="50"/>
+      <c r="A207" s="36"/>
+      <c r="B207" s="35"/>
+      <c r="D207" s="36"/>
     </row>
     <row r="208" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A208" s="50"/>
-      <c r="B208" s="49"/>
-      <c r="D208" s="50"/>
+      <c r="A208" s="36"/>
+      <c r="B208" s="35"/>
+      <c r="D208" s="36"/>
     </row>
     <row r="209" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A209" s="50"/>
-      <c r="B209" s="49"/>
-      <c r="D209" s="50"/>
+      <c r="A209" s="36"/>
+      <c r="B209" s="35"/>
+      <c r="D209" s="36"/>
     </row>
     <row r="210" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A210" s="50"/>
-      <c r="B210" s="49"/>
-      <c r="D210" s="50"/>
+      <c r="A210" s="36"/>
+      <c r="B210" s="35"/>
+      <c r="D210" s="36"/>
     </row>
     <row r="211" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A211" s="50"/>
-      <c r="B211" s="49"/>
-      <c r="D211" s="50"/>
+      <c r="A211" s="36"/>
+      <c r="B211" s="35"/>
+      <c r="D211" s="36"/>
     </row>
     <row r="212" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A212" s="50"/>
-      <c r="B212" s="49"/>
-      <c r="D212" s="50"/>
+      <c r="A212" s="36"/>
+      <c r="B212" s="35"/>
+      <c r="D212" s="36"/>
     </row>
     <row r="213" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A213" s="50"/>
-      <c r="B213" s="49"/>
-      <c r="D213" s="50"/>
+      <c r="A213" s="36"/>
+      <c r="B213" s="35"/>
+      <c r="D213" s="36"/>
     </row>
     <row r="214" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A214" s="50"/>
-      <c r="B214" s="49"/>
-      <c r="D214" s="50"/>
+      <c r="A214" s="36"/>
+      <c r="B214" s="35"/>
+      <c r="D214" s="36"/>
     </row>
     <row r="215" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A215" s="50"/>
-      <c r="B215" s="49"/>
-      <c r="D215" s="50"/>
+      <c r="A215" s="36"/>
+      <c r="B215" s="35"/>
+      <c r="D215" s="36"/>
     </row>
     <row r="216" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A216" s="50"/>
-      <c r="B216" s="49"/>
-      <c r="D216" s="50"/>
+      <c r="A216" s="36"/>
+      <c r="B216" s="35"/>
+      <c r="D216" s="36"/>
     </row>
     <row r="217" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A217" s="50"/>
-      <c r="B217" s="49"/>
-      <c r="D217" s="50"/>
+      <c r="A217" s="36"/>
+      <c r="B217" s="35"/>
+      <c r="D217" s="36"/>
     </row>
     <row r="218" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A218" s="50"/>
-      <c r="B218" s="49"/>
-      <c r="D218" s="50"/>
+      <c r="A218" s="36"/>
+      <c r="B218" s="35"/>
+      <c r="D218" s="36"/>
     </row>
     <row r="219" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A219" s="50"/>
-      <c r="B219" s="49"/>
-      <c r="D219" s="50"/>
+      <c r="A219" s="36"/>
+      <c r="B219" s="35"/>
+      <c r="D219" s="36"/>
     </row>
     <row r="220" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A220" s="50"/>
-      <c r="B220" s="49"/>
-      <c r="D220" s="50"/>
+      <c r="A220" s="36"/>
+      <c r="B220" s="35"/>
+      <c r="D220" s="36"/>
     </row>
     <row r="221" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A221" s="50"/>
-      <c r="B221" s="49"/>
-      <c r="D221" s="50"/>
+      <c r="A221" s="36"/>
+      <c r="B221" s="35"/>
+      <c r="D221" s="36"/>
     </row>
     <row r="222" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A222" s="50"/>
-      <c r="B222" s="49"/>
-      <c r="D222" s="50"/>
+      <c r="A222" s="36"/>
+      <c r="B222" s="35"/>
+      <c r="D222" s="36"/>
     </row>
     <row r="223" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A223" s="50"/>
-      <c r="B223" s="49"/>
-      <c r="D223" s="50"/>
+      <c r="A223" s="36"/>
+      <c r="B223" s="35"/>
+      <c r="D223" s="36"/>
     </row>
     <row r="224" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A224" s="50"/>
-      <c r="B224" s="49"/>
-      <c r="D224" s="50"/>
+      <c r="A224" s="36"/>
+      <c r="B224" s="35"/>
+      <c r="D224" s="36"/>
     </row>
     <row r="225" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A225" s="50"/>
-      <c r="B225" s="49"/>
-      <c r="D225" s="50"/>
+      <c r="A225" s="36"/>
+      <c r="B225" s="35"/>
+      <c r="D225" s="36"/>
     </row>
     <row r="226" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A226" s="50"/>
-      <c r="B226" s="49"/>
-      <c r="D226" s="50"/>
+      <c r="A226" s="36"/>
+      <c r="B226" s="35"/>
+      <c r="D226" s="36"/>
     </row>
     <row r="227" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A227" s="50"/>
-      <c r="B227" s="49"/>
-      <c r="D227" s="50"/>
+      <c r="A227" s="36"/>
+      <c r="B227" s="35"/>
+      <c r="D227" s="36"/>
     </row>
     <row r="228" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A228" s="50"/>
-      <c r="B228" s="49"/>
-      <c r="D228" s="50"/>
+      <c r="A228" s="36"/>
+      <c r="B228" s="35"/>
+      <c r="D228" s="36"/>
     </row>
     <row r="229" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A229" s="50"/>
-      <c r="B229" s="49"/>
-      <c r="D229" s="50"/>
+      <c r="A229" s="36"/>
+      <c r="B229" s="35"/>
+      <c r="D229" s="36"/>
     </row>
     <row r="230" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A230" s="50"/>
-      <c r="B230" s="49"/>
-      <c r="D230" s="50"/>
+      <c r="A230" s="36"/>
+      <c r="B230" s="35"/>
+      <c r="D230" s="36"/>
     </row>
     <row r="231" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A231" s="50"/>
-      <c r="B231" s="49"/>
-      <c r="D231" s="50"/>
+      <c r="A231" s="36"/>
+      <c r="B231" s="35"/>
+      <c r="D231" s="36"/>
     </row>
     <row r="232" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A232" s="50"/>
-      <c r="B232" s="49"/>
-      <c r="D232" s="50"/>
+      <c r="A232" s="36"/>
+      <c r="B232" s="35"/>
+      <c r="D232" s="36"/>
     </row>
     <row r="233" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A233" s="50"/>
-      <c r="B233" s="49"/>
-      <c r="D233" s="50"/>
+      <c r="A233" s="36"/>
+      <c r="B233" s="35"/>
+      <c r="D233" s="36"/>
     </row>
     <row r="234" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A234" s="50"/>
-      <c r="B234" s="49"/>
-      <c r="D234" s="50"/>
+      <c r="A234" s="36"/>
+      <c r="B234" s="35"/>
+      <c r="D234" s="36"/>
     </row>
     <row r="235" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A235" s="50"/>
-      <c r="B235" s="49"/>
-      <c r="D235" s="50"/>
+      <c r="A235" s="36"/>
+      <c r="B235" s="35"/>
+      <c r="D235" s="36"/>
     </row>
     <row r="236" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A236" s="50"/>
-      <c r="B236" s="49"/>
-      <c r="D236" s="50"/>
+      <c r="A236" s="36"/>
+      <c r="B236" s="35"/>
+      <c r="D236" s="36"/>
     </row>
     <row r="237" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A237" s="50"/>
-      <c r="B237" s="49"/>
-      <c r="D237" s="50"/>
+      <c r="A237" s="36"/>
+      <c r="B237" s="35"/>
+      <c r="D237" s="36"/>
     </row>
     <row r="238" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A238" s="50"/>
-      <c r="B238" s="49"/>
-      <c r="D238" s="50"/>
+      <c r="A238" s="36"/>
+      <c r="B238" s="35"/>
+      <c r="D238" s="36"/>
     </row>
     <row r="239" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A239" s="50"/>
-      <c r="B239" s="49"/>
-      <c r="D239" s="50"/>
+      <c r="A239" s="36"/>
+      <c r="B239" s="35"/>
+      <c r="D239" s="36"/>
     </row>
     <row r="240" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A240" s="50"/>
-      <c r="B240" s="49"/>
-      <c r="D240" s="50"/>
+      <c r="A240" s="36"/>
+      <c r="B240" s="35"/>
+      <c r="D240" s="36"/>
     </row>
     <row r="241" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A241" s="50"/>
-      <c r="B241" s="49"/>
-      <c r="D241" s="50"/>
+      <c r="A241" s="36"/>
+      <c r="B241" s="35"/>
+      <c r="D241" s="36"/>
     </row>
     <row r="242" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A242" s="50"/>
-      <c r="B242" s="49"/>
-      <c r="D242" s="50"/>
+      <c r="A242" s="36"/>
+      <c r="B242" s="35"/>
+      <c r="D242" s="36"/>
     </row>
     <row r="243" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A243" s="50"/>
-      <c r="B243" s="49"/>
-      <c r="D243" s="50"/>
+      <c r="A243" s="36"/>
+      <c r="B243" s="35"/>
+      <c r="D243" s="36"/>
     </row>
     <row r="244" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A244" s="50"/>
-      <c r="B244" s="49"/>
-      <c r="D244" s="50"/>
+      <c r="A244" s="36"/>
+      <c r="B244" s="35"/>
+      <c r="D244" s="36"/>
     </row>
     <row r="245" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A245" s="50"/>
-      <c r="B245" s="49"/>
-      <c r="D245" s="50"/>
+      <c r="A245" s="36"/>
+      <c r="B245" s="35"/>
+      <c r="D245" s="36"/>
     </row>
     <row r="246" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A246" s="50"/>
-      <c r="B246" s="49"/>
-      <c r="D246" s="50"/>
+      <c r="A246" s="36"/>
+      <c r="B246" s="35"/>
+      <c r="D246" s="36"/>
     </row>
     <row r="247" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A247" s="50"/>
-      <c r="B247" s="49"/>
-      <c r="D247" s="50"/>
+      <c r="A247" s="36"/>
+      <c r="B247" s="35"/>
+      <c r="D247" s="36"/>
     </row>
     <row r="248" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A248" s="50"/>
-      <c r="B248" s="49"/>
-      <c r="D248" s="50"/>
+      <c r="A248" s="36"/>
+      <c r="B248" s="35"/>
+      <c r="D248" s="36"/>
     </row>
     <row r="249" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A249" s="50"/>
-      <c r="B249" s="49"/>
-      <c r="D249" s="50"/>
+      <c r="A249" s="36"/>
+      <c r="B249" s="35"/>
+      <c r="D249" s="36"/>
     </row>
     <row r="250" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A250" s="50"/>
-      <c r="B250" s="49"/>
-      <c r="D250" s="50"/>
+      <c r="A250" s="36"/>
+      <c r="B250" s="35"/>
+      <c r="D250" s="36"/>
     </row>
     <row r="251" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A251" s="50"/>
-      <c r="B251" s="49"/>
-      <c r="D251" s="50"/>
+      <c r="A251" s="36"/>
+      <c r="B251" s="35"/>
+      <c r="D251" s="36"/>
     </row>
     <row r="252" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A252" s="50"/>
-      <c r="B252" s="49"/>
-      <c r="D252" s="50"/>
+      <c r="A252" s="36"/>
+      <c r="B252" s="35"/>
+      <c r="D252" s="36"/>
     </row>
     <row r="253" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A253" s="50"/>
-      <c r="B253" s="49"/>
-      <c r="D253" s="50"/>
+      <c r="A253" s="36"/>
+      <c r="B253" s="35"/>
+      <c r="D253" s="36"/>
     </row>
     <row r="254" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A254" s="50"/>
-      <c r="B254" s="49"/>
-      <c r="D254" s="50"/>
+      <c r="A254" s="36"/>
+      <c r="B254" s="35"/>
+      <c r="D254" s="36"/>
     </row>
     <row r="255" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A255" s="50"/>
-      <c r="B255" s="49"/>
-      <c r="D255" s="50"/>
+      <c r="A255" s="36"/>
+      <c r="B255" s="35"/>
+      <c r="D255" s="36"/>
     </row>
     <row r="256" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A256" s="50"/>
-      <c r="B256" s="49"/>
-      <c r="D256" s="50"/>
+      <c r="A256" s="36"/>
+      <c r="B256" s="35"/>
+      <c r="D256" s="36"/>
     </row>
     <row r="257" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A257" s="50"/>
-      <c r="B257" s="49"/>
-      <c r="D257" s="50"/>
+      <c r="A257" s="36"/>
+      <c r="B257" s="35"/>
+      <c r="D257" s="36"/>
     </row>
     <row r="258" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A258" s="50"/>
-      <c r="B258" s="49"/>
-      <c r="D258" s="50"/>
+      <c r="A258" s="36"/>
+      <c r="B258" s="35"/>
+      <c r="D258" s="36"/>
     </row>
     <row r="259" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A259" s="50"/>
-      <c r="B259" s="49"/>
-      <c r="D259" s="50"/>
+      <c r="A259" s="36"/>
+      <c r="B259" s="35"/>
+      <c r="D259" s="36"/>
     </row>
     <row r="260" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A260" s="50"/>
-      <c r="B260" s="49"/>
-      <c r="D260" s="50"/>
+      <c r="A260" s="36"/>
+      <c r="B260" s="35"/>
+      <c r="D260" s="36"/>
     </row>
     <row r="261" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A261" s="50"/>
-      <c r="B261" s="49"/>
-      <c r="D261" s="50"/>
+      <c r="A261" s="36"/>
+      <c r="B261" s="35"/>
+      <c r="D261" s="36"/>
     </row>
     <row r="262" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A262" s="50"/>
-      <c r="B262" s="49"/>
-      <c r="D262" s="50"/>
+      <c r="A262" s="36"/>
+      <c r="B262" s="35"/>
+      <c r="D262" s="36"/>
     </row>
     <row r="263" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A263" s="50"/>
-      <c r="B263" s="49"/>
-      <c r="D263" s="50"/>
+      <c r="A263" s="36"/>
+      <c r="B263" s="35"/>
+      <c r="D263" s="36"/>
     </row>
     <row r="264" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A264" s="50"/>
-      <c r="B264" s="49"/>
-      <c r="D264" s="50"/>
+      <c r="A264" s="36"/>
+      <c r="B264" s="35"/>
+      <c r="D264" s="36"/>
     </row>
     <row r="265" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A265" s="50"/>
-      <c r="B265" s="49"/>
-      <c r="D265" s="50"/>
+      <c r="A265" s="36"/>
+      <c r="B265" s="35"/>
+      <c r="D265" s="36"/>
     </row>
     <row r="266" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A266" s="50"/>
-      <c r="B266" s="49"/>
-      <c r="D266" s="50"/>
+      <c r="A266" s="36"/>
+      <c r="B266" s="35"/>
+      <c r="D266" s="36"/>
     </row>
     <row r="267" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A267" s="50"/>
-      <c r="B267" s="49"/>
-      <c r="D267" s="50"/>
+      <c r="A267" s="36"/>
+      <c r="B267" s="35"/>
+      <c r="D267" s="36"/>
     </row>
     <row r="268" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A268" s="50"/>
-      <c r="B268" s="49"/>
-      <c r="D268" s="50"/>
+      <c r="A268" s="36"/>
+      <c r="B268" s="35"/>
+      <c r="D268" s="36"/>
     </row>
     <row r="269" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A269" s="50"/>
-      <c r="B269" s="49"/>
-      <c r="D269" s="50"/>
+      <c r="A269" s="36"/>
+      <c r="B269" s="35"/>
+      <c r="D269" s="36"/>
     </row>
     <row r="270" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A270" s="50"/>
-      <c r="B270" s="49"/>
-      <c r="D270" s="50"/>
+      <c r="A270" s="36"/>
+      <c r="B270" s="35"/>
+      <c r="D270" s="36"/>
     </row>
     <row r="271" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A271" s="50"/>
-      <c r="B271" s="49"/>
-      <c r="D271" s="50"/>
+      <c r="A271" s="36"/>
+      <c r="B271" s="35"/>
+      <c r="D271" s="36"/>
     </row>
     <row r="272" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A272" s="50"/>
-      <c r="B272" s="49"/>
-      <c r="D272" s="50"/>
+      <c r="A272" s="36"/>
+      <c r="B272" s="35"/>
+      <c r="D272" s="36"/>
     </row>
     <row r="273" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A273" s="50"/>
-      <c r="B273" s="49"/>
-      <c r="D273" s="50"/>
+      <c r="A273" s="36"/>
+      <c r="B273" s="35"/>
+      <c r="D273" s="36"/>
     </row>
     <row r="274" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A274" s="50"/>
-      <c r="B274" s="49"/>
-      <c r="D274" s="50"/>
+      <c r="A274" s="36"/>
+      <c r="B274" s="35"/>
+      <c r="D274" s="36"/>
     </row>
     <row r="275" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A275" s="50"/>
-      <c r="B275" s="49"/>
-      <c r="D275" s="50"/>
+      <c r="A275" s="36"/>
+      <c r="B275" s="35"/>
+      <c r="D275" s="36"/>
     </row>
     <row r="276" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A276" s="50"/>
-      <c r="B276" s="49"/>
-      <c r="D276" s="50"/>
+      <c r="A276" s="36"/>
+      <c r="B276" s="35"/>
+      <c r="D276" s="36"/>
     </row>
     <row r="277" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A277" s="50"/>
-      <c r="B277" s="49"/>
-      <c r="D277" s="50"/>
+      <c r="A277" s="36"/>
+      <c r="B277" s="35"/>
+      <c r="D277" s="36"/>
     </row>
     <row r="278" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A278" s="50"/>
-      <c r="B278" s="49"/>
-      <c r="D278" s="50"/>
+      <c r="A278" s="36"/>
+      <c r="B278" s="35"/>
+      <c r="D278" s="36"/>
     </row>
     <row r="279" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A279" s="50"/>
-      <c r="B279" s="49"/>
-      <c r="D279" s="50"/>
+      <c r="A279" s="36"/>
+      <c r="B279" s="35"/>
+      <c r="D279" s="36"/>
     </row>
     <row r="280" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A280" s="50"/>
-      <c r="B280" s="49"/>
-      <c r="D280" s="50"/>
+      <c r="A280" s="36"/>
+      <c r="B280" s="35"/>
+      <c r="D280" s="36"/>
     </row>
     <row r="281" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A281" s="50"/>
-      <c r="B281" s="49"/>
-      <c r="D281" s="50"/>
+      <c r="A281" s="36"/>
+      <c r="B281" s="35"/>
+      <c r="D281" s="36"/>
     </row>
     <row r="282" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A282" s="50"/>
-      <c r="B282" s="49"/>
-      <c r="D282" s="50"/>
+      <c r="A282" s="36"/>
+      <c r="B282" s="35"/>
+      <c r="D282" s="36"/>
     </row>
     <row r="283" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A283" s="50"/>
-      <c r="B283" s="49"/>
-      <c r="D283" s="50"/>
+      <c r="A283" s="36"/>
+      <c r="B283" s="35"/>
+      <c r="D283" s="36"/>
     </row>
     <row r="284" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A284" s="50"/>
-      <c r="B284" s="49"/>
-      <c r="D284" s="50"/>
+      <c r="A284" s="36"/>
+      <c r="B284" s="35"/>
+      <c r="D284" s="36"/>
     </row>
     <row r="285" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A285" s="50"/>
-      <c r="B285" s="49"/>
-      <c r="D285" s="50"/>
+      <c r="A285" s="36"/>
+      <c r="B285" s="35"/>
+      <c r="D285" s="36"/>
     </row>
     <row r="286" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A286" s="50"/>
-      <c r="B286" s="49"/>
-      <c r="D286" s="50"/>
+      <c r="A286" s="36"/>
+      <c r="B286" s="35"/>
+      <c r="D286" s="36"/>
     </row>
     <row r="287" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A287" s="50"/>
-      <c r="B287" s="49"/>
-      <c r="D287" s="50"/>
+      <c r="A287" s="36"/>
+      <c r="B287" s="35"/>
+      <c r="D287" s="36"/>
     </row>
     <row r="288" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A288" s="50"/>
-      <c r="B288" s="49"/>
-      <c r="D288" s="50"/>
+      <c r="A288" s="36"/>
+      <c r="B288" s="35"/>
+      <c r="D288" s="36"/>
     </row>
     <row r="289" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A289" s="50"/>
-      <c r="B289" s="49"/>
-      <c r="D289" s="50"/>
+      <c r="A289" s="36"/>
+      <c r="B289" s="35"/>
+      <c r="D289" s="36"/>
     </row>
     <row r="290" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A290" s="50"/>
-      <c r="B290" s="49"/>
-      <c r="D290" s="50"/>
+      <c r="A290" s="36"/>
+      <c r="B290" s="35"/>
+      <c r="D290" s="36"/>
     </row>
     <row r="291" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A291" s="50"/>
-      <c r="B291" s="49"/>
-      <c r="D291" s="50"/>
+      <c r="A291" s="36"/>
+      <c r="B291" s="35"/>
+      <c r="D291" s="36"/>
     </row>
     <row r="292" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A292" s="50"/>
-      <c r="B292" s="49"/>
-      <c r="D292" s="50"/>
+      <c r="A292" s="36"/>
+      <c r="B292" s="35"/>
+      <c r="D292" s="36"/>
     </row>
     <row r="293" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A293" s="50"/>
-      <c r="B293" s="49"/>
-      <c r="D293" s="50"/>
+      <c r="A293" s="36"/>
+      <c r="B293" s="35"/>
+      <c r="D293" s="36"/>
     </row>
     <row r="294" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A294" s="50"/>
-      <c r="B294" s="49"/>
-      <c r="D294" s="50"/>
+      <c r="A294" s="36"/>
+      <c r="B294" s="35"/>
+      <c r="D294" s="36"/>
     </row>
     <row r="295" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A295" s="50"/>
-      <c r="B295" s="49"/>
-      <c r="D295" s="50"/>
+      <c r="A295" s="36"/>
+      <c r="B295" s="35"/>
+      <c r="D295" s="36"/>
     </row>
     <row r="296" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A296" s="50"/>
-      <c r="B296" s="49"/>
-      <c r="D296" s="50"/>
+      <c r="A296" s="36"/>
+      <c r="B296" s="35"/>
+      <c r="D296" s="36"/>
     </row>
     <row r="297" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A297" s="50"/>
-      <c r="B297" s="49"/>
-      <c r="D297" s="50"/>
+      <c r="A297" s="36"/>
+      <c r="B297" s="35"/>
+      <c r="D297" s="36"/>
     </row>
     <row r="298" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A298" s="50"/>
-      <c r="B298" s="49"/>
-      <c r="D298" s="50"/>
+      <c r="A298" s="36"/>
+      <c r="B298" s="35"/>
+      <c r="D298" s="36"/>
     </row>
     <row r="299" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A299" s="50"/>
-      <c r="B299" s="49"/>
-      <c r="D299" s="50"/>
+      <c r="A299" s="36"/>
+      <c r="B299" s="35"/>
+      <c r="D299" s="36"/>
     </row>
     <row r="300" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A300" s="50"/>
-      <c r="B300" s="49"/>
-      <c r="D300" s="50"/>
+      <c r="A300" s="36"/>
+      <c r="B300" s="35"/>
+      <c r="D300" s="36"/>
     </row>
     <row r="301" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A301" s="50"/>
-      <c r="B301" s="49"/>
-      <c r="D301" s="50"/>
+      <c r="A301" s="36"/>
+      <c r="B301" s="35"/>
+      <c r="D301" s="36"/>
     </row>
     <row r="302" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A302" s="50"/>
-      <c r="B302" s="49"/>
-      <c r="D302" s="50"/>
+      <c r="A302" s="36"/>
+      <c r="B302" s="35"/>
+      <c r="D302" s="36"/>
     </row>
     <row r="303" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A303" s="50"/>
-      <c r="B303" s="49"/>
-      <c r="D303" s="50"/>
+      <c r="A303" s="36"/>
+      <c r="B303" s="35"/>
+      <c r="D303" s="36"/>
     </row>
     <row r="304" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A304" s="50"/>
-      <c r="B304" s="49"/>
-      <c r="D304" s="50"/>
+      <c r="A304" s="36"/>
+      <c r="B304" s="35"/>
+      <c r="D304" s="36"/>
     </row>
     <row r="305" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A305" s="50"/>
-      <c r="B305" s="49"/>
-      <c r="D305" s="50"/>
+      <c r="A305" s="36"/>
+      <c r="B305" s="35"/>
+      <c r="D305" s="36"/>
     </row>
     <row r="306" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A306" s="50"/>
-      <c r="B306" s="49"/>
-      <c r="D306" s="50"/>
+      <c r="A306" s="36"/>
+      <c r="B306" s="35"/>
+      <c r="D306" s="36"/>
     </row>
     <row r="307" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A307" s="50"/>
-      <c r="B307" s="49"/>
-      <c r="D307" s="50"/>
+      <c r="A307" s="36"/>
+      <c r="B307" s="35"/>
+      <c r="D307" s="36"/>
     </row>
     <row r="308" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A308" s="50"/>
-      <c r="B308" s="49"/>
-      <c r="D308" s="50"/>
+      <c r="A308" s="36"/>
+      <c r="B308" s="35"/>
+      <c r="D308" s="36"/>
     </row>
     <row r="309" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A309" s="50"/>
-      <c r="B309" s="49"/>
-      <c r="D309" s="50"/>
+      <c r="A309" s="36"/>
+      <c r="B309" s="35"/>
+      <c r="D309" s="36"/>
     </row>
     <row r="310" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A310" s="50"/>
-      <c r="B310" s="49"/>
-      <c r="D310" s="50"/>
+      <c r="A310" s="36"/>
+      <c r="B310" s="35"/>
+      <c r="D310" s="36"/>
     </row>
     <row r="311" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A311" s="50"/>
-      <c r="B311" s="49"/>
-      <c r="D311" s="50"/>
+      <c r="A311" s="36"/>
+      <c r="B311" s="35"/>
+      <c r="D311" s="36"/>
     </row>
     <row r="312" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A312" s="50"/>
-      <c r="B312" s="49"/>
-      <c r="D312" s="50"/>
+      <c r="A312" s="36"/>
+      <c r="B312" s="35"/>
+      <c r="D312" s="36"/>
     </row>
     <row r="313" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A313" s="50"/>
-      <c r="B313" s="49"/>
-      <c r="D313" s="50"/>
+      <c r="A313" s="36"/>
+      <c r="B313" s="35"/>
+      <c r="D313" s="36"/>
     </row>
     <row r="314" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A314" s="50"/>
-      <c r="B314" s="49"/>
-      <c r="D314" s="50"/>
+      <c r="A314" s="36"/>
+      <c r="B314" s="35"/>
+      <c r="D314" s="36"/>
     </row>
     <row r="315" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A315" s="50"/>
-      <c r="B315" s="49"/>
-      <c r="D315" s="50"/>
+      <c r="A315" s="36"/>
+      <c r="B315" s="35"/>
+      <c r="D315" s="36"/>
     </row>
     <row r="316" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A316" s="50"/>
-      <c r="B316" s="49"/>
-      <c r="D316" s="50"/>
+      <c r="A316" s="36"/>
+      <c r="B316" s="35"/>
+      <c r="D316" s="36"/>
     </row>
     <row r="317" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A317" s="50"/>
-      <c r="B317" s="49"/>
-      <c r="D317" s="50"/>
+      <c r="A317" s="36"/>
+      <c r="B317" s="35"/>
+      <c r="D317" s="36"/>
     </row>
     <row r="318" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A318" s="50"/>
-      <c r="B318" s="49"/>
-      <c r="D318" s="50"/>
+      <c r="A318" s="36"/>
+      <c r="B318" s="35"/>
+      <c r="D318" s="36"/>
     </row>
     <row r="319" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A319" s="50"/>
-      <c r="B319" s="49"/>
-      <c r="D319" s="50"/>
+      <c r="A319" s="36"/>
+      <c r="B319" s="35"/>
+      <c r="D319" s="36"/>
     </row>
     <row r="320" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A320" s="50"/>
-      <c r="B320" s="49"/>
-      <c r="D320" s="50"/>
+      <c r="A320" s="36"/>
+      <c r="B320" s="35"/>
+      <c r="D320" s="36"/>
     </row>
     <row r="321" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A321" s="50"/>
-      <c r="B321" s="49"/>
-      <c r="D321" s="50"/>
+      <c r="A321" s="36"/>
+      <c r="B321" s="35"/>
+      <c r="D321" s="36"/>
     </row>
     <row r="322" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A322" s="50"/>
-      <c r="B322" s="49"/>
-      <c r="D322" s="50"/>
+      <c r="A322" s="36"/>
+      <c r="B322" s="35"/>
+      <c r="D322" s="36"/>
     </row>
     <row r="323" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A323" s="50"/>
-      <c r="B323" s="49"/>
-      <c r="D323" s="50"/>
+      <c r="A323" s="36"/>
+      <c r="B323" s="35"/>
+      <c r="D323" s="36"/>
     </row>
     <row r="324" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A324" s="50"/>
-      <c r="B324" s="49"/>
-      <c r="D324" s="50"/>
+      <c r="A324" s="36"/>
+      <c r="B324" s="35"/>
+      <c r="D324" s="36"/>
     </row>
     <row r="325" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A325" s="50"/>
-      <c r="B325" s="49"/>
-      <c r="D325" s="50"/>
+      <c r="A325" s="36"/>
+      <c r="B325" s="35"/>
+      <c r="D325" s="36"/>
     </row>
     <row r="326" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A326" s="50"/>
-      <c r="B326" s="49"/>
-      <c r="D326" s="50"/>
+      <c r="A326" s="36"/>
+      <c r="B326" s="35"/>
+      <c r="D326" s="36"/>
     </row>
     <row r="327" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A327" s="50"/>
-      <c r="B327" s="49"/>
-      <c r="D327" s="50"/>
+      <c r="A327" s="36"/>
+      <c r="B327" s="35"/>
+      <c r="D327" s="36"/>
     </row>
     <row r="328" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A328" s="50"/>
-      <c r="B328" s="49"/>
-      <c r="D328" s="50"/>
+      <c r="A328" s="36"/>
+      <c r="B328" s="35"/>
+      <c r="D328" s="36"/>
     </row>
     <row r="329" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A329" s="50"/>
-      <c r="B329" s="49"/>
-      <c r="D329" s="50"/>
+      <c r="A329" s="36"/>
+      <c r="B329" s="35"/>
+      <c r="D329" s="36"/>
     </row>
     <row r="330" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A330" s="50"/>
-      <c r="B330" s="49"/>
-      <c r="D330" s="50"/>
+      <c r="A330" s="36"/>
+      <c r="B330" s="35"/>
+      <c r="D330" s="36"/>
     </row>
     <row r="331" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A331" s="50"/>
-      <c r="B331" s="49"/>
-      <c r="D331" s="50"/>
+      <c r="A331" s="36"/>
+      <c r="B331" s="35"/>
+      <c r="D331" s="36"/>
     </row>
     <row r="332" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A332" s="50"/>
-      <c r="B332" s="49"/>
-      <c r="D332" s="50"/>
+      <c r="A332" s="36"/>
+      <c r="B332" s="35"/>
+      <c r="D332" s="36"/>
     </row>
     <row r="333" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A333" s="50"/>
-      <c r="B333" s="49"/>
-      <c r="D333" s="50"/>
+      <c r="A333" s="36"/>
+      <c r="B333" s="35"/>
+      <c r="D333" s="36"/>
     </row>
     <row r="334" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A334" s="50"/>
-      <c r="B334" s="49"/>
-      <c r="D334" s="50"/>
+      <c r="A334" s="36"/>
+      <c r="B334" s="35"/>
+      <c r="D334" s="36"/>
     </row>
     <row r="335" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A335" s="50"/>
-      <c r="B335" s="49"/>
-      <c r="D335" s="50"/>
+      <c r="A335" s="36"/>
+      <c r="B335" s="35"/>
+      <c r="D335" s="36"/>
     </row>
     <row r="336" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A336" s="50"/>
-      <c r="B336" s="49"/>
-      <c r="D336" s="50"/>
+      <c r="A336" s="36"/>
+      <c r="B336" s="35"/>
+      <c r="D336" s="36"/>
     </row>
     <row r="337" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A337" s="50"/>
-      <c r="B337" s="49"/>
-      <c r="D337" s="50"/>
+      <c r="A337" s="36"/>
+      <c r="B337" s="35"/>
+      <c r="D337" s="36"/>
     </row>
     <row r="338" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A338" s="50"/>
-      <c r="B338" s="49"/>
-      <c r="D338" s="50"/>
+      <c r="A338" s="36"/>
+      <c r="B338" s="35"/>
+      <c r="D338" s="36"/>
     </row>
     <row r="339" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A339" s="50"/>
-      <c r="B339" s="49"/>
-      <c r="D339" s="50"/>
+      <c r="A339" s="36"/>
+      <c r="B339" s="35"/>
+      <c r="D339" s="36"/>
     </row>
     <row r="340" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A340" s="50"/>
-      <c r="B340" s="49"/>
-      <c r="D340" s="50"/>
+      <c r="A340" s="36"/>
+      <c r="B340" s="35"/>
+      <c r="D340" s="36"/>
     </row>
     <row r="341" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A341" s="50"/>
-      <c r="B341" s="49"/>
-      <c r="D341" s="50"/>
+      <c r="A341" s="36"/>
+      <c r="B341" s="35"/>
+      <c r="D341" s="36"/>
     </row>
     <row r="342" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A342" s="50"/>
-      <c r="B342" s="49"/>
-      <c r="D342" s="50"/>
+      <c r="A342" s="36"/>
+      <c r="B342" s="35"/>
+      <c r="D342" s="36"/>
     </row>
     <row r="343" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A343" s="50"/>
-      <c r="B343" s="49"/>
-      <c r="D343" s="50"/>
+      <c r="A343" s="36"/>
+      <c r="B343" s="35"/>
+      <c r="D343" s="36"/>
     </row>
     <row r="344" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A344" s="50"/>
-      <c r="B344" s="49"/>
-      <c r="D344" s="50"/>
+      <c r="A344" s="36"/>
+      <c r="B344" s="35"/>
+      <c r="D344" s="36"/>
     </row>
     <row r="345" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A345" s="50"/>
-      <c r="B345" s="49"/>
-      <c r="D345" s="50"/>
+      <c r="A345" s="36"/>
+      <c r="B345" s="35"/>
+      <c r="D345" s="36"/>
     </row>
     <row r="346" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A346" s="50"/>
-      <c r="B346" s="49"/>
-      <c r="D346" s="50"/>
+      <c r="A346" s="36"/>
+      <c r="B346" s="35"/>
+      <c r="D346" s="36"/>
     </row>
     <row r="347" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A347" s="50"/>
-      <c r="B347" s="49"/>
-      <c r="D347" s="50"/>
+      <c r="A347" s="36"/>
+      <c r="B347" s="35"/>
+      <c r="D347" s="36"/>
     </row>
     <row r="348" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A348" s="50"/>
-      <c r="B348" s="49"/>
-      <c r="D348" s="50"/>
+      <c r="A348" s="36"/>
+      <c r="B348" s="35"/>
+      <c r="D348" s="36"/>
     </row>
     <row r="349" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A349" s="50"/>
-      <c r="B349" s="49"/>
-      <c r="D349" s="50"/>
+      <c r="A349" s="36"/>
+      <c r="B349" s="35"/>
+      <c r="D349" s="36"/>
     </row>
     <row r="350" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A350" s="50"/>
-      <c r="B350" s="49"/>
-      <c r="D350" s="50"/>
+      <c r="A350" s="36"/>
+      <c r="B350" s="35"/>
+      <c r="D350" s="36"/>
     </row>
     <row r="351" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A351" s="50"/>
-      <c r="B351" s="49"/>
-      <c r="D351" s="50"/>
+      <c r="A351" s="36"/>
+      <c r="B351" s="35"/>
+      <c r="D351" s="36"/>
     </row>
     <row r="352" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A352" s="50"/>
-      <c r="B352" s="49"/>
-      <c r="D352" s="50"/>
+      <c r="A352" s="36"/>
+      <c r="B352" s="35"/>
+      <c r="D352" s="36"/>
     </row>
     <row r="353" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A353" s="50"/>
-      <c r="B353" s="49"/>
-      <c r="D353" s="50"/>
+      <c r="A353" s="36"/>
+      <c r="B353" s="35"/>
+      <c r="D353" s="36"/>
     </row>
     <row r="354" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A354" s="50"/>
-      <c r="B354" s="49"/>
-      <c r="D354" s="50"/>
+      <c r="A354" s="36"/>
+      <c r="B354" s="35"/>
+      <c r="D354" s="36"/>
     </row>
     <row r="355" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A355" s="50"/>
-      <c r="B355" s="49"/>
-      <c r="D355" s="50"/>
+      <c r="A355" s="36"/>
+      <c r="B355" s="35"/>
+      <c r="D355" s="36"/>
     </row>
     <row r="356" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A356" s="50"/>
-      <c r="B356" s="49"/>
-      <c r="D356" s="50"/>
+      <c r="A356" s="36"/>
+      <c r="B356" s="35"/>
+      <c r="D356" s="36"/>
     </row>
     <row r="357" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A357" s="50"/>
-      <c r="B357" s="49"/>
-      <c r="D357" s="50"/>
+      <c r="A357" s="36"/>
+      <c r="B357" s="35"/>
+      <c r="D357" s="36"/>
     </row>
     <row r="358" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A358" s="50"/>
-      <c r="B358" s="49"/>
-      <c r="D358" s="50"/>
+      <c r="A358" s="36"/>
+      <c r="B358" s="35"/>
+      <c r="D358" s="36"/>
     </row>
     <row r="359" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A359" s="50"/>
-      <c r="B359" s="49"/>
-      <c r="D359" s="50"/>
+      <c r="A359" s="36"/>
+      <c r="B359" s="35"/>
+      <c r="D359" s="36"/>
     </row>
     <row r="360" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A360" s="50"/>
-      <c r="B360" s="49"/>
-      <c r="D360" s="50"/>
+      <c r="A360" s="36"/>
+      <c r="B360" s="35"/>
+      <c r="D360" s="36"/>
     </row>
     <row r="361" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A361" s="50"/>
-      <c r="B361" s="49"/>
-      <c r="D361" s="50"/>
+      <c r="A361" s="36"/>
+      <c r="B361" s="35"/>
+      <c r="D361" s="36"/>
     </row>
     <row r="362" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A362" s="50"/>
-      <c r="B362" s="49"/>
-      <c r="D362" s="50"/>
+      <c r="A362" s="36"/>
+      <c r="B362" s="35"/>
+      <c r="D362" s="36"/>
     </row>
     <row r="363" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A363" s="50"/>
-      <c r="B363" s="49"/>
-      <c r="D363" s="50"/>
+      <c r="A363" s="36"/>
+      <c r="B363" s="35"/>
+      <c r="D363" s="36"/>
     </row>
     <row r="364" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A364" s="50"/>
-      <c r="B364" s="49"/>
-      <c r="D364" s="50"/>
+      <c r="A364" s="36"/>
+      <c r="B364" s="35"/>
+      <c r="D364" s="36"/>
     </row>
     <row r="365" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A365" s="50"/>
-      <c r="B365" s="49"/>
-      <c r="D365" s="50"/>
+      <c r="A365" s="36"/>
+      <c r="B365" s="35"/>
+      <c r="D365" s="36"/>
     </row>
     <row r="366" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A366" s="50"/>
-      <c r="B366" s="49"/>
-      <c r="D366" s="50"/>
+      <c r="A366" s="36"/>
+      <c r="B366" s="35"/>
+      <c r="D366" s="36"/>
     </row>
     <row r="367" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A367" s="50"/>
-      <c r="B367" s="49"/>
-      <c r="D367" s="50"/>
+      <c r="A367" s="36"/>
+      <c r="B367" s="35"/>
+      <c r="D367" s="36"/>
     </row>
     <row r="368" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A368" s="50"/>
-      <c r="B368" s="49"/>
-      <c r="D368" s="50"/>
+      <c r="A368" s="36"/>
+      <c r="B368" s="35"/>
+      <c r="D368" s="36"/>
     </row>
     <row r="369" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A369" s="50"/>
-      <c r="B369" s="49"/>
-      <c r="D369" s="50"/>
+      <c r="A369" s="36"/>
+      <c r="B369" s="35"/>
+      <c r="D369" s="36"/>
     </row>
     <row r="370" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A370" s="50"/>
-      <c r="B370" s="49"/>
-      <c r="D370" s="50"/>
+      <c r="A370" s="36"/>
+      <c r="B370" s="35"/>
+      <c r="D370" s="36"/>
     </row>
     <row r="371" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A371" s="50"/>
-      <c r="B371" s="49"/>
-      <c r="D371" s="50"/>
+      <c r="A371" s="36"/>
+      <c r="B371" s="35"/>
+      <c r="D371" s="36"/>
     </row>
     <row r="372" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A372" s="50"/>
-      <c r="B372" s="49"/>
-      <c r="D372" s="50"/>
+      <c r="A372" s="36"/>
+      <c r="B372" s="35"/>
+      <c r="D372" s="36"/>
     </row>
     <row r="373" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A373" s="50"/>
-      <c r="B373" s="49"/>
-      <c r="D373" s="50"/>
+      <c r="A373" s="36"/>
+      <c r="B373" s="35"/>
+      <c r="D373" s="36"/>
     </row>
     <row r="374" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A374" s="50"/>
-      <c r="B374" s="49"/>
-      <c r="D374" s="50"/>
+      <c r="A374" s="36"/>
+      <c r="B374" s="35"/>
+      <c r="D374" s="36"/>
     </row>
     <row r="375" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A375" s="50"/>
-      <c r="B375" s="49"/>
-      <c r="D375" s="50"/>
+      <c r="A375" s="36"/>
+      <c r="B375" s="35"/>
+      <c r="D375" s="36"/>
     </row>
     <row r="376" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A376" s="50"/>
-      <c r="B376" s="49"/>
-      <c r="D376" s="50"/>
+      <c r="A376" s="36"/>
+      <c r="B376" s="35"/>
+      <c r="D376" s="36"/>
     </row>
     <row r="377" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A377" s="50"/>
-      <c r="B377" s="49"/>
-      <c r="D377" s="50"/>
+      <c r="A377" s="36"/>
+      <c r="B377" s="35"/>
+      <c r="D377" s="36"/>
     </row>
     <row r="378" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A378" s="50"/>
-      <c r="B378" s="49"/>
-      <c r="D378" s="50"/>
+      <c r="A378" s="36"/>
+      <c r="B378" s="35"/>
+      <c r="D378" s="36"/>
     </row>
     <row r="379" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A379" s="50"/>
-      <c r="B379" s="49"/>
-      <c r="D379" s="50"/>
+      <c r="A379" s="36"/>
+      <c r="B379" s="35"/>
+      <c r="D379" s="36"/>
     </row>
     <row r="380" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A380" s="50"/>
-      <c r="B380" s="49"/>
-      <c r="D380" s="50"/>
+      <c r="A380" s="36"/>
+      <c r="B380" s="35"/>
+      <c r="D380" s="36"/>
     </row>
     <row r="381" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A381" s="50"/>
-      <c r="B381" s="49"/>
-      <c r="D381" s="50"/>
+      <c r="A381" s="36"/>
+      <c r="B381" s="35"/>
+      <c r="D381" s="36"/>
     </row>
     <row r="382" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A382" s="50"/>
-      <c r="B382" s="49"/>
-      <c r="D382" s="50"/>
+      <c r="A382" s="36"/>
+      <c r="B382" s="35"/>
+      <c r="D382" s="36"/>
     </row>
     <row r="383" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A383" s="50"/>
-      <c r="B383" s="49"/>
-      <c r="D383" s="50"/>
+      <c r="A383" s="36"/>
+      <c r="B383" s="35"/>
+      <c r="D383" s="36"/>
     </row>
     <row r="384" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A384" s="50"/>
-      <c r="B384" s="49"/>
-      <c r="D384" s="50"/>
+      <c r="A384" s="36"/>
+      <c r="B384" s="35"/>
+      <c r="D384" s="36"/>
     </row>
     <row r="385" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A385" s="50"/>
-      <c r="B385" s="49"/>
-      <c r="D385" s="50"/>
+      <c r="A385" s="36"/>
+      <c r="B385" s="35"/>
+      <c r="D385" s="36"/>
     </row>
     <row r="386" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A386" s="50"/>
-      <c r="B386" s="49"/>
-      <c r="D386" s="50"/>
+      <c r="A386" s="36"/>
+      <c r="B386" s="35"/>
+      <c r="D386" s="36"/>
     </row>
     <row r="387" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A387" s="50"/>
-      <c r="B387" s="49"/>
-      <c r="D387" s="50"/>
+      <c r="A387" s="36"/>
+      <c r="B387" s="35"/>
+      <c r="D387" s="36"/>
     </row>
     <row r="388" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A388" s="50"/>
-      <c r="B388" s="49"/>
-      <c r="D388" s="50"/>
+      <c r="A388" s="36"/>
+      <c r="B388" s="35"/>
+      <c r="D388" s="36"/>
     </row>
     <row r="389" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A389" s="50"/>
-      <c r="B389" s="49"/>
-      <c r="D389" s="50"/>
+      <c r="A389" s="36"/>
+      <c r="B389" s="35"/>
+      <c r="D389" s="36"/>
     </row>
     <row r="390" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A390" s="50"/>
-      <c r="B390" s="49"/>
-      <c r="D390" s="50"/>
+      <c r="A390" s="36"/>
+      <c r="B390" s="35"/>
+      <c r="D390" s="36"/>
     </row>
     <row r="391" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A391" s="50"/>
-      <c r="B391" s="49"/>
-      <c r="D391" s="50"/>
+      <c r="A391" s="36"/>
+      <c r="B391" s="35"/>
+      <c r="D391" s="36"/>
     </row>
     <row r="392" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A392" s="50"/>
-      <c r="B392" s="49"/>
-      <c r="D392" s="50"/>
+      <c r="A392" s="36"/>
+      <c r="B392" s="35"/>
+      <c r="D392" s="36"/>
     </row>
     <row r="393" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A393" s="50"/>
-      <c r="B393" s="49"/>
-      <c r="D393" s="50"/>
+      <c r="A393" s="36"/>
+      <c r="B393" s="35"/>
+      <c r="D393" s="36"/>
     </row>
     <row r="394" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A394" s="50"/>
-      <c r="B394" s="49"/>
-      <c r="D394" s="50"/>
+      <c r="A394" s="36"/>
+      <c r="B394" s="35"/>
+      <c r="D394" s="36"/>
     </row>
     <row r="395" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A395" s="50"/>
-      <c r="B395" s="49"/>
-      <c r="D395" s="50"/>
+      <c r="A395" s="36"/>
+      <c r="B395" s="35"/>
+      <c r="D395" s="36"/>
     </row>
     <row r="396" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A396" s="50"/>
-      <c r="B396" s="49"/>
-      <c r="D396" s="50"/>
+      <c r="A396" s="36"/>
+      <c r="B396" s="35"/>
+      <c r="D396" s="36"/>
     </row>
     <row r="397" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A397" s="50"/>
-      <c r="B397" s="49"/>
-      <c r="D397" s="50"/>
+      <c r="A397" s="36"/>
+      <c r="B397" s="35"/>
+      <c r="D397" s="36"/>
     </row>
     <row r="398" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A398" s="50"/>
-      <c r="B398" s="49"/>
-      <c r="D398" s="50"/>
+      <c r="A398" s="36"/>
+      <c r="B398" s="35"/>
+      <c r="D398" s="36"/>
     </row>
     <row r="399" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A399" s="50"/>
-      <c r="B399" s="49"/>
-      <c r="D399" s="50"/>
+      <c r="A399" s="36"/>
+      <c r="B399" s="35"/>
+      <c r="D399" s="36"/>
     </row>
     <row r="400" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A400" s="50"/>
-      <c r="B400" s="49"/>
-      <c r="D400" s="50"/>
+      <c r="A400" s="36"/>
+      <c r="B400" s="35"/>
+      <c r="D400" s="36"/>
     </row>
     <row r="401" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A401" s="50"/>
-      <c r="B401" s="49"/>
-      <c r="D401" s="50"/>
+      <c r="A401" s="36"/>
+      <c r="B401" s="35"/>
+      <c r="D401" s="36"/>
     </row>
     <row r="402" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A402" s="50"/>
-      <c r="B402" s="49"/>
-      <c r="D402" s="50"/>
+      <c r="A402" s="36"/>
+      <c r="B402" s="35"/>
+      <c r="D402" s="36"/>
     </row>
     <row r="403" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A403" s="50"/>
-      <c r="B403" s="49"/>
-      <c r="D403" s="50"/>
+      <c r="A403" s="36"/>
+      <c r="B403" s="35"/>
+      <c r="D403" s="36"/>
     </row>
     <row r="404" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A404" s="50"/>
-      <c r="B404" s="49"/>
-      <c r="D404" s="50"/>
+      <c r="A404" s="36"/>
+      <c r="B404" s="35"/>
+      <c r="D404" s="36"/>
     </row>
     <row r="405" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A405" s="50"/>
-      <c r="B405" s="49"/>
-      <c r="D405" s="50"/>
+      <c r="A405" s="36"/>
+      <c r="B405" s="35"/>
+      <c r="D405" s="36"/>
     </row>
     <row r="406" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A406" s="50"/>
-      <c r="B406" s="49"/>
-      <c r="D406" s="50"/>
+      <c r="A406" s="36"/>
+      <c r="B406" s="35"/>
+      <c r="D406" s="36"/>
     </row>
     <row r="407" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A407" s="50"/>
-      <c r="B407" s="49"/>
-      <c r="D407" s="50"/>
+      <c r="A407" s="36"/>
+      <c r="B407" s="35"/>
+      <c r="D407" s="36"/>
     </row>
     <row r="408" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A408" s="50"/>
-      <c r="B408" s="49"/>
-      <c r="D408" s="50"/>
+      <c r="A408" s="36"/>
+      <c r="B408" s="35"/>
+      <c r="D408" s="36"/>
     </row>
     <row r="409" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A409" s="50"/>
-      <c r="B409" s="49"/>
-      <c r="D409" s="50"/>
+      <c r="A409" s="36"/>
+      <c r="B409" s="35"/>
+      <c r="D409" s="36"/>
     </row>
     <row r="410" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A410" s="50"/>
-      <c r="B410" s="49"/>
-      <c r="D410" s="50"/>
+      <c r="A410" s="36"/>
+      <c r="B410" s="35"/>
+      <c r="D410" s="36"/>
     </row>
     <row r="411" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A411" s="50"/>
-      <c r="B411" s="49"/>
-      <c r="D411" s="50"/>
+      <c r="A411" s="36"/>
+      <c r="B411" s="35"/>
+      <c r="D411" s="36"/>
     </row>
     <row r="412" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A412" s="50"/>
-      <c r="B412" s="49"/>
-      <c r="D412" s="50"/>
+      <c r="A412" s="36"/>
+      <c r="B412" s="35"/>
+      <c r="D412" s="36"/>
     </row>
     <row r="413" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A413" s="50"/>
-      <c r="B413" s="49"/>
-      <c r="D413" s="50"/>
+      <c r="A413" s="36"/>
+      <c r="B413" s="35"/>
+      <c r="D413" s="36"/>
     </row>
     <row r="414" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A414" s="50"/>
-      <c r="B414" s="49"/>
-      <c r="D414" s="50"/>
+      <c r="A414" s="36"/>
+      <c r="B414" s="35"/>
+      <c r="D414" s="36"/>
     </row>
     <row r="415" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A415" s="50"/>
-      <c r="B415" s="49"/>
-      <c r="D415" s="50"/>
+      <c r="A415" s="36"/>
+      <c r="B415" s="35"/>
+      <c r="D415" s="36"/>
     </row>
     <row r="416" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A416" s="50"/>
-      <c r="B416" s="49"/>
-      <c r="D416" s="50"/>
+      <c r="A416" s="36"/>
+      <c r="B416" s="35"/>
+      <c r="D416" s="36"/>
     </row>
     <row r="417" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A417" s="50"/>
-      <c r="B417" s="49"/>
-      <c r="D417" s="50"/>
+      <c r="A417" s="36"/>
+      <c r="B417" s="35"/>
+      <c r="D417" s="36"/>
     </row>
     <row r="418" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A418" s="50"/>
-      <c r="B418" s="49"/>
-      <c r="D418" s="50"/>
+      <c r="A418" s="36"/>
+      <c r="B418" s="35"/>
+      <c r="D418" s="36"/>
     </row>
     <row r="419" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A419" s="50"/>
-      <c r="B419" s="49"/>
-      <c r="D419" s="50"/>
+      <c r="A419" s="36"/>
+      <c r="B419" s="35"/>
+      <c r="D419" s="36"/>
     </row>
     <row r="420" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A420" s="50"/>
-      <c r="B420" s="49"/>
-      <c r="D420" s="50"/>
+      <c r="A420" s="36"/>
+      <c r="B420" s="35"/>
+      <c r="D420" s="36"/>
     </row>
     <row r="421" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A421" s="50"/>
-      <c r="B421" s="49"/>
-      <c r="D421" s="50"/>
+      <c r="A421" s="36"/>
+      <c r="B421" s="35"/>
+      <c r="D421" s="36"/>
     </row>
     <row r="422" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A422" s="50"/>
-      <c r="B422" s="49"/>
-      <c r="D422" s="50"/>
+      <c r="A422" s="36"/>
+      <c r="B422" s="35"/>
+      <c r="D422" s="36"/>
     </row>
     <row r="423" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A423" s="50"/>
-      <c r="B423" s="49"/>
-      <c r="D423" s="50"/>
+      <c r="A423" s="36"/>
+      <c r="B423" s="35"/>
+      <c r="D423" s="36"/>
     </row>
     <row r="424" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A424" s="50"/>
-      <c r="B424" s="49"/>
-      <c r="D424" s="50"/>
+      <c r="A424" s="36"/>
+      <c r="B424" s="35"/>
+      <c r="D424" s="36"/>
     </row>
     <row r="425" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A425" s="50"/>
-      <c r="B425" s="49"/>
-      <c r="D425" s="50"/>
+      <c r="A425" s="36"/>
+      <c r="B425" s="35"/>
+      <c r="D425" s="36"/>
     </row>
     <row r="426" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A426" s="50"/>
-      <c r="B426" s="49"/>
-      <c r="D426" s="50"/>
+      <c r="A426" s="36"/>
+      <c r="B426" s="35"/>
+      <c r="D426" s="36"/>
     </row>
     <row r="427" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A427" s="50"/>
-      <c r="B427" s="49"/>
-      <c r="D427" s="50"/>
+      <c r="A427" s="36"/>
+      <c r="B427" s="35"/>
+      <c r="D427" s="36"/>
     </row>
     <row r="428" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A428" s="50"/>
-      <c r="B428" s="49"/>
-      <c r="D428" s="50"/>
+      <c r="A428" s="36"/>
+      <c r="B428" s="35"/>
+      <c r="D428" s="36"/>
     </row>
     <row r="429" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A429" s="50"/>
-      <c r="B429" s="49"/>
-      <c r="D429" s="50"/>
+      <c r="A429" s="36"/>
+      <c r="B429" s="35"/>
+      <c r="D429" s="36"/>
     </row>
     <row r="430" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A430" s="50"/>
-      <c r="B430" s="49"/>
-      <c r="D430" s="50"/>
+      <c r="A430" s="36"/>
+      <c r="B430" s="35"/>
+      <c r="D430" s="36"/>
     </row>
     <row r="431" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A431" s="50"/>
-      <c r="B431" s="49"/>
-      <c r="D431" s="50"/>
+      <c r="A431" s="36"/>
+      <c r="B431" s="35"/>
+      <c r="D431" s="36"/>
     </row>
     <row r="432" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A432" s="50"/>
-      <c r="B432" s="49"/>
-      <c r="D432" s="50"/>
+      <c r="A432" s="36"/>
+      <c r="B432" s="35"/>
+      <c r="D432" s="36"/>
     </row>
     <row r="433" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A433" s="50"/>
-      <c r="B433" s="49"/>
-      <c r="D433" s="50"/>
+      <c r="A433" s="36"/>
+      <c r="B433" s="35"/>
+      <c r="D433" s="36"/>
     </row>
     <row r="434" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A434" s="50"/>
-      <c r="B434" s="49"/>
-      <c r="D434" s="50"/>
+      <c r="A434" s="36"/>
+      <c r="B434" s="35"/>
+      <c r="D434" s="36"/>
     </row>
     <row r="435" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A435" s="50"/>
-      <c r="B435" s="49"/>
-      <c r="D435" s="50"/>
+      <c r="A435" s="36"/>
+      <c r="B435" s="35"/>
+      <c r="D435" s="36"/>
     </row>
     <row r="436" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A436" s="50"/>
-      <c r="B436" s="49"/>
-      <c r="D436" s="50"/>
+      <c r="A436" s="36"/>
+      <c r="B436" s="35"/>
+      <c r="D436" s="36"/>
     </row>
     <row r="437" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A437" s="50"/>
-      <c r="B437" s="49"/>
-      <c r="D437" s="50"/>
+      <c r="A437" s="36"/>
+      <c r="B437" s="35"/>
+      <c r="D437" s="36"/>
     </row>
     <row r="438" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A438" s="50"/>
-      <c r="B438" s="49"/>
-      <c r="D438" s="50"/>
+      <c r="A438" s="36"/>
+      <c r="B438" s="35"/>
+      <c r="D438" s="36"/>
     </row>
     <row r="439" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A439" s="50"/>
-      <c r="B439" s="49"/>
-      <c r="D439" s="50"/>
+      <c r="A439" s="36"/>
+      <c r="B439" s="35"/>
+      <c r="D439" s="36"/>
     </row>
     <row r="440" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A440" s="50"/>
-      <c r="B440" s="49"/>
-      <c r="D440" s="50"/>
+      <c r="A440" s="36"/>
+      <c r="B440" s="35"/>
+      <c r="D440" s="36"/>
     </row>
     <row r="441" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A441" s="50"/>
-      <c r="B441" s="49"/>
-      <c r="D441" s="50"/>
+      <c r="A441" s="36"/>
+      <c r="B441" s="35"/>
+      <c r="D441" s="36"/>
     </row>
     <row r="442" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A442" s="50"/>
-      <c r="B442" s="49"/>
-      <c r="D442" s="50"/>
+      <c r="A442" s="36"/>
+      <c r="B442" s="35"/>
+      <c r="D442" s="36"/>
     </row>
     <row r="443" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A443" s="50"/>
-      <c r="B443" s="49"/>
-      <c r="D443" s="50"/>
+      <c r="A443" s="36"/>
+      <c r="B443" s="35"/>
+      <c r="D443" s="36"/>
     </row>
     <row r="444" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A444" s="50"/>
-      <c r="B444" s="49"/>
-      <c r="D444" s="50"/>
+      <c r="A444" s="36"/>
+      <c r="B444" s="35"/>
+      <c r="D444" s="36"/>
     </row>
     <row r="445" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A445" s="50"/>
-      <c r="B445" s="49"/>
-      <c r="D445" s="50"/>
+      <c r="A445" s="36"/>
+      <c r="B445" s="35"/>
+      <c r="D445" s="36"/>
     </row>
     <row r="446" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A446" s="50"/>
-      <c r="B446" s="49"/>
-      <c r="D446" s="50"/>
+      <c r="A446" s="36"/>
+      <c r="B446" s="35"/>
+      <c r="D446" s="36"/>
     </row>
     <row r="447" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A447" s="50"/>
-      <c r="B447" s="49"/>
-      <c r="D447" s="50"/>
+      <c r="A447" s="36"/>
+      <c r="B447" s="35"/>
+      <c r="D447" s="36"/>
     </row>
     <row r="448" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A448" s="50"/>
-      <c r="B448" s="49"/>
-      <c r="D448" s="50"/>
+      <c r="A448" s="36"/>
+      <c r="B448" s="35"/>
+      <c r="D448" s="36"/>
     </row>
     <row r="449" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A449" s="50"/>
-      <c r="B449" s="49"/>
-      <c r="D449" s="50"/>
+      <c r="A449" s="36"/>
+      <c r="B449" s="35"/>
+      <c r="D449" s="36"/>
     </row>
     <row r="450" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A450" s="50"/>
-      <c r="B450" s="49"/>
-      <c r="D450" s="50"/>
+      <c r="A450" s="36"/>
+      <c r="B450" s="35"/>
+      <c r="D450" s="36"/>
     </row>
     <row r="451" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A451" s="50"/>
-      <c r="B451" s="49"/>
-      <c r="D451" s="50"/>
+      <c r="A451" s="36"/>
+      <c r="B451" s="35"/>
+      <c r="D451" s="36"/>
     </row>
     <row r="452" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A452" s="50"/>
-      <c r="B452" s="49"/>
-      <c r="D452" s="50"/>
+      <c r="A452" s="36"/>
+      <c r="B452" s="35"/>
+      <c r="D452" s="36"/>
     </row>
     <row r="453" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A453" s="50"/>
-      <c r="B453" s="49"/>
-      <c r="D453" s="50"/>
+      <c r="A453" s="36"/>
+      <c r="B453" s="35"/>
+      <c r="D453" s="36"/>
     </row>
     <row r="454" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A454" s="50"/>
-      <c r="B454" s="49"/>
-      <c r="D454" s="50"/>
+      <c r="A454" s="36"/>
+      <c r="B454" s="35"/>
+      <c r="D454" s="36"/>
     </row>
     <row r="455" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A455" s="50"/>
-      <c r="B455" s="49"/>
-      <c r="D455" s="50"/>
+      <c r="A455" s="36"/>
+      <c r="B455" s="35"/>
+      <c r="D455" s="36"/>
     </row>
     <row r="456" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A456" s="50"/>
-      <c r="B456" s="49"/>
-      <c r="D456" s="50"/>
+      <c r="A456" s="36"/>
+      <c r="B456" s="35"/>
+      <c r="D456" s="36"/>
     </row>
     <row r="457" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A457" s="50"/>
-      <c r="B457" s="49"/>
-      <c r="D457" s="50"/>
+      <c r="A457" s="36"/>
+      <c r="B457" s="35"/>
+      <c r="D457" s="36"/>
     </row>
     <row r="458" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A458" s="50"/>
-      <c r="B458" s="49"/>
-      <c r="D458" s="50"/>
+      <c r="A458" s="36"/>
+      <c r="B458" s="35"/>
+      <c r="D458" s="36"/>
     </row>
     <row r="459" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A459" s="50"/>
-      <c r="B459" s="49"/>
-      <c r="D459" s="50"/>
+      <c r="A459" s="36"/>
+      <c r="B459" s="35"/>
+      <c r="D459" s="36"/>
     </row>
     <row r="460" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A460" s="50"/>
-      <c r="B460" s="49"/>
-      <c r="D460" s="50"/>
+      <c r="A460" s="36"/>
+      <c r="B460" s="35"/>
+      <c r="D460" s="36"/>
     </row>
     <row r="461" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A461" s="50"/>
-      <c r="B461" s="49"/>
-      <c r="D461" s="50"/>
+      <c r="A461" s="36"/>
+      <c r="B461" s="35"/>
+      <c r="D461" s="36"/>
     </row>
     <row r="462" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A462" s="50"/>
-      <c r="B462" s="49"/>
-      <c r="D462" s="50"/>
+      <c r="A462" s="36"/>
+      <c r="B462" s="35"/>
+      <c r="D462" s="36"/>
     </row>
     <row r="463" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A463" s="50"/>
-      <c r="B463" s="49"/>
-      <c r="D463" s="50"/>
+      <c r="A463" s="36"/>
+      <c r="B463" s="35"/>
+      <c r="D463" s="36"/>
     </row>
     <row r="464" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A464" s="50"/>
-      <c r="B464" s="49"/>
-      <c r="D464" s="50"/>
+      <c r="A464" s="36"/>
+      <c r="B464" s="35"/>
+      <c r="D464" s="36"/>
     </row>
     <row r="465" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A465" s="50"/>
-      <c r="B465" s="49"/>
-      <c r="D465" s="50"/>
+      <c r="A465" s="36"/>
+      <c r="B465" s="35"/>
+      <c r="D465" s="36"/>
     </row>
     <row r="466" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A466" s="50"/>
-      <c r="B466" s="49"/>
-      <c r="D466" s="50"/>
+      <c r="A466" s="36"/>
+      <c r="B466" s="35"/>
+      <c r="D466" s="36"/>
     </row>
     <row r="467" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A467" s="50"/>
-      <c r="B467" s="49"/>
-      <c r="D467" s="50"/>
+      <c r="A467" s="36"/>
+      <c r="B467" s="35"/>
+      <c r="D467" s="36"/>
     </row>
     <row r="468" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A468" s="50"/>
-      <c r="B468" s="49"/>
-      <c r="D468" s="50"/>
+      <c r="A468" s="36"/>
+      <c r="B468" s="35"/>
+      <c r="D468" s="36"/>
     </row>
     <row r="469" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A469" s="50"/>
-      <c r="B469" s="49"/>
-      <c r="D469" s="50"/>
+      <c r="A469" s="36"/>
+      <c r="B469" s="35"/>
+      <c r="D469" s="36"/>
     </row>
     <row r="470" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A470" s="50"/>
-      <c r="B470" s="49"/>
-      <c r="D470" s="50"/>
+      <c r="A470" s="36"/>
+      <c r="B470" s="35"/>
+      <c r="D470" s="36"/>
     </row>
     <row r="471" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A471" s="50"/>
-      <c r="B471" s="49"/>
-      <c r="D471" s="50"/>
+      <c r="A471" s="36"/>
+      <c r="B471" s="35"/>
+      <c r="D471" s="36"/>
     </row>
     <row r="472" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A472" s="50"/>
-      <c r="B472" s="49"/>
-      <c r="D472" s="50"/>
+      <c r="A472" s="36"/>
+      <c r="B472" s="35"/>
+      <c r="D472" s="36"/>
     </row>
     <row r="473" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A473" s="50"/>
-      <c r="B473" s="49"/>
-      <c r="D473" s="50"/>
+      <c r="A473" s="36"/>
+      <c r="B473" s="35"/>
+      <c r="D473" s="36"/>
     </row>
     <row r="474" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A474" s="50"/>
-      <c r="B474" s="49"/>
-      <c r="D474" s="50"/>
+      <c r="A474" s="36"/>
+      <c r="B474" s="35"/>
+      <c r="D474" s="36"/>
     </row>
     <row r="475" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A475" s="50"/>
-      <c r="B475" s="49"/>
-      <c r="D475" s="50"/>
+      <c r="A475" s="36"/>
+      <c r="B475" s="35"/>
+      <c r="D475" s="36"/>
     </row>
     <row r="476" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A476" s="50"/>
-      <c r="B476" s="49"/>
-      <c r="D476" s="50"/>
+      <c r="A476" s="36"/>
+      <c r="B476" s="35"/>
+      <c r="D476" s="36"/>
     </row>
     <row r="477" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A477" s="50"/>
-      <c r="B477" s="49"/>
-      <c r="D477" s="50"/>
+      <c r="A477" s="36"/>
+      <c r="B477" s="35"/>
+      <c r="D477" s="36"/>
     </row>
     <row r="478" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A478" s="50"/>
-      <c r="B478" s="49"/>
-      <c r="D478" s="50"/>
+      <c r="A478" s="36"/>
+      <c r="B478" s="35"/>
+      <c r="D478" s="36"/>
     </row>
     <row r="479" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A479" s="50"/>
-      <c r="B479" s="49"/>
-      <c r="D479" s="50"/>
+      <c r="A479" s="36"/>
+      <c r="B479" s="35"/>
+      <c r="D479" s="36"/>
     </row>
     <row r="480" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A480" s="50"/>
-      <c r="B480" s="49"/>
-      <c r="D480" s="50"/>
+      <c r="A480" s="36"/>
+      <c r="B480" s="35"/>
+      <c r="D480" s="36"/>
     </row>
     <row r="481" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A481" s="50"/>
-      <c r="B481" s="49"/>
-      <c r="D481" s="50"/>
+      <c r="A481" s="36"/>
+      <c r="B481" s="35"/>
+      <c r="D481" s="36"/>
     </row>
     <row r="482" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A482" s="50"/>
-      <c r="B482" s="49"/>
-      <c r="D482" s="50"/>
+      <c r="A482" s="36"/>
+      <c r="B482" s="35"/>
+      <c r="D482" s="36"/>
     </row>
     <row r="483" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A483" s="50"/>
-      <c r="B483" s="49"/>
-      <c r="D483" s="50"/>
+      <c r="A483" s="36"/>
+      <c r="B483" s="35"/>
+      <c r="D483" s="36"/>
     </row>
     <row r="484" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A484" s="50"/>
-      <c r="B484" s="49"/>
-      <c r="D484" s="50"/>
+      <c r="A484" s="36"/>
+      <c r="B484" s="35"/>
+      <c r="D484" s="36"/>
     </row>
     <row r="485" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A485" s="50"/>
-      <c r="B485" s="49"/>
-      <c r="D485" s="50"/>
+      <c r="A485" s="36"/>
+      <c r="B485" s="35"/>
+      <c r="D485" s="36"/>
     </row>
     <row r="486" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A486" s="50"/>
-      <c r="B486" s="49"/>
-      <c r="D486" s="50"/>
+      <c r="A486" s="36"/>
+      <c r="B486" s="35"/>
+      <c r="D486" s="36"/>
     </row>
     <row r="487" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A487" s="50"/>
-      <c r="B487" s="49"/>
-      <c r="D487" s="50"/>
+      <c r="A487" s="36"/>
+      <c r="B487" s="35"/>
+      <c r="D487" s="36"/>
     </row>
     <row r="488" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A488" s="50"/>
-      <c r="B488" s="49"/>
-      <c r="D488" s="50"/>
+      <c r="A488" s="36"/>
+      <c r="B488" s="35"/>
+      <c r="D488" s="36"/>
     </row>
     <row r="489" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A489" s="50"/>
-      <c r="B489" s="49"/>
-      <c r="D489" s="50"/>
+      <c r="A489" s="36"/>
+      <c r="B489" s="35"/>
+      <c r="D489" s="36"/>
     </row>
     <row r="490" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A490" s="50"/>
-      <c r="B490" s="49"/>
-      <c r="D490" s="50"/>
+      <c r="A490" s="36"/>
+      <c r="B490" s="35"/>
+      <c r="D490" s="36"/>
     </row>
     <row r="491" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A491" s="50"/>
-      <c r="B491" s="49"/>
-      <c r="D491" s="50"/>
+      <c r="A491" s="36"/>
+      <c r="B491" s="35"/>
+      <c r="D491" s="36"/>
     </row>
     <row r="492" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A492" s="50"/>
-      <c r="B492" s="49"/>
-      <c r="D492" s="50"/>
+      <c r="A492" s="36"/>
+      <c r="B492" s="35"/>
+      <c r="D492" s="36"/>
     </row>
     <row r="493" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A493" s="50"/>
-      <c r="B493" s="49"/>
-      <c r="D493" s="50"/>
+      <c r="A493" s="36"/>
+      <c r="B493" s="35"/>
+      <c r="D493" s="36"/>
     </row>
     <row r="494" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A494" s="50"/>
-      <c r="B494" s="49"/>
-      <c r="D494" s="50"/>
+      <c r="A494" s="36"/>
+      <c r="B494" s="35"/>
+      <c r="D494" s="36"/>
     </row>
     <row r="495" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A495" s="50"/>
-      <c r="B495" s="49"/>
-      <c r="D495" s="50"/>
+      <c r="A495" s="36"/>
+      <c r="B495" s="35"/>
+      <c r="D495" s="36"/>
     </row>
     <row r="496" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A496" s="50"/>
-      <c r="B496" s="49"/>
-      <c r="D496" s="50"/>
+      <c r="A496" s="36"/>
+      <c r="B496" s="35"/>
+      <c r="D496" s="36"/>
     </row>
     <row r="497" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A497" s="50"/>
-      <c r="B497" s="49"/>
-      <c r="D497" s="50"/>
+      <c r="A497" s="36"/>
+      <c r="B497" s="35"/>
+      <c r="D497" s="36"/>
     </row>
     <row r="498" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A498" s="50"/>
-      <c r="B498" s="49"/>
-      <c r="D498" s="50"/>
+      <c r="A498" s="36"/>
+      <c r="B498" s="35"/>
+      <c r="D498" s="36"/>
     </row>
     <row r="499" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A499" s="50"/>
-      <c r="B499" s="49"/>
-      <c r="D499" s="50"/>
+      <c r="A499" s="36"/>
+      <c r="B499" s="35"/>
+      <c r="D499" s="36"/>
     </row>
     <row r="500" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A500" s="50"/>
-      <c r="B500" s="49"/>
-      <c r="D500" s="50"/>
+      <c r="A500" s="36"/>
+      <c r="B500" s="35"/>
+      <c r="D500" s="36"/>
     </row>
     <row r="501" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A501" s="50"/>
-      <c r="B501" s="49"/>
-      <c r="D501" s="50"/>
+      <c r="A501" s="36"/>
+      <c r="B501" s="35"/>
+      <c r="D501" s="36"/>
     </row>
     <row r="502" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A502" s="50"/>
-      <c r="B502" s="49"/>
-      <c r="D502" s="50"/>
+      <c r="A502" s="36"/>
+      <c r="B502" s="35"/>
+      <c r="D502" s="36"/>
     </row>
     <row r="503" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A503" s="50"/>
-      <c r="B503" s="49"/>
-      <c r="D503" s="50"/>
+      <c r="A503" s="36"/>
+      <c r="B503" s="35"/>
+      <c r="D503" s="36"/>
     </row>
     <row r="504" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A504" s="50"/>
-      <c r="B504" s="49"/>
-      <c r="D504" s="50"/>
+      <c r="A504" s="36"/>
+      <c r="B504" s="35"/>
+      <c r="D504" s="36"/>
     </row>
     <row r="505" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A505" s="50"/>
-      <c r="B505" s="49"/>
-      <c r="D505" s="50"/>
+      <c r="A505" s="36"/>
+      <c r="B505" s="35"/>
+      <c r="D505" s="36"/>
     </row>
     <row r="506" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A506" s="50"/>
-      <c r="B506" s="49"/>
-      <c r="D506" s="50"/>
+      <c r="A506" s="36"/>
+      <c r="B506" s="35"/>
+      <c r="D506" s="36"/>
     </row>
     <row r="507" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A507" s="50"/>
-      <c r="B507" s="49"/>
-      <c r="D507" s="50"/>
+      <c r="A507" s="36"/>
+      <c r="B507" s="35"/>
+      <c r="D507" s="36"/>
     </row>
     <row r="508" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A508" s="50"/>
-      <c r="B508" s="49"/>
-      <c r="D508" s="50"/>
+      <c r="A508" s="36"/>
+      <c r="B508" s="35"/>
+      <c r="D508" s="36"/>
     </row>
     <row r="509" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A509" s="50"/>
-      <c r="B509" s="49"/>
-      <c r="D509" s="50"/>
+      <c r="A509" s="36"/>
+      <c r="B509" s="35"/>
+      <c r="D509" s="36"/>
     </row>
     <row r="510" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A510" s="50"/>
-      <c r="B510" s="49"/>
-      <c r="D510" s="50"/>
+      <c r="A510" s="36"/>
+      <c r="B510" s="35"/>
+      <c r="D510" s="36"/>
     </row>
     <row r="511" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A511" s="50"/>
-      <c r="B511" s="49"/>
-      <c r="D511" s="50"/>
+      <c r="A511" s="36"/>
+      <c r="B511" s="35"/>
+      <c r="D511" s="36"/>
     </row>
     <row r="512" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A512" s="50"/>
-      <c r="B512" s="49"/>
-      <c r="D512" s="50"/>
+      <c r="A512" s="36"/>
+      <c r="B512" s="35"/>
+      <c r="D512" s="36"/>
     </row>
     <row r="513" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A513" s="50"/>
-      <c r="B513" s="49"/>
-      <c r="D513" s="50"/>
+      <c r="A513" s="36"/>
+      <c r="B513" s="35"/>
+      <c r="D513" s="36"/>
     </row>
     <row r="514" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A514" s="50"/>
-      <c r="B514" s="49"/>
-      <c r="D514" s="50"/>
+      <c r="A514" s="36"/>
+      <c r="B514" s="35"/>
+      <c r="D514" s="36"/>
     </row>
     <row r="515" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A515" s="50"/>
-      <c r="B515" s="49"/>
-      <c r="D515" s="50"/>
+      <c r="A515" s="36"/>
+      <c r="B515" s="35"/>
+      <c r="D515" s="36"/>
     </row>
     <row r="516" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A516" s="50"/>
-      <c r="B516" s="49"/>
-      <c r="D516" s="50"/>
+      <c r="A516" s="36"/>
+      <c r="B516" s="35"/>
+      <c r="D516" s="36"/>
     </row>
     <row r="517" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A517" s="50"/>
-      <c r="B517" s="49"/>
-      <c r="D517" s="50"/>
+      <c r="A517" s="36"/>
+      <c r="B517" s="35"/>
+      <c r="D517" s="36"/>
     </row>
     <row r="518" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A518" s="50"/>
-      <c r="B518" s="49"/>
-      <c r="D518" s="50"/>
+      <c r="A518" s="36"/>
+      <c r="B518" s="35"/>
+      <c r="D518" s="36"/>
     </row>
     <row r="519" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A519" s="50"/>
-      <c r="B519" s="49"/>
-      <c r="D519" s="50"/>
+      <c r="A519" s="36"/>
+      <c r="B519" s="35"/>
+      <c r="D519" s="36"/>
     </row>
     <row r="520" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A520" s="50"/>
-      <c r="B520" s="49"/>
-      <c r="D520" s="50"/>
+      <c r="A520" s="36"/>
+      <c r="B520" s="35"/>
+      <c r="D520" s="36"/>
     </row>
     <row r="521" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A521" s="50"/>
-      <c r="B521" s="49"/>
-      <c r="D521" s="50"/>
+      <c r="A521" s="36"/>
+      <c r="B521" s="35"/>
+      <c r="D521" s="36"/>
     </row>
     <row r="522" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A522" s="50"/>
-      <c r="B522" s="49"/>
-      <c r="D522" s="50"/>
+      <c r="A522" s="36"/>
+      <c r="B522" s="35"/>
+      <c r="D522" s="36"/>
     </row>
     <row r="523" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A523" s="50"/>
-      <c r="B523" s="49"/>
-      <c r="D523" s="50"/>
+      <c r="A523" s="36"/>
+      <c r="B523" s="35"/>
+      <c r="D523" s="36"/>
     </row>
     <row r="524" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A524" s="50"/>
-      <c r="B524" s="49"/>
-      <c r="D524" s="50"/>
+      <c r="A524" s="36"/>
+      <c r="B524" s="35"/>
+      <c r="D524" s="36"/>
     </row>
     <row r="525" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A525" s="50"/>
-      <c r="B525" s="49"/>
-      <c r="D525" s="50"/>
+      <c r="A525" s="36"/>
+      <c r="B525" s="35"/>
+      <c r="D525" s="36"/>
     </row>
     <row r="526" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A526" s="50"/>
-      <c r="B526" s="49"/>
-      <c r="D526" s="50"/>
+      <c r="A526" s="36"/>
+      <c r="B526" s="35"/>
+      <c r="D526" s="36"/>
     </row>
     <row r="527" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A527" s="50"/>
-      <c r="B527" s="49"/>
-      <c r="D527" s="50"/>
+      <c r="A527" s="36"/>
+      <c r="B527" s="35"/>
+      <c r="D527" s="36"/>
     </row>
     <row r="528" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A528" s="50"/>
-      <c r="B528" s="49"/>
-      <c r="D528" s="50"/>
+      <c r="A528" s="36"/>
+      <c r="B528" s="35"/>
+      <c r="D528" s="36"/>
     </row>
     <row r="529" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A529" s="50"/>
-      <c r="B529" s="49"/>
-      <c r="D529" s="50"/>
+      <c r="A529" s="36"/>
+      <c r="B529" s="35"/>
+      <c r="D529" s="36"/>
     </row>
     <row r="530" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A530" s="50"/>
-      <c r="B530" s="49"/>
-      <c r="D530" s="50"/>
+      <c r="A530" s="36"/>
+      <c r="B530" s="35"/>
+      <c r="D530" s="36"/>
     </row>
     <row r="531" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A531" s="50"/>
-      <c r="B531" s="49"/>
-      <c r="D531" s="50"/>
+      <c r="A531" s="36"/>
+      <c r="B531" s="35"/>
+      <c r="D531" s="36"/>
     </row>
     <row r="532" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A532" s="50"/>
-      <c r="B532" s="49"/>
-      <c r="D532" s="50"/>
+      <c r="A532" s="36"/>
+      <c r="B532" s="35"/>
+      <c r="D532" s="36"/>
     </row>
     <row r="533" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A533" s="50"/>
-      <c r="B533" s="49"/>
-      <c r="D533" s="50"/>
+      <c r="A533" s="36"/>
+      <c r="B533" s="35"/>
+      <c r="D533" s="36"/>
     </row>
     <row r="534" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A534" s="50"/>
-      <c r="B534" s="49"/>
-      <c r="D534" s="50"/>
+      <c r="A534" s="36"/>
+      <c r="B534" s="35"/>
+      <c r="D534" s="36"/>
     </row>
     <row r="535" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A535" s="50"/>
-      <c r="B535" s="49"/>
-      <c r="D535" s="50"/>
+      <c r="A535" s="36"/>
+      <c r="B535" s="35"/>
+      <c r="D535" s="36"/>
     </row>
     <row r="536" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A536" s="50"/>
-      <c r="B536" s="49"/>
-      <c r="D536" s="50"/>
+      <c r="A536" s="36"/>
+      <c r="B536" s="35"/>
+      <c r="D536" s="36"/>
     </row>
     <row r="537" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A537" s="50"/>
-      <c r="B537" s="49"/>
-      <c r="D537" s="50"/>
+      <c r="A537" s="36"/>
+      <c r="B537" s="35"/>
+      <c r="D537" s="36"/>
     </row>
     <row r="538" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A538" s="50"/>
-      <c r="B538" s="49"/>
-      <c r="D538" s="50"/>
+      <c r="A538" s="36"/>
+      <c r="B538" s="35"/>
+      <c r="D538" s="36"/>
     </row>
     <row r="539" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A539" s="50"/>
-      <c r="B539" s="49"/>
-      <c r="D539" s="50"/>
+      <c r="A539" s="36"/>
+      <c r="B539" s="35"/>
+      <c r="D539" s="36"/>
     </row>
     <row r="540" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A540" s="50"/>
-      <c r="B540" s="49"/>
-      <c r="D540" s="50"/>
+      <c r="A540" s="36"/>
+      <c r="B540" s="35"/>
+      <c r="D540" s="36"/>
     </row>
     <row r="541" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A541" s="50"/>
-      <c r="B541" s="49"/>
-      <c r="D541" s="50"/>
+      <c r="A541" s="36"/>
+      <c r="B541" s="35"/>
+      <c r="D541" s="36"/>
     </row>
     <row r="542" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A542" s="50"/>
-      <c r="B542" s="49"/>
-      <c r="D542" s="50"/>
+      <c r="A542" s="36"/>
+      <c r="B542" s="35"/>
+      <c r="D542" s="36"/>
     </row>
     <row r="543" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A543" s="50"/>
-      <c r="B543" s="49"/>
-      <c r="D543" s="50"/>
+      <c r="A543" s="36"/>
+      <c r="B543" s="35"/>
+      <c r="D543" s="36"/>
     </row>
     <row r="544" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A544" s="50"/>
-      <c r="B544" s="49"/>
-      <c r="D544" s="50"/>
+      <c r="A544" s="36"/>
+      <c r="B544" s="35"/>
+      <c r="D544" s="36"/>
     </row>
     <row r="545" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A545" s="50"/>
-      <c r="B545" s="49"/>
-      <c r="D545" s="50"/>
+      <c r="A545" s="36"/>
+      <c r="B545" s="35"/>
+      <c r="D545" s="36"/>
     </row>
     <row r="546" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A546" s="50"/>
-      <c r="B546" s="49"/>
-      <c r="D546" s="50"/>
+      <c r="A546" s="36"/>
+      <c r="B546" s="35"/>
+      <c r="D546" s="36"/>
     </row>
     <row r="547" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A547" s="50"/>
-      <c r="B547" s="49"/>
-      <c r="D547" s="50"/>
+      <c r="A547" s="36"/>
+      <c r="B547" s="35"/>
+      <c r="D547" s="36"/>
     </row>
     <row r="548" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A548" s="50"/>
-      <c r="B548" s="49"/>
-      <c r="D548" s="50"/>
+      <c r="A548" s="36"/>
+      <c r="B548" s="35"/>
+      <c r="D548" s="36"/>
     </row>
     <row r="549" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A549" s="50"/>
-      <c r="B549" s="49"/>
-      <c r="D549" s="50"/>
+      <c r="A549" s="36"/>
+      <c r="B549" s="35"/>
+      <c r="D549" s="36"/>
     </row>
     <row r="550" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A550" s="50"/>
-      <c r="B550" s="49"/>
-      <c r="D550" s="50"/>
+      <c r="A550" s="36"/>
+      <c r="B550" s="35"/>
+      <c r="D550" s="36"/>
     </row>
     <row r="551" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A551" s="50"/>
-      <c r="B551" s="49"/>
-      <c r="D551" s="50"/>
+      <c r="A551" s="36"/>
+      <c r="B551" s="35"/>
+      <c r="D551" s="36"/>
     </row>
     <row r="552" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A552" s="50"/>
-      <c r="B552" s="49"/>
-      <c r="D552" s="50"/>
+      <c r="A552" s="36"/>
+      <c r="B552" s="35"/>
+      <c r="D552" s="36"/>
     </row>
     <row r="553" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A553" s="50"/>
-      <c r="B553" s="49"/>
-      <c r="D553" s="50"/>
+      <c r="A553" s="36"/>
+      <c r="B553" s="35"/>
+      <c r="D553" s="36"/>
     </row>
     <row r="554" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A554" s="50"/>
-      <c r="B554" s="49"/>
-      <c r="D554" s="50"/>
+      <c r="A554" s="36"/>
+      <c r="B554" s="35"/>
+      <c r="D554" s="36"/>
     </row>
     <row r="555" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A555" s="50"/>
-      <c r="B555" s="49"/>
-      <c r="D555" s="50"/>
+      <c r="A555" s="36"/>
+      <c r="B555" s="35"/>
+      <c r="D555" s="36"/>
     </row>
     <row r="556" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A556" s="50"/>
-      <c r="B556" s="49"/>
-      <c r="D556" s="50"/>
+      <c r="A556" s="36"/>
+      <c r="B556" s="35"/>
+      <c r="D556" s="36"/>
     </row>
     <row r="557" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A557" s="50"/>
-      <c r="B557" s="49"/>
-      <c r="D557" s="50"/>
+      <c r="A557" s="36"/>
+      <c r="B557" s="35"/>
+      <c r="D557" s="36"/>
     </row>
     <row r="558" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A558" s="50"/>
-      <c r="B558" s="49"/>
-      <c r="D558" s="50"/>
+      <c r="A558" s="36"/>
+      <c r="B558" s="35"/>
+      <c r="D558" s="36"/>
     </row>
     <row r="559" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A559" s="50"/>
-      <c r="B559" s="49"/>
-      <c r="D559" s="50"/>
+      <c r="A559" s="36"/>
+      <c r="B559" s="35"/>
+      <c r="D559" s="36"/>
     </row>
     <row r="560" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A560" s="50"/>
-      <c r="B560" s="49"/>
-      <c r="D560" s="50"/>
+      <c r="A560" s="36"/>
+      <c r="B560" s="35"/>
+      <c r="D560" s="36"/>
     </row>
     <row r="561" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A561" s="50"/>
-      <c r="B561" s="49"/>
-      <c r="D561" s="50"/>
+      <c r="A561" s="36"/>
+      <c r="B561" s="35"/>
+      <c r="D561" s="36"/>
     </row>
     <row r="562" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A562" s="50"/>
-      <c r="B562" s="49"/>
-      <c r="D562" s="50"/>
+      <c r="A562" s="36"/>
+      <c r="B562" s="35"/>
+      <c r="D562" s="36"/>
     </row>
     <row r="563" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A563" s="50"/>
-      <c r="B563" s="49"/>
-      <c r="D563" s="50"/>
+      <c r="A563" s="36"/>
+      <c r="B563" s="35"/>
+      <c r="D563" s="36"/>
     </row>
     <row r="564" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A564" s="50"/>
-      <c r="B564" s="49"/>
-      <c r="D564" s="50"/>
+      <c r="A564" s="36"/>
+      <c r="B564" s="35"/>
+      <c r="D564" s="36"/>
     </row>
     <row r="565" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A565" s="50"/>
-      <c r="B565" s="49"/>
-      <c r="D565" s="50"/>
+      <c r="A565" s="36"/>
+      <c r="B565" s="35"/>
+      <c r="D565" s="36"/>
     </row>
     <row r="566" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A566" s="50"/>
-      <c r="B566" s="49"/>
-      <c r="D566" s="50"/>
+      <c r="A566" s="36"/>
+      <c r="B566" s="35"/>
+      <c r="D566" s="36"/>
     </row>
     <row r="567" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A567" s="50"/>
-      <c r="B567" s="49"/>
-      <c r="D567" s="50"/>
+      <c r="A567" s="36"/>
+      <c r="B567" s="35"/>
+      <c r="D567" s="36"/>
     </row>
     <row r="568" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A568" s="50"/>
-      <c r="B568" s="49"/>
-      <c r="D568" s="50"/>
+      <c r="A568" s="36"/>
+      <c r="B568" s="35"/>
+      <c r="D568" s="36"/>
     </row>
     <row r="569" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A569" s="50"/>
-      <c r="B569" s="49"/>
-      <c r="D569" s="50"/>
+      <c r="A569" s="36"/>
+      <c r="B569" s="35"/>
+      <c r="D569" s="36"/>
     </row>
     <row r="570" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A570" s="50"/>
-      <c r="B570" s="49"/>
-      <c r="D570" s="50"/>
+      <c r="A570" s="36"/>
+      <c r="B570" s="35"/>
+      <c r="D570" s="36"/>
     </row>
     <row r="571" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A571" s="50"/>
-      <c r="B571" s="49"/>
-      <c r="D571" s="50"/>
+      <c r="A571" s="36"/>
+      <c r="B571" s="35"/>
+      <c r="D571" s="36"/>
     </row>
     <row r="572" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A572" s="50"/>
-      <c r="B572" s="49"/>
-      <c r="D572" s="50"/>
+      <c r="A572" s="36"/>
+      <c r="B572" s="35"/>
+      <c r="D572" s="36"/>
     </row>
     <row r="573" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A573" s="50"/>
-      <c r="B573" s="49"/>
-      <c r="D573" s="50"/>
+      <c r="A573" s="36"/>
+      <c r="B573" s="35"/>
+      <c r="D573" s="36"/>
     </row>
     <row r="574" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A574" s="50"/>
-      <c r="B574" s="49"/>
-      <c r="D574" s="50"/>
+      <c r="A574" s="36"/>
+      <c r="B574" s="35"/>
+      <c r="D574" s="36"/>
     </row>
     <row r="575" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A575" s="50"/>
-      <c r="B575" s="49"/>
-      <c r="D575" s="50"/>
+      <c r="A575" s="36"/>
+      <c r="B575" s="35"/>
+      <c r="D575" s="36"/>
     </row>
     <row r="576" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A576" s="50"/>
-      <c r="B576" s="49"/>
-      <c r="D576" s="50"/>
+      <c r="A576" s="36"/>
+      <c r="B576" s="35"/>
+      <c r="D576" s="36"/>
     </row>
     <row r="577" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A577" s="50"/>
-      <c r="B577" s="49"/>
-      <c r="D577" s="50"/>
+      <c r="A577" s="36"/>
+      <c r="B577" s="35"/>
+      <c r="D577" s="36"/>
     </row>
     <row r="578" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A578" s="50"/>
-      <c r="B578" s="49"/>
-      <c r="D578" s="50"/>
+      <c r="A578" s="36"/>
+      <c r="B578" s="35"/>
+      <c r="D578" s="36"/>
     </row>
     <row r="579" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A579" s="50"/>
-      <c r="B579" s="49"/>
-      <c r="D579" s="50"/>
+      <c r="A579" s="36"/>
+      <c r="B579" s="35"/>
+      <c r="D579" s="36"/>
     </row>
     <row r="580" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A580" s="50"/>
-      <c r="B580" s="49"/>
-      <c r="D580" s="50"/>
+      <c r="A580" s="36"/>
+      <c r="B580" s="35"/>
+      <c r="D580" s="36"/>
     </row>
     <row r="581" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A581" s="50"/>
-      <c r="B581" s="49"/>
-      <c r="D581" s="50"/>
+      <c r="A581" s="36"/>
+      <c r="B581" s="35"/>
+      <c r="D581" s="36"/>
     </row>
     <row r="582" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A582" s="50"/>
-      <c r="B582" s="49"/>
-      <c r="D582" s="50"/>
+      <c r="A582" s="36"/>
+      <c r="B582" s="35"/>
+      <c r="D582" s="36"/>
     </row>
     <row r="583" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A583" s="50"/>
-      <c r="B583" s="49"/>
-      <c r="D583" s="50"/>
+      <c r="A583" s="36"/>
+      <c r="B583" s="35"/>
+      <c r="D583" s="36"/>
     </row>
     <row r="584" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A584" s="50"/>
-      <c r="B584" s="49"/>
-      <c r="D584" s="50"/>
+      <c r="A584" s="36"/>
+      <c r="B584" s="35"/>
+      <c r="D584" s="36"/>
     </row>
     <row r="585" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A585" s="50"/>
-      <c r="B585" s="49"/>
-      <c r="D585" s="50"/>
+      <c r="A585" s="36"/>
+      <c r="B585" s="35"/>
+      <c r="D585" s="36"/>
     </row>
     <row r="586" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A586" s="50"/>
-      <c r="B586" s="49"/>
-      <c r="D586" s="50"/>
+      <c r="A586" s="36"/>
+      <c r="B586" s="35"/>
+      <c r="D586" s="36"/>
     </row>
     <row r="587" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A587" s="50"/>
-      <c r="B587" s="49"/>
-      <c r="D587" s="50"/>
+      <c r="A587" s="36"/>
+      <c r="B587" s="35"/>
+      <c r="D587" s="36"/>
     </row>
     <row r="588" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A588" s="50"/>
-      <c r="B588" s="49"/>
-      <c r="D588" s="50"/>
+      <c r="A588" s="36"/>
+      <c r="B588" s="35"/>
+      <c r="D588" s="36"/>
     </row>
     <row r="589" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A589" s="50"/>
-      <c r="B589" s="49"/>
-      <c r="D589" s="50"/>
+      <c r="A589" s="36"/>
+      <c r="B589" s="35"/>
+      <c r="D589" s="36"/>
     </row>
     <row r="590" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A590" s="50"/>
-      <c r="B590" s="49"/>
-      <c r="D590" s="50"/>
+      <c r="A590" s="36"/>
+      <c r="B590" s="35"/>
+      <c r="D590" s="36"/>
     </row>
     <row r="591" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A591" s="50"/>
-      <c r="B591" s="49"/>
-      <c r="D591" s="50"/>
+      <c r="A591" s="36"/>
+      <c r="B591" s="35"/>
+      <c r="D591" s="36"/>
     </row>
     <row r="592" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A592" s="50"/>
-      <c r="B592" s="49"/>
-      <c r="D592" s="50"/>
+      <c r="A592" s="36"/>
+      <c r="B592" s="35"/>
+      <c r="D592" s="36"/>
     </row>
     <row r="593" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A593" s="50"/>
-      <c r="B593" s="49"/>
-      <c r="D593" s="50"/>
+      <c r="A593" s="36"/>
+      <c r="B593" s="35"/>
+      <c r="D593" s="36"/>
     </row>
     <row r="594" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A594" s="50"/>
-      <c r="B594" s="49"/>
-      <c r="D594" s="50"/>
+      <c r="A594" s="36"/>
+      <c r="B594" s="35"/>
+      <c r="D594" s="36"/>
     </row>
     <row r="595" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A595" s="50"/>
-      <c r="B595" s="49"/>
-      <c r="D595" s="50"/>
+      <c r="A595" s="36"/>
+      <c r="B595" s="35"/>
+      <c r="D595" s="36"/>
     </row>
     <row r="596" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A596" s="50"/>
-      <c r="B596" s="49"/>
-      <c r="D596" s="50"/>
+      <c r="A596" s="36"/>
+      <c r="B596" s="35"/>
+      <c r="D596" s="36"/>
     </row>
     <row r="597" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A597" s="50"/>
-      <c r="B597" s="49"/>
-      <c r="D597" s="50"/>
+      <c r="A597" s="36"/>
+      <c r="B597" s="35"/>
+      <c r="D597" s="36"/>
     </row>
     <row r="598" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A598" s="50"/>
-      <c r="B598" s="49"/>
-      <c r="D598" s="50"/>
+      <c r="A598" s="36"/>
+      <c r="B598" s="35"/>
+      <c r="D598" s="36"/>
     </row>
     <row r="599" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A599" s="50"/>
-      <c r="B599" s="49"/>
-      <c r="D599" s="50"/>
+      <c r="A599" s="36"/>
+      <c r="B599" s="35"/>
+      <c r="D599" s="36"/>
     </row>
     <row r="600" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A600" s="50"/>
-      <c r="B600" s="49"/>
-      <c r="D600" s="50"/>
+      <c r="A600" s="36"/>
+      <c r="B600" s="35"/>
+      <c r="D600" s="36"/>
     </row>
     <row r="601" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A601" s="50"/>
-      <c r="B601" s="49"/>
-      <c r="D601" s="50"/>
+      <c r="A601" s="36"/>
+      <c r="B601" s="35"/>
+      <c r="D601" s="36"/>
     </row>
     <row r="602" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A602" s="50"/>
-      <c r="B602" s="49"/>
-      <c r="D602" s="50"/>
+      <c r="A602" s="36"/>
+      <c r="B602" s="35"/>
+      <c r="D602" s="36"/>
     </row>
     <row r="603" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A603" s="50"/>
-      <c r="B603" s="49"/>
-      <c r="D603" s="50"/>
+      <c r="A603" s="36"/>
+      <c r="B603" s="35"/>
+      <c r="D603" s="36"/>
     </row>
     <row r="604" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A604" s="50"/>
-      <c r="B604" s="49"/>
-      <c r="D604" s="50"/>
+      <c r="A604" s="36"/>
+      <c r="B604" s="35"/>
+      <c r="D604" s="36"/>
     </row>
     <row r="605" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A605" s="50"/>
-      <c r="B605" s="49"/>
-      <c r="D605" s="50"/>
+      <c r="A605" s="36"/>
+      <c r="B605" s="35"/>
+      <c r="D605" s="36"/>
     </row>
     <row r="606" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A606" s="50"/>
-      <c r="B606" s="49"/>
-      <c r="D606" s="50"/>
+      <c r="A606" s="36"/>
+      <c r="B606" s="35"/>
+      <c r="D606" s="36"/>
     </row>
     <row r="607" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A607" s="50"/>
-      <c r="B607" s="49"/>
-      <c r="D607" s="50"/>
+      <c r="A607" s="36"/>
+      <c r="B607" s="35"/>
+      <c r="D607" s="36"/>
     </row>
     <row r="608" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A608" s="50"/>
-      <c r="B608" s="49"/>
-      <c r="D608" s="50"/>
+      <c r="A608" s="36"/>
+      <c r="B608" s="35"/>
+      <c r="D608" s="36"/>
     </row>
     <row r="609" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A609" s="50"/>
-      <c r="B609" s="49"/>
-      <c r="D609" s="50"/>
+      <c r="A609" s="36"/>
+      <c r="B609" s="35"/>
+      <c r="D609" s="36"/>
     </row>
     <row r="610" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A610" s="50"/>
-      <c r="B610" s="49"/>
-      <c r="D610" s="50"/>
+      <c r="A610" s="36"/>
+      <c r="B610" s="35"/>
+      <c r="D610" s="36"/>
     </row>
     <row r="611" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A611" s="50"/>
-      <c r="B611" s="49"/>
-      <c r="D611" s="50"/>
+      <c r="A611" s="36"/>
+      <c r="B611" s="35"/>
+      <c r="D611" s="36"/>
     </row>
     <row r="612" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A612" s="50"/>
-      <c r="B612" s="49"/>
-      <c r="D612" s="50"/>
+      <c r="A612" s="36"/>
+      <c r="B612" s="35"/>
+      <c r="D612" s="36"/>
     </row>
     <row r="613" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A613" s="50"/>
-      <c r="B613" s="49"/>
-      <c r="D613" s="50"/>
+      <c r="A613" s="36"/>
+      <c r="B613" s="35"/>
+      <c r="D613" s="36"/>
     </row>
     <row r="614" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A614" s="50"/>
-      <c r="B614" s="49"/>
-      <c r="D614" s="50"/>
+      <c r="A614" s="36"/>
+      <c r="B614" s="35"/>
+      <c r="D614" s="36"/>
     </row>
     <row r="615" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A615" s="50"/>
-      <c r="B615" s="49"/>
-      <c r="D615" s="50"/>
+      <c r="A615" s="36"/>
+      <c r="B615" s="35"/>
+      <c r="D615" s="36"/>
     </row>
     <row r="616" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A616" s="50"/>
-      <c r="B616" s="49"/>
-      <c r="D616" s="50"/>
+      <c r="A616" s="36"/>
+      <c r="B616" s="35"/>
+      <c r="D616" s="36"/>
     </row>
     <row r="617" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A617" s="50"/>
-      <c r="B617" s="49"/>
-      <c r="D617" s="50"/>
+      <c r="A617" s="36"/>
+      <c r="B617" s="35"/>
+      <c r="D617" s="36"/>
     </row>
     <row r="618" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A618" s="50"/>
-      <c r="B618" s="49"/>
-      <c r="D618" s="50"/>
+      <c r="A618" s="36"/>
+      <c r="B618" s="35"/>
+      <c r="D618" s="36"/>
     </row>
     <row r="619" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A619" s="50"/>
-      <c r="B619" s="49"/>
-      <c r="D619" s="50"/>
+      <c r="A619" s="36"/>
+      <c r="B619" s="35"/>
+      <c r="D619" s="36"/>
     </row>
     <row r="620" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A620" s="50"/>
-      <c r="B620" s="49"/>
-      <c r="D620" s="50"/>
+      <c r="A620" s="36"/>
+      <c r="B620" s="35"/>
+      <c r="D620" s="36"/>
     </row>
     <row r="621" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A621" s="50"/>
-      <c r="B621" s="49"/>
-      <c r="D621" s="50"/>
+      <c r="A621" s="36"/>
+      <c r="B621" s="35"/>
+      <c r="D621" s="36"/>
     </row>
     <row r="622" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A622" s="50"/>
-      <c r="B622" s="49"/>
-      <c r="D622" s="50"/>
+      <c r="A622" s="36"/>
+      <c r="B622" s="35"/>
+      <c r="D622" s="36"/>
     </row>
     <row r="623" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A623" s="50"/>
-      <c r="B623" s="49"/>
-      <c r="D623" s="50"/>
+      <c r="A623" s="36"/>
+      <c r="B623" s="35"/>
+      <c r="D623" s="36"/>
     </row>
     <row r="624" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A624" s="50"/>
-      <c r="B624" s="49"/>
-      <c r="D624" s="50"/>
+      <c r="A624" s="36"/>
+      <c r="B624" s="35"/>
+      <c r="D624" s="36"/>
     </row>
     <row r="625" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A625" s="50"/>
-      <c r="B625" s="49"/>
-      <c r="D625" s="50"/>
+      <c r="A625" s="36"/>
+      <c r="B625" s="35"/>
+      <c r="D625" s="36"/>
     </row>
     <row r="626" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A626" s="50"/>
-      <c r="B626" s="49"/>
-      <c r="D626" s="50"/>
+      <c r="A626" s="36"/>
+      <c r="B626" s="35"/>
+      <c r="D626" s="36"/>
     </row>
     <row r="627" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A627" s="50"/>
-      <c r="B627" s="49"/>
-      <c r="D627" s="50"/>
+      <c r="A627" s="36"/>
+      <c r="B627" s="35"/>
+      <c r="D627" s="36"/>
     </row>
     <row r="628" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A628" s="50"/>
-      <c r="B628" s="49"/>
-      <c r="D628" s="50"/>
+      <c r="A628" s="36"/>
+      <c r="B628" s="35"/>
+      <c r="D628" s="36"/>
     </row>
     <row r="629" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A629" s="50"/>
-      <c r="B629" s="49"/>
-      <c r="D629" s="50"/>
+      <c r="A629" s="36"/>
+      <c r="B629" s="35"/>
+      <c r="D629" s="36"/>
     </row>
     <row r="630" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A630" s="50"/>
-      <c r="B630" s="49"/>
-      <c r="D630" s="50"/>
+      <c r="A630" s="36"/>
+      <c r="B630" s="35"/>
+      <c r="D630" s="36"/>
     </row>
     <row r="631" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A631" s="50"/>
-      <c r="B631" s="49"/>
-      <c r="D631" s="50"/>
+      <c r="A631" s="36"/>
+      <c r="B631" s="35"/>
+      <c r="D631" s="36"/>
     </row>
     <row r="632" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A632" s="50"/>
-      <c r="B632" s="49"/>
-      <c r="D632" s="50"/>
+      <c r="A632" s="36"/>
+      <c r="B632" s="35"/>
+      <c r="D632" s="36"/>
     </row>
     <row r="633" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A633" s="50"/>
-      <c r="B633" s="49"/>
-      <c r="D633" s="50"/>
+      <c r="A633" s="36"/>
+      <c r="B633" s="35"/>
+      <c r="D633" s="36"/>
     </row>
     <row r="634" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A634" s="50"/>
-      <c r="B634" s="49"/>
-      <c r="D634" s="50"/>
+      <c r="A634" s="36"/>
+      <c r="B634" s="35"/>
+      <c r="D634" s="36"/>
     </row>
     <row r="635" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A635" s="50"/>
-      <c r="B635" s="49"/>
-      <c r="D635" s="50"/>
+      <c r="A635" s="36"/>
+      <c r="B635" s="35"/>
+      <c r="D635" s="36"/>
     </row>
     <row r="636" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A636" s="50"/>
-      <c r="B636" s="49"/>
-      <c r="D636" s="50"/>
+      <c r="A636" s="36"/>
+      <c r="B636" s="35"/>
+      <c r="D636" s="36"/>
     </row>
     <row r="637" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A637" s="50"/>
-      <c r="B637" s="49"/>
-      <c r="D637" s="50"/>
+      <c r="A637" s="36"/>
+      <c r="B637" s="35"/>
+      <c r="D637" s="36"/>
     </row>
     <row r="638" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A638" s="50"/>
-      <c r="B638" s="49"/>
-      <c r="D638" s="50"/>
+      <c r="A638" s="36"/>
+      <c r="B638" s="35"/>
+      <c r="D638" s="36"/>
     </row>
     <row r="639" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A639" s="50"/>
-      <c r="B639" s="49"/>
-      <c r="D639" s="50"/>
+      <c r="A639" s="36"/>
+      <c r="B639" s="35"/>
+      <c r="D639" s="36"/>
     </row>
     <row r="640" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A640" s="50"/>
-      <c r="B640" s="49"/>
-      <c r="D640" s="50"/>
+      <c r="A640" s="36"/>
+      <c r="B640" s="35"/>
+      <c r="D640" s="36"/>
     </row>
     <row r="641" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A641" s="50"/>
-      <c r="B641" s="49"/>
-      <c r="D641" s="50"/>
+      <c r="A641" s="36"/>
+      <c r="B641" s="35"/>
+      <c r="D641" s="36"/>
     </row>
     <row r="642" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A642" s="50"/>
-      <c r="B642" s="49"/>
-      <c r="D642" s="50"/>
+      <c r="A642" s="36"/>
+      <c r="B642" s="35"/>
+      <c r="D642" s="36"/>
     </row>
     <row r="643" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A643" s="50"/>
-      <c r="B643" s="49"/>
-      <c r="D643" s="50"/>
+      <c r="A643" s="36"/>
+      <c r="B643" s="35"/>
+      <c r="D643" s="36"/>
     </row>
     <row r="644" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A644" s="50"/>
-      <c r="B644" s="49"/>
-      <c r="D644" s="50"/>
+      <c r="A644" s="36"/>
+      <c r="B644" s="35"/>
+      <c r="D644" s="36"/>
     </row>
     <row r="645" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A645" s="50"/>
-      <c r="B645" s="49"/>
-      <c r="D645" s="50"/>
+      <c r="A645" s="36"/>
+      <c r="B645" s="35"/>
+      <c r="D645" s="36"/>
     </row>
     <row r="646" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A646" s="50"/>
-      <c r="B646" s="49"/>
-      <c r="D646" s="50"/>
+      <c r="A646" s="36"/>
+      <c r="B646" s="35"/>
+      <c r="D646" s="36"/>
     </row>
     <row r="647" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A647" s="50"/>
-      <c r="B647" s="49"/>
-      <c r="D647" s="50"/>
+      <c r="A647" s="36"/>
+      <c r="B647" s="35"/>
+      <c r="D647" s="36"/>
     </row>
     <row r="648" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A648" s="50"/>
-      <c r="B648" s="49"/>
-      <c r="D648" s="50"/>
+      <c r="A648" s="36"/>
+      <c r="B648" s="35"/>
+      <c r="D648" s="36"/>
     </row>
     <row r="649" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A649" s="50"/>
-      <c r="B649" s="49"/>
-      <c r="D649" s="50"/>
+      <c r="A649" s="36"/>
+      <c r="B649" s="35"/>
+      <c r="D649" s="36"/>
     </row>
     <row r="650" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A650" s="50"/>
-      <c r="B650" s="49"/>
-      <c r="D650" s="50"/>
+      <c r="A650" s="36"/>
+      <c r="B650" s="35"/>
+      <c r="D650" s="36"/>
     </row>
     <row r="651" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A651" s="50"/>
-      <c r="B651" s="49"/>
-      <c r="D651" s="50"/>
+      <c r="A651" s="36"/>
+      <c r="B651" s="35"/>
+      <c r="D651" s="36"/>
     </row>
     <row r="652" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A652" s="50"/>
-      <c r="B652" s="49"/>
-      <c r="D652" s="50"/>
+      <c r="A652" s="36"/>
+      <c r="B652" s="35"/>
+      <c r="D652" s="36"/>
     </row>
     <row r="653" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A653" s="50"/>
-      <c r="B653" s="49"/>
-      <c r="D653" s="50"/>
+      <c r="A653" s="36"/>
+      <c r="B653" s="35"/>
+      <c r="D653" s="36"/>
     </row>
     <row r="654" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A654" s="50"/>
-      <c r="B654" s="49"/>
-      <c r="D654" s="50"/>
+      <c r="A654" s="36"/>
+      <c r="B654" s="35"/>
+      <c r="D654" s="36"/>
     </row>
     <row r="655" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A655" s="50"/>
-      <c r="B655" s="49"/>
-      <c r="D655" s="50"/>
+      <c r="A655" s="36"/>
+      <c r="B655" s="35"/>
+      <c r="D655" s="36"/>
     </row>
     <row r="656" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A656" s="50"/>
-      <c r="B656" s="49"/>
-      <c r="D656" s="50"/>
+      <c r="A656" s="36"/>
+      <c r="B656" s="35"/>
+      <c r="D656" s="36"/>
     </row>
     <row r="657" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A657" s="50"/>
-      <c r="B657" s="49"/>
-      <c r="D657" s="50"/>
+      <c r="A657" s="36"/>
+      <c r="B657" s="35"/>
+      <c r="D657" s="36"/>
     </row>
     <row r="658" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A658" s="50"/>
-      <c r="B658" s="49"/>
-      <c r="D658" s="50"/>
+      <c r="A658" s="36"/>
+      <c r="B658" s="35"/>
+      <c r="D658" s="36"/>
     </row>
     <row r="659" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A659" s="50"/>
-      <c r="B659" s="49"/>
-      <c r="D659" s="50"/>
+      <c r="A659" s="36"/>
+      <c r="B659" s="35"/>
+      <c r="D659" s="36"/>
     </row>
     <row r="660" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A660" s="50"/>
-      <c r="B660" s="49"/>
-      <c r="D660" s="50"/>
+      <c r="A660" s="36"/>
+      <c r="B660" s="35"/>
+      <c r="D660" s="36"/>
     </row>
     <row r="661" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A661" s="50"/>
-      <c r="B661" s="49"/>
-      <c r="D661" s="50"/>
+      <c r="A661" s="36"/>
+      <c r="B661" s="35"/>
+      <c r="D661" s="36"/>
     </row>
     <row r="662" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A662" s="50"/>
-      <c r="B662" s="49"/>
-      <c r="D662" s="50"/>
+      <c r="A662" s="36"/>
+      <c r="B662" s="35"/>
+      <c r="D662" s="36"/>
     </row>
     <row r="663" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A663" s="50"/>
-      <c r="B663" s="49"/>
-      <c r="D663" s="50"/>
+      <c r="A663" s="36"/>
+      <c r="B663" s="35"/>
+      <c r="D663" s="36"/>
     </row>
     <row r="664" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A664" s="50"/>
-      <c r="B664" s="49"/>
-      <c r="D664" s="50"/>
+      <c r="A664" s="36"/>
+      <c r="B664" s="35"/>
+      <c r="D664" s="36"/>
     </row>
     <row r="665" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A665" s="50"/>
-      <c r="B665" s="49"/>
-      <c r="D665" s="50"/>
+      <c r="A665" s="36"/>
+      <c r="B665" s="35"/>
+      <c r="D665" s="36"/>
     </row>
     <row r="666" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A666" s="50"/>
-      <c r="B666" s="49"/>
-      <c r="D666" s="50"/>
+      <c r="A666" s="36"/>
+      <c r="B666" s="35"/>
+      <c r="D666" s="36"/>
     </row>
     <row r="667" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A667" s="50"/>
-      <c r="B667" s="49"/>
-      <c r="D667" s="50"/>
+      <c r="A667" s="36"/>
+      <c r="B667" s="35"/>
+      <c r="D667" s="36"/>
     </row>
     <row r="668" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A668" s="50"/>
-      <c r="B668" s="49"/>
-      <c r="D668" s="50"/>
+      <c r="A668" s="36"/>
+      <c r="B668" s="35"/>
+      <c r="D668" s="36"/>
     </row>
     <row r="669" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A669" s="50"/>
-      <c r="B669" s="49"/>
-      <c r="D669" s="50"/>
+      <c r="A669" s="36"/>
+      <c r="B669" s="35"/>
+      <c r="D669" s="36"/>
     </row>
     <row r="670" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A670" s="50"/>
-      <c r="B670" s="49"/>
-      <c r="D670" s="50"/>
+      <c r="A670" s="36"/>
+      <c r="B670" s="35"/>
+      <c r="D670" s="36"/>
     </row>
     <row r="671" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A671" s="50"/>
-      <c r="B671" s="49"/>
-      <c r="D671" s="50"/>
+      <c r="A671" s="36"/>
+      <c r="B671" s="35"/>
+      <c r="D671" s="36"/>
     </row>
     <row r="672" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A672" s="50"/>
-      <c r="B672" s="49"/>
-      <c r="D672" s="50"/>
+      <c r="A672" s="36"/>
+      <c r="B672" s="35"/>
+      <c r="D672" s="36"/>
     </row>
     <row r="673" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A673" s="50"/>
-      <c r="B673" s="49"/>
-      <c r="D673" s="50"/>
+      <c r="A673" s="36"/>
+      <c r="B673" s="35"/>
+      <c r="D673" s="36"/>
     </row>
     <row r="674" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A674" s="50"/>
-      <c r="B674" s="49"/>
-      <c r="D674" s="50"/>
+      <c r="A674" s="36"/>
+      <c r="B674" s="35"/>
+      <c r="D674" s="36"/>
     </row>
     <row r="675" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A675" s="50"/>
-      <c r="B675" s="49"/>
-      <c r="D675" s="50"/>
+      <c r="A675" s="36"/>
+      <c r="B675" s="35"/>
+      <c r="D675" s="36"/>
     </row>
     <row r="676" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A676" s="50"/>
-      <c r="B676" s="49"/>
-      <c r="D676" s="50"/>
+      <c r="A676" s="36"/>
+      <c r="B676" s="35"/>
+      <c r="D676" s="36"/>
     </row>
     <row r="677" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A677" s="50"/>
-      <c r="B677" s="49"/>
-      <c r="D677" s="50"/>
+      <c r="A677" s="36"/>
+      <c r="B677" s="35"/>
+      <c r="D677" s="36"/>
     </row>
     <row r="678" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A678" s="50"/>
-      <c r="B678" s="49"/>
-      <c r="D678" s="50"/>
+      <c r="A678" s="36"/>
+      <c r="B678" s="35"/>
+      <c r="D678" s="36"/>
     </row>
     <row r="679" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A679" s="50"/>
-      <c r="B679" s="49"/>
-      <c r="D679" s="50"/>
+      <c r="A679" s="36"/>
+      <c r="B679" s="35"/>
+      <c r="D679" s="36"/>
     </row>
     <row r="680" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A680" s="50"/>
-      <c r="B680" s="49"/>
-      <c r="D680" s="50"/>
+      <c r="A680" s="36"/>
+      <c r="B680" s="35"/>
+      <c r="D680" s="36"/>
     </row>
     <row r="681" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A681" s="50"/>
-      <c r="B681" s="49"/>
-      <c r="D681" s="50"/>
+      <c r="A681" s="36"/>
+      <c r="B681" s="35"/>
+      <c r="D681" s="36"/>
     </row>
     <row r="682" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A682" s="50"/>
-      <c r="B682" s="49"/>
-      <c r="D682" s="50"/>
+      <c r="A682" s="36"/>
+      <c r="B682" s="35"/>
+      <c r="D682" s="36"/>
     </row>
     <row r="683" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A683" s="50"/>
-      <c r="B683" s="49"/>
-      <c r="D683" s="50"/>
+      <c r="A683" s="36"/>
+      <c r="B683" s="35"/>
+      <c r="D683" s="36"/>
     </row>
     <row r="684" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A684" s="50"/>
-      <c r="B684" s="49"/>
-      <c r="D684" s="50"/>
+      <c r="A684" s="36"/>
+      <c r="B684" s="35"/>
+      <c r="D684" s="36"/>
     </row>
     <row r="685" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A685" s="50"/>
-      <c r="B685" s="49"/>
-      <c r="D685" s="50"/>
+      <c r="A685" s="36"/>
+      <c r="B685" s="35"/>
+      <c r="D685" s="36"/>
     </row>
     <row r="686" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A686" s="50"/>
-      <c r="B686" s="49"/>
-      <c r="D686" s="50"/>
+      <c r="A686" s="36"/>
+      <c r="B686" s="35"/>
+      <c r="D686" s="36"/>
     </row>
     <row r="687" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A687" s="50"/>
-      <c r="B687" s="49"/>
-      <c r="D687" s="50"/>
+      <c r="A687" s="36"/>
+      <c r="B687" s="35"/>
+      <c r="D687" s="36"/>
     </row>
     <row r="688" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A688" s="50"/>
-      <c r="B688" s="49"/>
-      <c r="D688" s="50"/>
+      <c r="A688" s="36"/>
+      <c r="B688" s="35"/>
+      <c r="D688" s="36"/>
     </row>
     <row r="689" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A689" s="50"/>
-      <c r="B689" s="49"/>
-      <c r="D689" s="50"/>
+      <c r="A689" s="36"/>
+      <c r="B689" s="35"/>
+      <c r="D689" s="36"/>
     </row>
     <row r="690" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A690" s="50"/>
-      <c r="B690" s="49"/>
-      <c r="D690" s="50"/>
+      <c r="A690" s="36"/>
+      <c r="B690" s="35"/>
+      <c r="D690" s="36"/>
     </row>
     <row r="691" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A691" s="50"/>
-      <c r="B691" s="49"/>
-      <c r="D691" s="50"/>
+      <c r="A691" s="36"/>
+      <c r="B691" s="35"/>
+      <c r="D691" s="36"/>
     </row>
     <row r="692" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A692" s="50"/>
-      <c r="B692" s="49"/>
-      <c r="D692" s="50"/>
+      <c r="A692" s="36"/>
+      <c r="B692" s="35"/>
+      <c r="D692" s="36"/>
     </row>
     <row r="693" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A693" s="50"/>
-      <c r="B693" s="49"/>
-      <c r="D693" s="50"/>
+      <c r="A693" s="36"/>
+      <c r="B693" s="35"/>
+      <c r="D693" s="36"/>
     </row>
     <row r="694" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A694" s="50"/>
-      <c r="B694" s="49"/>
-      <c r="D694" s="50"/>
+      <c r="A694" s="36"/>
+      <c r="B694" s="35"/>
+      <c r="D694" s="36"/>
     </row>
     <row r="695" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A695" s="50"/>
-      <c r="B695" s="49"/>
-      <c r="D695" s="50"/>
+      <c r="A695" s="36"/>
+      <c r="B695" s="35"/>
+      <c r="D695" s="36"/>
     </row>
     <row r="696" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A696" s="50"/>
-      <c r="B696" s="49"/>
-      <c r="D696" s="50"/>
+      <c r="A696" s="36"/>
+      <c r="B696" s="35"/>
+      <c r="D696" s="36"/>
     </row>
     <row r="697" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A697" s="50"/>
-      <c r="B697" s="49"/>
-      <c r="D697" s="50"/>
+      <c r="A697" s="36"/>
+      <c r="B697" s="35"/>
+      <c r="D697" s="36"/>
     </row>
     <row r="698" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A698" s="50"/>
-      <c r="B698" s="49"/>
-      <c r="D698" s="50"/>
+      <c r="A698" s="36"/>
+      <c r="B698" s="35"/>
+      <c r="D698" s="36"/>
     </row>
     <row r="699" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A699" s="50"/>
-      <c r="B699" s="49"/>
-      <c r="D699" s="50"/>
+      <c r="A699" s="36"/>
+      <c r="B699" s="35"/>
+      <c r="D699" s="36"/>
     </row>
     <row r="700" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A700" s="50"/>
-      <c r="B700" s="49"/>
-      <c r="D700" s="50"/>
+      <c r="A700" s="36"/>
+      <c r="B700" s="35"/>
+      <c r="D700" s="36"/>
     </row>
     <row r="701" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A701" s="50"/>
-      <c r="B701" s="49"/>
-      <c r="D701" s="50"/>
+      <c r="A701" s="36"/>
+      <c r="B701" s="35"/>
+      <c r="D701" s="36"/>
     </row>
     <row r="702" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A702" s="50"/>
-      <c r="B702" s="49"/>
-      <c r="D702" s="50"/>
+      <c r="A702" s="36"/>
+      <c r="B702" s="35"/>
+      <c r="D702" s="36"/>
     </row>
     <row r="703" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A703" s="50"/>
-      <c r="B703" s="49"/>
-      <c r="D703" s="50"/>
+      <c r="A703" s="36"/>
+      <c r="B703" s="35"/>
+      <c r="D703" s="36"/>
     </row>
     <row r="704" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A704" s="50"/>
-      <c r="B704" s="49"/>
-      <c r="D704" s="50"/>
+      <c r="A704" s="36"/>
+      <c r="B704" s="35"/>
+      <c r="D704" s="36"/>
     </row>
     <row r="705" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A705" s="50"/>
-      <c r="B705" s="49"/>
-      <c r="D705" s="50"/>
+      <c r="A705" s="36"/>
+      <c r="B705" s="35"/>
+      <c r="D705" s="36"/>
     </row>
     <row r="706" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A706" s="50"/>
-      <c r="B706" s="49"/>
-      <c r="D706" s="50"/>
+      <c r="A706" s="36"/>
+      <c r="B706" s="35"/>
+      <c r="D706" s="36"/>
     </row>
     <row r="707" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A707" s="50"/>
-      <c r="B707" s="49"/>
-      <c r="D707" s="50"/>
+      <c r="A707" s="36"/>
+      <c r="B707" s="35"/>
+      <c r="D707" s="36"/>
     </row>
     <row r="708" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A708" s="50"/>
-      <c r="B708" s="49"/>
-      <c r="D708" s="50"/>
+      <c r="A708" s="36"/>
+      <c r="B708" s="35"/>
+      <c r="D708" s="36"/>
     </row>
     <row r="709" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A709" s="50"/>
-      <c r="B709" s="49"/>
-      <c r="D709" s="50"/>
+      <c r="A709" s="36"/>
+      <c r="B709" s="35"/>
+      <c r="D709" s="36"/>
     </row>
     <row r="710" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A710" s="50"/>
-      <c r="B710" s="49"/>
-      <c r="D710" s="50"/>
+      <c r="A710" s="36"/>
+      <c r="B710" s="35"/>
+      <c r="D710" s="36"/>
     </row>
     <row r="711" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A711" s="50"/>
-      <c r="B711" s="49"/>
-      <c r="D711" s="50"/>
+      <c r="A711" s="36"/>
+      <c r="B711" s="35"/>
+      <c r="D711" s="36"/>
     </row>
     <row r="712" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A712" s="50"/>
-      <c r="B712" s="49"/>
-      <c r="D712" s="50"/>
+      <c r="A712" s="36"/>
+      <c r="B712" s="35"/>
+      <c r="D712" s="36"/>
     </row>
     <row r="713" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A713" s="50"/>
-      <c r="B713" s="49"/>
-      <c r="D713" s="50"/>
+      <c r="A713" s="36"/>
+      <c r="B713" s="35"/>
+      <c r="D713" s="36"/>
     </row>
     <row r="714" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A714" s="50"/>
-      <c r="B714" s="49"/>
-      <c r="D714" s="50"/>
+      <c r="A714" s="36"/>
+      <c r="B714" s="35"/>
+      <c r="D714" s="36"/>
     </row>
     <row r="715" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A715" s="50"/>
-      <c r="B715" s="49"/>
-      <c r="D715" s="50"/>
+      <c r="A715" s="36"/>
+      <c r="B715" s="35"/>
+      <c r="D715" s="36"/>
     </row>
     <row r="716" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A716" s="50"/>
-      <c r="B716" s="49"/>
-      <c r="D716" s="50"/>
+      <c r="A716" s="36"/>
+      <c r="B716" s="35"/>
+      <c r="D716" s="36"/>
     </row>
     <row r="717" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A717" s="50"/>
-      <c r="B717" s="49"/>
-      <c r="D717" s="50"/>
+      <c r="A717" s="36"/>
+      <c r="B717" s="35"/>
+      <c r="D717" s="36"/>
     </row>
     <row r="718" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A718" s="50"/>
-      <c r="B718" s="49"/>
-      <c r="D718" s="50"/>
+      <c r="A718" s="36"/>
+      <c r="B718" s="35"/>
+      <c r="D718" s="36"/>
     </row>
     <row r="719" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A719" s="50"/>
-      <c r="B719" s="49"/>
-      <c r="D719" s="50"/>
+      <c r="A719" s="36"/>
+      <c r="B719" s="35"/>
+      <c r="D719" s="36"/>
     </row>
     <row r="720" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A720" s="50"/>
-      <c r="B720" s="49"/>
-      <c r="D720" s="50"/>
+      <c r="A720" s="36"/>
+      <c r="B720" s="35"/>
+      <c r="D720" s="36"/>
     </row>
     <row r="721" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A721" s="50"/>
-      <c r="B721" s="49"/>
-      <c r="D721" s="50"/>
+      <c r="A721" s="36"/>
+      <c r="B721" s="35"/>
+      <c r="D721" s="36"/>
     </row>
     <row r="722" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A722" s="50"/>
-      <c r="B722" s="49"/>
-      <c r="D722" s="50"/>
+      <c r="A722" s="36"/>
+      <c r="B722" s="35"/>
+      <c r="D722" s="36"/>
     </row>
     <row r="723" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A723" s="50"/>
-      <c r="B723" s="49"/>
-      <c r="D723" s="50"/>
+      <c r="A723" s="36"/>
+      <c r="B723" s="35"/>
+      <c r="D723" s="36"/>
     </row>
     <row r="724" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A724" s="50"/>
-      <c r="B724" s="49"/>
-      <c r="D724" s="50"/>
+      <c r="A724" s="36"/>
+      <c r="B724" s="35"/>
+      <c r="D724" s="36"/>
     </row>
     <row r="725" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A725" s="50"/>
-      <c r="B725" s="49"/>
-      <c r="D725" s="50"/>
+      <c r="A725" s="36"/>
+      <c r="B725" s="35"/>
+      <c r="D725" s="36"/>
     </row>
     <row r="726" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A726" s="50"/>
-      <c r="B726" s="49"/>
-      <c r="D726" s="50"/>
+      <c r="A726" s="36"/>
+      <c r="B726" s="35"/>
+      <c r="D726" s="36"/>
     </row>
     <row r="727" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A727" s="50"/>
-      <c r="B727" s="49"/>
-      <c r="D727" s="50"/>
+      <c r="A727" s="36"/>
+      <c r="B727" s="35"/>
+      <c r="D727" s="36"/>
     </row>
     <row r="728" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A728" s="50"/>
-      <c r="B728" s="49"/>
-      <c r="D728" s="50"/>
+      <c r="A728" s="36"/>
+      <c r="B728" s="35"/>
+      <c r="D728" s="36"/>
     </row>
     <row r="729" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A729" s="50"/>
-      <c r="B729" s="49"/>
-      <c r="D729" s="50"/>
+      <c r="A729" s="36"/>
+      <c r="B729" s="35"/>
+      <c r="D729" s="36"/>
     </row>
     <row r="730" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A730" s="50"/>
-      <c r="B730" s="49"/>
-      <c r="D730" s="50"/>
+      <c r="A730" s="36"/>
+      <c r="B730" s="35"/>
+      <c r="D730" s="36"/>
     </row>
     <row r="731" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A731" s="50"/>
-      <c r="B731" s="49"/>
-      <c r="D731" s="50"/>
+      <c r="A731" s="36"/>
+      <c r="B731" s="35"/>
+      <c r="D731" s="36"/>
     </row>
     <row r="732" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A732" s="50"/>
-      <c r="B732" s="49"/>
-      <c r="D732" s="50"/>
+      <c r="A732" s="36"/>
+      <c r="B732" s="35"/>
+      <c r="D732" s="36"/>
     </row>
     <row r="733" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A733" s="50"/>
-      <c r="B733" s="49"/>
-      <c r="D733" s="50"/>
+      <c r="A733" s="36"/>
+      <c r="B733" s="35"/>
+      <c r="D733" s="36"/>
     </row>
     <row r="734" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A734" s="50"/>
-      <c r="B734" s="49"/>
-      <c r="D734" s="50"/>
+      <c r="A734" s="36"/>
+      <c r="B734" s="35"/>
+      <c r="D734" s="36"/>
     </row>
     <row r="735" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A735" s="50"/>
-      <c r="B735" s="49"/>
-      <c r="D735" s="50"/>
+      <c r="A735" s="36"/>
+      <c r="B735" s="35"/>
+      <c r="D735" s="36"/>
     </row>
     <row r="736" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A736" s="50"/>
-      <c r="B736" s="49"/>
-      <c r="D736" s="50"/>
+      <c r="A736" s="36"/>
+      <c r="B736" s="35"/>
+      <c r="D736" s="36"/>
     </row>
     <row r="737" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A737" s="50"/>
-      <c r="B737" s="49"/>
-      <c r="D737" s="50"/>
+      <c r="A737" s="36"/>
+      <c r="B737" s="35"/>
+      <c r="D737" s="36"/>
     </row>
     <row r="738" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A738" s="50"/>
-      <c r="B738" s="49"/>
-      <c r="D738" s="50"/>
+      <c r="A738" s="36"/>
+      <c r="B738" s="35"/>
+      <c r="D738" s="36"/>
     </row>
     <row r="739" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A739" s="50"/>
-      <c r="B739" s="49"/>
-      <c r="D739" s="50"/>
+      <c r="A739" s="36"/>
+      <c r="B739" s="35"/>
+      <c r="D739" s="36"/>
     </row>
     <row r="740" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A740" s="50"/>
-      <c r="B740" s="49"/>
-      <c r="D740" s="50"/>
+      <c r="A740" s="36"/>
+      <c r="B740" s="35"/>
+      <c r="D740" s="36"/>
     </row>
     <row r="741" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A741" s="50"/>
-      <c r="B741" s="49"/>
-      <c r="D741" s="50"/>
+      <c r="A741" s="36"/>
+      <c r="B741" s="35"/>
+      <c r="D741" s="36"/>
     </row>
     <row r="742" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A742" s="50"/>
-      <c r="B742" s="49"/>
-      <c r="D742" s="50"/>
+      <c r="A742" s="36"/>
+      <c r="B742" s="35"/>
+      <c r="D742" s="36"/>
     </row>
     <row r="743" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A743" s="50"/>
-      <c r="B743" s="49"/>
-      <c r="D743" s="50"/>
+      <c r="A743" s="36"/>
+      <c r="B743" s="35"/>
+      <c r="D743" s="36"/>
     </row>
     <row r="744" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A744" s="50"/>
-      <c r="B744" s="49"/>
-      <c r="D744" s="50"/>
+      <c r="A744" s="36"/>
+      <c r="B744" s="35"/>
+      <c r="D744" s="36"/>
     </row>
     <row r="745" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A745" s="50"/>
-      <c r="B745" s="49"/>
-      <c r="D745" s="50"/>
+      <c r="A745" s="36"/>
+      <c r="B745" s="35"/>
+      <c r="D745" s="36"/>
     </row>
     <row r="746" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A746" s="50"/>
-      <c r="B746" s="49"/>
-      <c r="D746" s="50"/>
+      <c r="A746" s="36"/>
+      <c r="B746" s="35"/>
+      <c r="D746" s="36"/>
     </row>
     <row r="747" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A747" s="50"/>
-      <c r="B747" s="49"/>
-      <c r="D747" s="50"/>
+      <c r="A747" s="36"/>
+      <c r="B747" s="35"/>
+      <c r="D747" s="36"/>
     </row>
     <row r="748" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A748" s="50"/>
-      <c r="B748" s="49"/>
-      <c r="D748" s="50"/>
+      <c r="A748" s="36"/>
+      <c r="B748" s="35"/>
+      <c r="D748" s="36"/>
     </row>
     <row r="749" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A749" s="50"/>
-      <c r="B749" s="49"/>
-      <c r="D749" s="50"/>
+      <c r="A749" s="36"/>
+      <c r="B749" s="35"/>
+      <c r="D749" s="36"/>
     </row>
     <row r="750" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A750" s="50"/>
-      <c r="B750" s="49"/>
-      <c r="D750" s="50"/>
+      <c r="A750" s="36"/>
+      <c r="B750" s="35"/>
+      <c r="D750" s="36"/>
     </row>
     <row r="751" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A751" s="50"/>
-      <c r="B751" s="49"/>
-      <c r="D751" s="50"/>
+      <c r="A751" s="36"/>
+      <c r="B751" s="35"/>
+      <c r="D751" s="36"/>
     </row>
     <row r="752" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A752" s="50"/>
-      <c r="B752" s="49"/>
-      <c r="D752" s="50"/>
+      <c r="A752" s="36"/>
+      <c r="B752" s="35"/>
+      <c r="D752" s="36"/>
     </row>
     <row r="753" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A753" s="50"/>
-      <c r="B753" s="49"/>
-      <c r="D753" s="50"/>
+      <c r="A753" s="36"/>
+      <c r="B753" s="35"/>
+      <c r="D753" s="36"/>
     </row>
     <row r="754" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A754" s="50"/>
-      <c r="B754" s="49"/>
-      <c r="D754" s="50"/>
+      <c r="A754" s="36"/>
+      <c r="B754" s="35"/>
+      <c r="D754" s="36"/>
     </row>
     <row r="755" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A755" s="50"/>
-      <c r="B755" s="49"/>
-      <c r="D755" s="50"/>
+      <c r="A755" s="36"/>
+      <c r="B755" s="35"/>
+      <c r="D755" s="36"/>
     </row>
     <row r="756" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A756" s="50"/>
-      <c r="B756" s="49"/>
-      <c r="D756" s="50"/>
+      <c r="A756" s="36"/>
+      <c r="B756" s="35"/>
+      <c r="D756" s="36"/>
     </row>
     <row r="757" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A757" s="50"/>
-      <c r="B757" s="49"/>
-      <c r="D757" s="50"/>
+      <c r="A757" s="36"/>
+      <c r="B757" s="35"/>
+      <c r="D757" s="36"/>
     </row>
     <row r="758" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A758" s="50"/>
-      <c r="B758" s="49"/>
-      <c r="D758" s="50"/>
+      <c r="A758" s="36"/>
+      <c r="B758" s="35"/>
+      <c r="D758" s="36"/>
     </row>
     <row r="759" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A759" s="50"/>
-      <c r="B759" s="49"/>
-      <c r="D759" s="50"/>
+      <c r="A759" s="36"/>
+      <c r="B759" s="35"/>
+      <c r="D759" s="36"/>
     </row>
     <row r="760" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A760" s="50"/>
-      <c r="B760" s="49"/>
-      <c r="D760" s="50"/>
+      <c r="A760" s="36"/>
+      <c r="B760" s="35"/>
+      <c r="D760" s="36"/>
     </row>
     <row r="761" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A761" s="50"/>
-      <c r="B761" s="49"/>
-      <c r="D761" s="50"/>
+      <c r="A761" s="36"/>
+      <c r="B761" s="35"/>
+      <c r="D761" s="36"/>
     </row>
     <row r="762" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A762" s="50"/>
-      <c r="B762" s="49"/>
-      <c r="D762" s="50"/>
+      <c r="A762" s="36"/>
+      <c r="B762" s="35"/>
+      <c r="D762" s="36"/>
     </row>
     <row r="763" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A763" s="50"/>
-      <c r="B763" s="49"/>
-      <c r="D763" s="50"/>
+      <c r="A763" s="36"/>
+      <c r="B763" s="35"/>
+      <c r="D763" s="36"/>
     </row>
     <row r="764" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A764" s="50"/>
-      <c r="B764" s="49"/>
-      <c r="D764" s="50"/>
+      <c r="A764" s="36"/>
+      <c r="B764" s="35"/>
+      <c r="D764" s="36"/>
     </row>
     <row r="765" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A765" s="50"/>
-      <c r="B765" s="49"/>
-      <c r="D765" s="50"/>
+      <c r="A765" s="36"/>
+      <c r="B765" s="35"/>
+      <c r="D765" s="36"/>
     </row>
     <row r="766" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A766" s="50"/>
-      <c r="B766" s="49"/>
-      <c r="D766" s="50"/>
+      <c r="A766" s="36"/>
+      <c r="B766" s="35"/>
+      <c r="D766" s="36"/>
     </row>
     <row r="767" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A767" s="50"/>
-      <c r="B767" s="49"/>
-      <c r="D767" s="50"/>
+      <c r="A767" s="36"/>
+      <c r="B767" s="35"/>
+      <c r="D767" s="36"/>
     </row>
     <row r="768" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A768" s="50"/>
-      <c r="B768" s="49"/>
-      <c r="D768" s="50"/>
+      <c r="A768" s="36"/>
+      <c r="B768" s="35"/>
+      <c r="D768" s="36"/>
     </row>
     <row r="769" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A769" s="50"/>
-      <c r="B769" s="49"/>
-      <c r="D769" s="50"/>
+      <c r="A769" s="36"/>
+      <c r="B769" s="35"/>
+      <c r="D769" s="36"/>
     </row>
     <row r="770" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A770" s="50"/>
-      <c r="B770" s="49"/>
-      <c r="D770" s="50"/>
+      <c r="A770" s="36"/>
+      <c r="B770" s="35"/>
+      <c r="D770" s="36"/>
     </row>
     <row r="771" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A771" s="50"/>
-      <c r="B771" s="49"/>
-      <c r="D771" s="50"/>
+      <c r="A771" s="36"/>
+      <c r="B771" s="35"/>
+      <c r="D771" s="36"/>
     </row>
     <row r="772" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A772" s="50"/>
-      <c r="B772" s="49"/>
-      <c r="D772" s="50"/>
+      <c r="A772" s="36"/>
+      <c r="B772" s="35"/>
+      <c r="D772" s="36"/>
     </row>
     <row r="773" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A773" s="50"/>
-      <c r="B773" s="49"/>
-      <c r="D773" s="50"/>
+      <c r="A773" s="36"/>
+      <c r="B773" s="35"/>
+      <c r="D773" s="36"/>
     </row>
     <row r="774" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A774" s="50"/>
-      <c r="B774" s="49"/>
-      <c r="D774" s="50"/>
+      <c r="A774" s="36"/>
+      <c r="B774" s="35"/>
+      <c r="D774" s="36"/>
     </row>
     <row r="775" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A775" s="50"/>
-      <c r="B775" s="49"/>
-      <c r="D775" s="50"/>
+      <c r="A775" s="36"/>
+      <c r="B775" s="35"/>
+      <c r="D775" s="36"/>
     </row>
     <row r="776" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A776" s="50"/>
-      <c r="B776" s="49"/>
-      <c r="D776" s="50"/>
+      <c r="A776" s="36"/>
+      <c r="B776" s="35"/>
+      <c r="D776" s="36"/>
     </row>
     <row r="777" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A777" s="50"/>
-      <c r="B777" s="49"/>
-      <c r="D777" s="50"/>
+      <c r="A777" s="36"/>
+      <c r="B777" s="35"/>
+      <c r="D777" s="36"/>
     </row>
     <row r="778" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A778" s="50"/>
-      <c r="B778" s="49"/>
-      <c r="D778" s="50"/>
+      <c r="A778" s="36"/>
+      <c r="B778" s="35"/>
+      <c r="D778" s="36"/>
     </row>
     <row r="779" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A779" s="50"/>
-      <c r="B779" s="49"/>
-      <c r="D779" s="50"/>
+      <c r="A779" s="36"/>
+      <c r="B779" s="35"/>
+      <c r="D779" s="36"/>
     </row>
     <row r="780" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A780" s="50"/>
-      <c r="B780" s="49"/>
-      <c r="D780" s="50"/>
+      <c r="A780" s="36"/>
+      <c r="B780" s="35"/>
+      <c r="D780" s="36"/>
     </row>
     <row r="781" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A781" s="50"/>
-      <c r="B781" s="49"/>
-      <c r="D781" s="50"/>
+      <c r="A781" s="36"/>
+      <c r="B781" s="35"/>
+      <c r="D781" s="36"/>
     </row>
     <row r="782" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A782" s="50"/>
-      <c r="B782" s="49"/>
-      <c r="D782" s="50"/>
+      <c r="A782" s="36"/>
+      <c r="B782" s="35"/>
+      <c r="D782" s="36"/>
     </row>
     <row r="783" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A783" s="50"/>
-      <c r="B783" s="49"/>
-      <c r="D783" s="50"/>
+      <c r="A783" s="36"/>
+      <c r="B783" s="35"/>
+      <c r="D783" s="36"/>
     </row>
     <row r="784" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A784" s="50"/>
-      <c r="B784" s="49"/>
-      <c r="D784" s="50"/>
+      <c r="A784" s="36"/>
+      <c r="B784" s="35"/>
+      <c r="D784" s="36"/>
     </row>
     <row r="785" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A785" s="50"/>
-      <c r="B785" s="49"/>
-      <c r="D785" s="50"/>
+      <c r="A785" s="36"/>
+      <c r="B785" s="35"/>
+      <c r="D785" s="36"/>
     </row>
     <row r="786" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A786" s="50"/>
-      <c r="B786" s="49"/>
-      <c r="D786" s="50"/>
+      <c r="A786" s="36"/>
+      <c r="B786" s="35"/>
+      <c r="D786" s="36"/>
     </row>
     <row r="787" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A787" s="50"/>
-      <c r="B787" s="49"/>
-      <c r="D787" s="50"/>
+      <c r="A787" s="36"/>
+      <c r="B787" s="35"/>
+      <c r="D787" s="36"/>
     </row>
     <row r="788" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A788" s="50"/>
-      <c r="B788" s="49"/>
-      <c r="D788" s="50"/>
+      <c r="A788" s="36"/>
+      <c r="B788" s="35"/>
+      <c r="D788" s="36"/>
     </row>
     <row r="789" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A789" s="50"/>
-      <c r="B789" s="49"/>
-      <c r="D789" s="50"/>
+      <c r="A789" s="36"/>
+      <c r="B789" s="35"/>
+      <c r="D789" s="36"/>
     </row>
     <row r="790" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A790" s="50"/>
-      <c r="B790" s="49"/>
-      <c r="D790" s="50"/>
+      <c r="A790" s="36"/>
+      <c r="B790" s="35"/>
+      <c r="D790" s="36"/>
     </row>
     <row r="791" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A791" s="50"/>
-      <c r="B791" s="49"/>
-      <c r="D791" s="50"/>
+      <c r="A791" s="36"/>
+      <c r="B791" s="35"/>
+      <c r="D791" s="36"/>
     </row>
     <row r="792" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A792" s="50"/>
-      <c r="B792" s="49"/>
-      <c r="D792" s="50"/>
+      <c r="A792" s="36"/>
+      <c r="B792" s="35"/>
+      <c r="D792" s="36"/>
     </row>
     <row r="793" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A793" s="50"/>
-      <c r="B793" s="49"/>
-      <c r="D793" s="50"/>
+      <c r="A793" s="36"/>
+      <c r="B793" s="35"/>
+      <c r="D793" s="36"/>
     </row>
     <row r="794" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A794" s="50"/>
-      <c r="B794" s="49"/>
-      <c r="D794" s="50"/>
+      <c r="A794" s="36"/>
+      <c r="B794" s="35"/>
+      <c r="D794" s="36"/>
     </row>
     <row r="795" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A795" s="50"/>
-      <c r="B795" s="49"/>
-      <c r="D795" s="50"/>
+      <c r="A795" s="36"/>
+      <c r="B795" s="35"/>
+      <c r="D795" s="36"/>
     </row>
     <row r="796" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A796" s="50"/>
-      <c r="B796" s="49"/>
-      <c r="D796" s="50"/>
+      <c r="A796" s="36"/>
+      <c r="B796" s="35"/>
+      <c r="D796" s="36"/>
     </row>
     <row r="797" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A797" s="50"/>
-      <c r="B797" s="49"/>
-      <c r="D797" s="50"/>
+      <c r="A797" s="36"/>
+      <c r="B797" s="35"/>
+      <c r="D797" s="36"/>
     </row>
     <row r="798" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A798" s="50"/>
-      <c r="B798" s="49"/>
-      <c r="D798" s="50"/>
+      <c r="A798" s="36"/>
+      <c r="B798" s="35"/>
+      <c r="D798" s="36"/>
     </row>
     <row r="799" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A799" s="50"/>
-      <c r="B799" s="49"/>
-      <c r="D799" s="50"/>
+      <c r="A799" s="36"/>
+      <c r="B799" s="35"/>
+      <c r="D799" s="36"/>
     </row>
     <row r="800" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A800" s="50"/>
-      <c r="B800" s="49"/>
-      <c r="D800" s="50"/>
+      <c r="A800" s="36"/>
+      <c r="B800" s="35"/>
+      <c r="D800" s="36"/>
     </row>
     <row r="801" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A801" s="50"/>
-      <c r="B801" s="49"/>
-      <c r="D801" s="50"/>
+      <c r="A801" s="36"/>
+      <c r="B801" s="35"/>
+      <c r="D801" s="36"/>
     </row>
     <row r="802" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A802" s="50"/>
-      <c r="B802" s="49"/>
-      <c r="D802" s="50"/>
+      <c r="A802" s="36"/>
+      <c r="B802" s="35"/>
+      <c r="D802" s="36"/>
     </row>
     <row r="803" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A803" s="50"/>
-      <c r="B803" s="49"/>
-      <c r="D803" s="50"/>
+      <c r="A803" s="36"/>
+      <c r="B803" s="35"/>
+      <c r="D803" s="36"/>
     </row>
     <row r="804" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A804" s="50"/>
-      <c r="B804" s="49"/>
-      <c r="D804" s="50"/>
+      <c r="A804" s="36"/>
+      <c r="B804" s="35"/>
+      <c r="D804" s="36"/>
     </row>
     <row r="805" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A805" s="50"/>
-      <c r="B805" s="49"/>
-      <c r="D805" s="50"/>
+      <c r="A805" s="36"/>
+      <c r="B805" s="35"/>
+      <c r="D805" s="36"/>
     </row>
     <row r="806" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A806" s="50"/>
-      <c r="B806" s="49"/>
-      <c r="D806" s="50"/>
+      <c r="A806" s="36"/>
+      <c r="B806" s="35"/>
+      <c r="D806" s="36"/>
     </row>
     <row r="807" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A807" s="50"/>
-      <c r="B807" s="49"/>
-      <c r="D807" s="50"/>
+      <c r="A807" s="36"/>
+      <c r="B807" s="35"/>
+      <c r="D807" s="36"/>
     </row>
     <row r="808" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A808" s="50"/>
-      <c r="B808" s="49"/>
-      <c r="D808" s="50"/>
+      <c r="A808" s="36"/>
+      <c r="B808" s="35"/>
+      <c r="D808" s="36"/>
     </row>
     <row r="809" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A809" s="50"/>
-      <c r="B809" s="49"/>
-      <c r="D809" s="50"/>
+      <c r="A809" s="36"/>
+      <c r="B809" s="35"/>
+      <c r="D809" s="36"/>
     </row>
     <row r="810" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A810" s="50"/>
-      <c r="B810" s="49"/>
-      <c r="D810" s="50"/>
+      <c r="A810" s="36"/>
+      <c r="B810" s="35"/>
+      <c r="D810" s="36"/>
     </row>
     <row r="811" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A811" s="50"/>
-      <c r="B811" s="49"/>
-      <c r="D811" s="50"/>
+      <c r="A811" s="36"/>
+      <c r="B811" s="35"/>
+      <c r="D811" s="36"/>
     </row>
     <row r="812" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A812" s="50"/>
-      <c r="B812" s="49"/>
-      <c r="D812" s="50"/>
+      <c r="A812" s="36"/>
+      <c r="B812" s="35"/>
+      <c r="D812" s="36"/>
     </row>
     <row r="813" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A813" s="50"/>
-      <c r="B813" s="49"/>
-      <c r="D813" s="50"/>
+      <c r="A813" s="36"/>
+      <c r="B813" s="35"/>
+      <c r="D813" s="36"/>
     </row>
     <row r="814" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A814" s="50"/>
-      <c r="B814" s="49"/>
-      <c r="D814" s="50"/>
+      <c r="A814" s="36"/>
+      <c r="B814" s="35"/>
+      <c r="D814" s="36"/>
     </row>
     <row r="815" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A815" s="50"/>
-      <c r="B815" s="49"/>
-      <c r="D815" s="50"/>
+      <c r="A815" s="36"/>
+      <c r="B815" s="35"/>
+      <c r="D815" s="36"/>
     </row>
     <row r="816" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A816" s="50"/>
-      <c r="B816" s="49"/>
-      <c r="D816" s="50"/>
+      <c r="A816" s="36"/>
+      <c r="B816" s="35"/>
+      <c r="D816" s="36"/>
     </row>
     <row r="817" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A817" s="50"/>
-      <c r="B817" s="49"/>
-      <c r="D817" s="50"/>
+      <c r="A817" s="36"/>
+      <c r="B817" s="35"/>
+      <c r="D817" s="36"/>
     </row>
     <row r="818" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A818" s="50"/>
-      <c r="B818" s="49"/>
-      <c r="D818" s="50"/>
+      <c r="A818" s="36"/>
+      <c r="B818" s="35"/>
+      <c r="D818" s="36"/>
     </row>
     <row r="819" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A819" s="50"/>
-      <c r="B819" s="49"/>
-      <c r="D819" s="50"/>
+      <c r="A819" s="36"/>
+      <c r="B819" s="35"/>
+      <c r="D819" s="36"/>
     </row>
     <row r="820" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A820" s="50"/>
-      <c r="B820" s="49"/>
-      <c r="D820" s="50"/>
+      <c r="A820" s="36"/>
+      <c r="B820" s="35"/>
+      <c r="D820" s="36"/>
     </row>
     <row r="821" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A821" s="50"/>
-      <c r="B821" s="49"/>
-      <c r="D821" s="50"/>
+      <c r="A821" s="36"/>
+      <c r="B821" s="35"/>
+      <c r="D821" s="36"/>
     </row>
     <row r="822" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A822" s="50"/>
-      <c r="B822" s="49"/>
-      <c r="D822" s="50"/>
+      <c r="A822" s="36"/>
+      <c r="B822" s="35"/>
+      <c r="D822" s="36"/>
     </row>
     <row r="823" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A823" s="50"/>
-      <c r="B823" s="49"/>
-      <c r="D823" s="50"/>
+      <c r="A823" s="36"/>
+      <c r="B823" s="35"/>
+      <c r="D823" s="36"/>
     </row>
     <row r="824" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A824" s="50"/>
-      <c r="B824" s="49"/>
-      <c r="D824" s="50"/>
+      <c r="A824" s="36"/>
+      <c r="B824" s="35"/>
+      <c r="D824" s="36"/>
     </row>
     <row r="825" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A825" s="50"/>
-      <c r="B825" s="49"/>
-      <c r="D825" s="50"/>
+      <c r="A825" s="36"/>
+      <c r="B825" s="35"/>
+      <c r="D825" s="36"/>
     </row>
     <row r="826" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A826" s="50"/>
-      <c r="B826" s="49"/>
-      <c r="D826" s="50"/>
+      <c r="A826" s="36"/>
+      <c r="B826" s="35"/>
+      <c r="D826" s="36"/>
     </row>
     <row r="827" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A827" s="50"/>
-      <c r="B827" s="49"/>
-      <c r="D827" s="50"/>
+      <c r="A827" s="36"/>
+      <c r="B827" s="35"/>
+      <c r="D827" s="36"/>
     </row>
     <row r="828" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A828" s="50"/>
-      <c r="B828" s="49"/>
-      <c r="D828" s="50"/>
+      <c r="A828" s="36"/>
+      <c r="B828" s="35"/>
+      <c r="D828" s="36"/>
     </row>
     <row r="829" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A829" s="50"/>
-      <c r="B829" s="49"/>
-      <c r="D829" s="50"/>
+      <c r="A829" s="36"/>
+      <c r="B829" s="35"/>
+      <c r="D829" s="36"/>
     </row>
     <row r="830" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A830" s="50"/>
-      <c r="B830" s="49"/>
-      <c r="D830" s="50"/>
+      <c r="A830" s="36"/>
+      <c r="B830" s="35"/>
+      <c r="D830" s="36"/>
     </row>
     <row r="831" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A831" s="50"/>
-      <c r="B831" s="49"/>
-      <c r="D831" s="50"/>
+      <c r="A831" s="36"/>
+      <c r="B831" s="35"/>
+      <c r="D831" s="36"/>
     </row>
     <row r="832" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A832" s="50"/>
-      <c r="B832" s="49"/>
-      <c r="D832" s="50"/>
+      <c r="A832" s="36"/>
+      <c r="B832" s="35"/>
+      <c r="D832" s="36"/>
     </row>
     <row r="833" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A833" s="50"/>
-      <c r="B833" s="49"/>
-      <c r="D833" s="50"/>
+      <c r="A833" s="36"/>
+      <c r="B833" s="35"/>
+      <c r="D833" s="36"/>
     </row>
     <row r="834" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A834" s="50"/>
-      <c r="B834" s="49"/>
-      <c r="D834" s="50"/>
+      <c r="A834" s="36"/>
+      <c r="B834" s="35"/>
+      <c r="D834" s="36"/>
     </row>
     <row r="835" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A835" s="50"/>
-      <c r="B835" s="49"/>
-      <c r="D835" s="50"/>
+      <c r="A835" s="36"/>
+      <c r="B835" s="35"/>
+      <c r="D835" s="36"/>
     </row>
     <row r="836" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A836" s="50"/>
-      <c r="B836" s="49"/>
-      <c r="D836" s="50"/>
+      <c r="A836" s="36"/>
+      <c r="B836" s="35"/>
+      <c r="D836" s="36"/>
     </row>
     <row r="837" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A837" s="50"/>
-      <c r="B837" s="49"/>
-      <c r="D837" s="50"/>
+      <c r="A837" s="36"/>
+      <c r="B837" s="35"/>
+      <c r="D837" s="36"/>
     </row>
     <row r="838" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A838" s="50"/>
-      <c r="B838" s="49"/>
-      <c r="D838" s="50"/>
+      <c r="A838" s="36"/>
+      <c r="B838" s="35"/>
+      <c r="D838" s="36"/>
     </row>
     <row r="839" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A839" s="50"/>
-      <c r="B839" s="49"/>
-      <c r="D839" s="50"/>
+      <c r="A839" s="36"/>
+      <c r="B839" s="35"/>
+      <c r="D839" s="36"/>
     </row>
     <row r="840" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A840" s="50"/>
-      <c r="B840" s="49"/>
-      <c r="D840" s="50"/>
+      <c r="A840" s="36"/>
+      <c r="B840" s="35"/>
+      <c r="D840" s="36"/>
     </row>
     <row r="841" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A841" s="50"/>
-      <c r="B841" s="49"/>
-      <c r="D841" s="50"/>
+      <c r="A841" s="36"/>
+      <c r="B841" s="35"/>
+      <c r="D841" s="36"/>
     </row>
     <row r="842" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A842" s="50"/>
-      <c r="B842" s="49"/>
-      <c r="D842" s="50"/>
+      <c r="A842" s="36"/>
+      <c r="B842" s="35"/>
+      <c r="D842" s="36"/>
     </row>
     <row r="843" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A843" s="50"/>
-      <c r="B843" s="49"/>
-      <c r="D843" s="50"/>
+      <c r="A843" s="36"/>
+      <c r="B843" s="35"/>
+      <c r="D843" s="36"/>
     </row>
     <row r="844" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A844" s="50"/>
-      <c r="B844" s="49"/>
-      <c r="D844" s="50"/>
+      <c r="A844" s="36"/>
+      <c r="B844" s="35"/>
+      <c r="D844" s="36"/>
     </row>
     <row r="845" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A845" s="50"/>
-      <c r="B845" s="49"/>
-      <c r="D845" s="50"/>
+      <c r="A845" s="36"/>
+      <c r="B845" s="35"/>
+      <c r="D845" s="36"/>
     </row>
     <row r="846" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A846" s="50"/>
-      <c r="B846" s="49"/>
-      <c r="D846" s="50"/>
+      <c r="A846" s="36"/>
+      <c r="B846" s="35"/>
+      <c r="D846" s="36"/>
     </row>
     <row r="847" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A847" s="50"/>
-      <c r="B847" s="49"/>
-      <c r="D847" s="50"/>
+      <c r="A847" s="36"/>
+      <c r="B847" s="35"/>
+      <c r="D847" s="36"/>
     </row>
     <row r="848" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A848" s="50"/>
-      <c r="B848" s="49"/>
-      <c r="D848" s="50"/>
+      <c r="A848" s="36"/>
+      <c r="B848" s="35"/>
+      <c r="D848" s="36"/>
     </row>
     <row r="849" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A849" s="50"/>
-      <c r="B849" s="49"/>
-      <c r="D849" s="50"/>
+      <c r="A849" s="36"/>
+      <c r="B849" s="35"/>
+      <c r="D849" s="36"/>
     </row>
     <row r="850" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A850" s="50"/>
-      <c r="B850" s="49"/>
-      <c r="D850" s="50"/>
+      <c r="A850" s="36"/>
+      <c r="B850" s="35"/>
+      <c r="D850" s="36"/>
     </row>
     <row r="851" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A851" s="50"/>
-      <c r="B851" s="49"/>
-      <c r="D851" s="50"/>
+      <c r="A851" s="36"/>
+      <c r="B851" s="35"/>
+      <c r="D851" s="36"/>
     </row>
     <row r="852" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A852" s="50"/>
-      <c r="B852" s="49"/>
-      <c r="D852" s="50"/>
+      <c r="A852" s="36"/>
+      <c r="B852" s="35"/>
+      <c r="D852" s="36"/>
     </row>
     <row r="853" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A853" s="50"/>
-      <c r="B853" s="49"/>
-      <c r="D853" s="50"/>
+      <c r="A853" s="36"/>
+      <c r="B853" s="35"/>
+      <c r="D853" s="36"/>
     </row>
     <row r="854" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A854" s="50"/>
-      <c r="B854" s="49"/>
-      <c r="D854" s="50"/>
+      <c r="A854" s="36"/>
+      <c r="B854" s="35"/>
+      <c r="D854" s="36"/>
     </row>
     <row r="855" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A855" s="50"/>
-      <c r="B855" s="49"/>
-      <c r="D855" s="50"/>
+      <c r="A855" s="36"/>
+      <c r="B855" s="35"/>
+      <c r="D855" s="36"/>
     </row>
     <row r="856" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A856" s="50"/>
-      <c r="B856" s="49"/>
-      <c r="D856" s="50"/>
+      <c r="A856" s="36"/>
+      <c r="B856" s="35"/>
+      <c r="D856" s="36"/>
     </row>
     <row r="857" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A857" s="50"/>
-      <c r="B857" s="49"/>
-      <c r="D857" s="50"/>
+      <c r="A857" s="36"/>
+      <c r="B857" s="35"/>
+      <c r="D857" s="36"/>
     </row>
     <row r="858" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A858" s="50"/>
-      <c r="B858" s="49"/>
-      <c r="D858" s="50"/>
+      <c r="A858" s="36"/>
+      <c r="B858" s="35"/>
+      <c r="D858" s="36"/>
     </row>
     <row r="859" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A859" s="50"/>
-      <c r="B859" s="49"/>
-      <c r="D859" s="50"/>
+      <c r="A859" s="36"/>
+      <c r="B859" s="35"/>
+      <c r="D859" s="36"/>
     </row>
     <row r="860" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A860" s="50"/>
-      <c r="B860" s="49"/>
-      <c r="D860" s="50"/>
+      <c r="A860" s="36"/>
+      <c r="B860" s="35"/>
+      <c r="D860" s="36"/>
     </row>
     <row r="861" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A861" s="50"/>
-      <c r="B861" s="49"/>
-      <c r="D861" s="50"/>
+      <c r="A861" s="36"/>
+      <c r="B861" s="35"/>
+      <c r="D861" s="36"/>
     </row>
     <row r="862" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A862" s="50"/>
-      <c r="B862" s="49"/>
-      <c r="D862" s="50"/>
+      <c r="A862" s="36"/>
+      <c r="B862" s="35"/>
+      <c r="D862" s="36"/>
     </row>
     <row r="863" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A863" s="50"/>
-      <c r="B863" s="49"/>
-      <c r="D863" s="50"/>
+      <c r="A863" s="36"/>
+      <c r="B863" s="35"/>
+      <c r="D863" s="36"/>
     </row>
     <row r="864" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A864" s="50"/>
-      <c r="B864" s="49"/>
-      <c r="D864" s="50"/>
+      <c r="A864" s="36"/>
+      <c r="B864" s="35"/>
+      <c r="D864" s="36"/>
     </row>
     <row r="865" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A865" s="50"/>
-      <c r="B865" s="49"/>
-      <c r="D865" s="50"/>
+      <c r="A865" s="36"/>
+      <c r="B865" s="35"/>
+      <c r="D865" s="36"/>
     </row>
     <row r="866" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A866" s="50"/>
-      <c r="B866" s="49"/>
-      <c r="D866" s="50"/>
+      <c r="A866" s="36"/>
+      <c r="B866" s="35"/>
+      <c r="D866" s="36"/>
     </row>
     <row r="867" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A867" s="50"/>
-      <c r="B867" s="49"/>
-      <c r="D867" s="50"/>
+      <c r="A867" s="36"/>
+      <c r="B867" s="35"/>
+      <c r="D867" s="36"/>
     </row>
     <row r="868" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A868" s="50"/>
-      <c r="B868" s="49"/>
-      <c r="D868" s="50"/>
+      <c r="A868" s="36"/>
+      <c r="B868" s="35"/>
+      <c r="D868" s="36"/>
     </row>
     <row r="869" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A869" s="50"/>
-      <c r="B869" s="49"/>
-      <c r="D869" s="50"/>
+      <c r="A869" s="36"/>
+      <c r="B869" s="35"/>
+      <c r="D869" s="36"/>
     </row>
     <row r="870" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A870" s="50"/>
-      <c r="B870" s="49"/>
-      <c r="D870" s="50"/>
+      <c r="A870" s="36"/>
+      <c r="B870" s="35"/>
+      <c r="D870" s="36"/>
     </row>
     <row r="871" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A871" s="50"/>
-      <c r="B871" s="49"/>
-      <c r="D871" s="50"/>
+      <c r="A871" s="36"/>
+      <c r="B871" s="35"/>
+      <c r="D871" s="36"/>
     </row>
     <row r="872" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A872" s="50"/>
-      <c r="B872" s="49"/>
-      <c r="D872" s="50"/>
+      <c r="A872" s="36"/>
+      <c r="B872" s="35"/>
+      <c r="D872" s="36"/>
     </row>
     <row r="873" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A873" s="50"/>
-      <c r="B873" s="49"/>
-      <c r="D873" s="50"/>
+      <c r="A873" s="36"/>
+      <c r="B873" s="35"/>
+      <c r="D873" s="36"/>
     </row>
     <row r="874" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A874" s="50"/>
-      <c r="B874" s="49"/>
-      <c r="D874" s="50"/>
+      <c r="A874" s="36"/>
+      <c r="B874" s="35"/>
+      <c r="D874" s="36"/>
     </row>
     <row r="875" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A875" s="50"/>
-      <c r="B875" s="49"/>
-      <c r="D875" s="50"/>
+      <c r="A875" s="36"/>
+      <c r="B875" s="35"/>
+      <c r="D875" s="36"/>
     </row>
     <row r="876" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A876" s="50"/>
-      <c r="B876" s="49"/>
-      <c r="D876" s="50"/>
+      <c r="A876" s="36"/>
+      <c r="B876" s="35"/>
+      <c r="D876" s="36"/>
     </row>
     <row r="877" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A877" s="50"/>
-      <c r="B877" s="49"/>
-      <c r="D877" s="50"/>
+      <c r="A877" s="36"/>
+      <c r="B877" s="35"/>
+      <c r="D877" s="36"/>
     </row>
     <row r="878" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A878" s="50"/>
-      <c r="B878" s="49"/>
-      <c r="D878" s="50"/>
+      <c r="A878" s="36"/>
+      <c r="B878" s="35"/>
+      <c r="D878" s="36"/>
     </row>
     <row r="879" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A879" s="50"/>
-      <c r="B879" s="49"/>
-      <c r="D879" s="50"/>
+      <c r="A879" s="36"/>
+      <c r="B879" s="35"/>
+      <c r="D879" s="36"/>
     </row>
     <row r="880" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A880" s="50"/>
-      <c r="B880" s="49"/>
-      <c r="D880" s="50"/>
+      <c r="A880" s="36"/>
+      <c r="B880" s="35"/>
+      <c r="D880" s="36"/>
     </row>
     <row r="881" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A881" s="50"/>
-      <c r="B881" s="49"/>
-      <c r="D881" s="50"/>
+      <c r="A881" s="36"/>
+      <c r="B881" s="35"/>
+      <c r="D881" s="36"/>
     </row>
     <row r="882" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A882" s="50"/>
-      <c r="B882" s="49"/>
-      <c r="D882" s="50"/>
+      <c r="A882" s="36"/>
+      <c r="B882" s="35"/>
+      <c r="D882" s="36"/>
     </row>
     <row r="883" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A883" s="50"/>
-      <c r="B883" s="49"/>
-      <c r="D883" s="50"/>
+      <c r="A883" s="36"/>
+      <c r="B883" s="35"/>
+      <c r="D883" s="36"/>
     </row>
     <row r="884" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A884" s="50"/>
-      <c r="B884" s="49"/>
-      <c r="D884" s="50"/>
+      <c r="A884" s="36"/>
+      <c r="B884" s="35"/>
+      <c r="D884" s="36"/>
     </row>
     <row r="885" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A885" s="50"/>
-      <c r="B885" s="49"/>
-      <c r="D885" s="50"/>
+      <c r="A885" s="36"/>
+      <c r="B885" s="35"/>
+      <c r="D885" s="36"/>
     </row>
     <row r="886" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A886" s="50"/>
-      <c r="B886" s="49"/>
-      <c r="D886" s="50"/>
+      <c r="A886" s="36"/>
+      <c r="B886" s="35"/>
+      <c r="D886" s="36"/>
     </row>
     <row r="887" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A887" s="50"/>
-      <c r="B887" s="49"/>
-      <c r="D887" s="50"/>
+      <c r="A887" s="36"/>
+      <c r="B887" s="35"/>
+      <c r="D887" s="36"/>
     </row>
     <row r="888" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A888" s="50"/>
-      <c r="B888" s="49"/>
-      <c r="D888" s="50"/>
+      <c r="A888" s="36"/>
+      <c r="B888" s="35"/>
+      <c r="D888" s="36"/>
     </row>
     <row r="889" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A889" s="50"/>
-      <c r="B889" s="49"/>
-      <c r="D889" s="50"/>
+      <c r="A889" s="36"/>
+      <c r="B889" s="35"/>
+      <c r="D889" s="36"/>
     </row>
     <row r="890" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A890" s="50"/>
-      <c r="B890" s="49"/>
-      <c r="D890" s="50"/>
+      <c r="A890" s="36"/>
+      <c r="B890" s="35"/>
+      <c r="D890" s="36"/>
     </row>
     <row r="891" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A891" s="50"/>
-      <c r="B891" s="49"/>
-      <c r="D891" s="50"/>
+      <c r="A891" s="36"/>
+      <c r="B891" s="35"/>
+      <c r="D891" s="36"/>
     </row>
     <row r="892" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A892" s="50"/>
-      <c r="B892" s="49"/>
-      <c r="D892" s="50"/>
+      <c r="A892" s="36"/>
+      <c r="B892" s="35"/>
+      <c r="D892" s="36"/>
     </row>
     <row r="893" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A893" s="50"/>
-      <c r="B893" s="49"/>
-      <c r="D893" s="50"/>
+      <c r="A893" s="36"/>
+      <c r="B893" s="35"/>
+      <c r="D893" s="36"/>
     </row>
     <row r="894" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A894" s="50"/>
-      <c r="B894" s="49"/>
-      <c r="D894" s="50"/>
+      <c r="A894" s="36"/>
+      <c r="B894" s="35"/>
+      <c r="D894" s="36"/>
     </row>
     <row r="895" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A895" s="50"/>
-      <c r="B895" s="49"/>
-      <c r="D895" s="50"/>
+      <c r="A895" s="36"/>
+      <c r="B895" s="35"/>
+      <c r="D895" s="36"/>
     </row>
     <row r="896" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A896" s="50"/>
-      <c r="B896" s="49"/>
-      <c r="D896" s="50"/>
+      <c r="A896" s="36"/>
+      <c r="B896" s="35"/>
+      <c r="D896" s="36"/>
     </row>
     <row r="897" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A897" s="50"/>
-      <c r="B897" s="49"/>
-      <c r="D897" s="50"/>
+      <c r="A897" s="36"/>
+      <c r="B897" s="35"/>
+      <c r="D897" s="36"/>
     </row>
     <row r="898" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A898" s="50"/>
-      <c r="B898" s="49"/>
-      <c r="D898" s="50"/>
+      <c r="A898" s="36"/>
+      <c r="B898" s="35"/>
+      <c r="D898" s="36"/>
     </row>
     <row r="899" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A899" s="50"/>
-      <c r="B899" s="49"/>
-      <c r="D899" s="50"/>
+      <c r="A899" s="36"/>
+      <c r="B899" s="35"/>
+      <c r="D899" s="36"/>
     </row>
     <row r="900" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A900" s="50"/>
-      <c r="B900" s="49"/>
-      <c r="D900" s="50"/>
+      <c r="A900" s="36"/>
+      <c r="B900" s="35"/>
+      <c r="D900" s="36"/>
     </row>
     <row r="901" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A901" s="50"/>
-      <c r="B901" s="49"/>
-      <c r="D901" s="50"/>
+      <c r="A901" s="36"/>
+      <c r="B901" s="35"/>
+      <c r="D901" s="36"/>
     </row>
     <row r="902" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A902" s="50"/>
-      <c r="B902" s="49"/>
-      <c r="D902" s="50"/>
+      <c r="A902" s="36"/>
+      <c r="B902" s="35"/>
+      <c r="D902" s="36"/>
     </row>
     <row r="903" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A903" s="50"/>
-      <c r="B903" s="49"/>
-      <c r="D903" s="50"/>
+      <c r="A903" s="36"/>
+      <c r="B903" s="35"/>
+      <c r="D903" s="36"/>
     </row>
     <row r="904" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A904" s="50"/>
-      <c r="B904" s="49"/>
-      <c r="D904" s="50"/>
+      <c r="A904" s="36"/>
+      <c r="B904" s="35"/>
+      <c r="D904" s="36"/>
     </row>
     <row r="905" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A905" s="50"/>
-      <c r="B905" s="49"/>
-      <c r="D905" s="50"/>
+      <c r="A905" s="36"/>
+      <c r="B905" s="35"/>
+      <c r="D905" s="36"/>
     </row>
     <row r="906" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A906" s="50"/>
-      <c r="B906" s="49"/>
-      <c r="D906" s="50"/>
+      <c r="A906" s="36"/>
+      <c r="B906" s="35"/>
+      <c r="D906" s="36"/>
     </row>
     <row r="907" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A907" s="50"/>
-      <c r="B907" s="49"/>
-      <c r="D907" s="50"/>
+      <c r="A907" s="36"/>
+      <c r="B907" s="35"/>
+      <c r="D907" s="36"/>
     </row>
     <row r="908" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A908" s="50"/>
-      <c r="B908" s="49"/>
-      <c r="D908" s="50"/>
+      <c r="A908" s="36"/>
+      <c r="B908" s="35"/>
+      <c r="D908" s="36"/>
     </row>
     <row r="909" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A909" s="50"/>
-      <c r="B909" s="49"/>
-      <c r="D909" s="50"/>
+      <c r="A909" s="36"/>
+      <c r="B909" s="35"/>
+      <c r="D909" s="36"/>
     </row>
     <row r="910" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A910" s="50"/>
-      <c r="B910" s="49"/>
-      <c r="D910" s="50"/>
+      <c r="A910" s="36"/>
+      <c r="B910" s="35"/>
+      <c r="D910" s="36"/>
     </row>
     <row r="911" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A911" s="50"/>
-      <c r="B911" s="49"/>
-      <c r="D911" s="50"/>
+      <c r="A911" s="36"/>
+      <c r="B911" s="35"/>
+      <c r="D911" s="36"/>
     </row>
     <row r="912" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A912" s="50"/>
-      <c r="B912" s="49"/>
-      <c r="D912" s="50"/>
+      <c r="A912" s="36"/>
+      <c r="B912" s="35"/>
+      <c r="D912" s="36"/>
     </row>
     <row r="913" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A913" s="50"/>
-      <c r="B913" s="49"/>
-      <c r="D913" s="50"/>
+      <c r="A913" s="36"/>
+      <c r="B913" s="35"/>
+      <c r="D913" s="36"/>
     </row>
     <row r="914" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A914" s="50"/>
-      <c r="B914" s="49"/>
-      <c r="D914" s="50"/>
+      <c r="A914" s="36"/>
+      <c r="B914" s="35"/>
+      <c r="D914" s="36"/>
     </row>
     <row r="915" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A915" s="50"/>
-      <c r="B915" s="49"/>
-      <c r="D915" s="50"/>
+      <c r="A915" s="36"/>
+      <c r="B915" s="35"/>
+      <c r="D915" s="36"/>
     </row>
     <row r="916" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A916" s="50"/>
-      <c r="B916" s="49"/>
-      <c r="D916" s="50"/>
+      <c r="A916" s="36"/>
+      <c r="B916" s="35"/>
+      <c r="D916" s="36"/>
     </row>
     <row r="917" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A917" s="50"/>
-      <c r="B917" s="49"/>
-      <c r="D917" s="50"/>
+      <c r="A917" s="36"/>
+      <c r="B917" s="35"/>
+      <c r="D917" s="36"/>
     </row>
     <row r="918" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A918" s="50"/>
-      <c r="B918" s="49"/>
-      <c r="D918" s="50"/>
+      <c r="A918" s="36"/>
+      <c r="B918" s="35"/>
+      <c r="D918" s="36"/>
     </row>
     <row r="919" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A919" s="50"/>
-      <c r="B919" s="49"/>
-      <c r="D919" s="50"/>
+      <c r="A919" s="36"/>
+      <c r="B919" s="35"/>
+      <c r="D919" s="36"/>
     </row>
     <row r="920" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A920" s="50"/>
-      <c r="B920" s="49"/>
-      <c r="D920" s="50"/>
+      <c r="A920" s="36"/>
+      <c r="B920" s="35"/>
+      <c r="D920" s="36"/>
     </row>
     <row r="921" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A921" s="50"/>
-      <c r="B921" s="49"/>
-      <c r="D921" s="50"/>
+      <c r="A921" s="36"/>
+      <c r="B921" s="35"/>
+      <c r="D921" s="36"/>
     </row>
     <row r="922" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A922" s="50"/>
-      <c r="B922" s="49"/>
-      <c r="D922" s="50"/>
+      <c r="A922" s="36"/>
+      <c r="B922" s="35"/>
+      <c r="D922" s="36"/>
     </row>
     <row r="923" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A923" s="50"/>
-      <c r="B923" s="49"/>
-      <c r="D923" s="50"/>
+      <c r="A923" s="36"/>
+      <c r="B923" s="35"/>
+      <c r="D923" s="36"/>
     </row>
     <row r="924" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A924" s="50"/>
-      <c r="B924" s="49"/>
-      <c r="D924" s="50"/>
+      <c r="A924" s="36"/>
+      <c r="B924" s="35"/>
+      <c r="D924" s="36"/>
     </row>
     <row r="925" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A925" s="50"/>
-      <c r="B925" s="49"/>
-      <c r="D925" s="50"/>
+      <c r="A925" s="36"/>
+      <c r="B925" s="35"/>
+      <c r="D925" s="36"/>
     </row>
     <row r="926" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A926" s="50"/>
-      <c r="B926" s="49"/>
-      <c r="D926" s="50"/>
+      <c r="A926" s="36"/>
+      <c r="B926" s="35"/>
+      <c r="D926" s="36"/>
     </row>
     <row r="927" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A927" s="50"/>
-      <c r="B927" s="49"/>
-      <c r="D927" s="50"/>
+      <c r="A927" s="36"/>
+      <c r="B927" s="35"/>
+      <c r="D927" s="36"/>
     </row>
     <row r="928" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A928" s="50"/>
-      <c r="B928" s="49"/>
-      <c r="D928" s="50"/>
+      <c r="A928" s="36"/>
+      <c r="B928" s="35"/>
+      <c r="D928" s="36"/>
     </row>
     <row r="929" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A929" s="50"/>
-      <c r="B929" s="49"/>
-      <c r="D929" s="50"/>
+      <c r="A929" s="36"/>
+      <c r="B929" s="35"/>
+      <c r="D929" s="36"/>
     </row>
     <row r="930" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A930" s="50"/>
-      <c r="B930" s="49"/>
-      <c r="D930" s="50"/>
+      <c r="A930" s="36"/>
+      <c r="B930" s="35"/>
+      <c r="D930" s="36"/>
     </row>
     <row r="931" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A931" s="50"/>
-      <c r="B931" s="49"/>
-      <c r="D931" s="50"/>
+      <c r="A931" s="36"/>
+      <c r="B931" s="35"/>
+      <c r="D931" s="36"/>
     </row>
     <row r="932" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A932" s="50"/>
-      <c r="B932" s="49"/>
-      <c r="D932" s="50"/>
+      <c r="A932" s="36"/>
+      <c r="B932" s="35"/>
+      <c r="D932" s="36"/>
     </row>
     <row r="933" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A933" s="50"/>
-      <c r="B933" s="49"/>
-      <c r="D933" s="50"/>
+      <c r="A933" s="36"/>
+      <c r="B933" s="35"/>
+      <c r="D933" s="36"/>
     </row>
     <row r="934" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A934" s="50"/>
-      <c r="B934" s="49"/>
-      <c r="D934" s="50"/>
+      <c r="A934" s="36"/>
+      <c r="B934" s="35"/>
+      <c r="D934" s="36"/>
     </row>
     <row r="935" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A935" s="50"/>
-      <c r="B935" s="49"/>
-      <c r="D935" s="50"/>
+      <c r="A935" s="36"/>
+      <c r="B935" s="35"/>
+      <c r="D935" s="36"/>
     </row>
     <row r="936" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A936" s="50"/>
-      <c r="B936" s="49"/>
-      <c r="D936" s="50"/>
+      <c r="A936" s="36"/>
+      <c r="B936" s="35"/>
+      <c r="D936" s="36"/>
     </row>
     <row r="937" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A937" s="50"/>
-      <c r="B937" s="49"/>
-      <c r="D937" s="50"/>
+      <c r="A937" s="36"/>
+      <c r="B937" s="35"/>
+      <c r="D937" s="36"/>
     </row>
     <row r="938" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A938" s="50"/>
-      <c r="B938" s="49"/>
-      <c r="D938" s="50"/>
+      <c r="A938" s="36"/>
+      <c r="B938" s="35"/>
+      <c r="D938" s="36"/>
     </row>
     <row r="939" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A939" s="50"/>
-      <c r="B939" s="49"/>
-      <c r="D939" s="50"/>
+      <c r="A939" s="36"/>
+      <c r="B939" s="35"/>
+      <c r="D939" s="36"/>
     </row>
     <row r="940" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A940" s="50"/>
-      <c r="B940" s="49"/>
-      <c r="D940" s="50"/>
+      <c r="A940" s="36"/>
+      <c r="B940" s="35"/>
+      <c r="D940" s="36"/>
     </row>
     <row r="941" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A941" s="50"/>
-      <c r="B941" s="49"/>
-      <c r="D941" s="50"/>
+      <c r="A941" s="36"/>
+      <c r="B941" s="35"/>
+      <c r="D941" s="36"/>
     </row>
     <row r="942" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A942" s="50"/>
-      <c r="B942" s="49"/>
-      <c r="D942" s="50"/>
+      <c r="A942" s="36"/>
+      <c r="B942" s="35"/>
+      <c r="D942" s="36"/>
     </row>
     <row r="943" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A943" s="50"/>
-      <c r="B943" s="49"/>
-      <c r="D943" s="50"/>
+      <c r="A943" s="36"/>
+      <c r="B943" s="35"/>
+      <c r="D943" s="36"/>
     </row>
     <row r="944" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A944" s="50"/>
-      <c r="B944" s="49"/>
-      <c r="D944" s="50"/>
+      <c r="A944" s="36"/>
+      <c r="B944" s="35"/>
+      <c r="D944" s="36"/>
     </row>
     <row r="945" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A945" s="50"/>
-      <c r="B945" s="49"/>
-      <c r="D945" s="50"/>
+      <c r="A945" s="36"/>
+      <c r="B945" s="35"/>
+      <c r="D945" s="36"/>
     </row>
     <row r="946" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A946" s="50"/>
-      <c r="B946" s="49"/>
-      <c r="D946" s="50"/>
+      <c r="A946" s="36"/>
+      <c r="B946" s="35"/>
+      <c r="D946" s="36"/>
     </row>
     <row r="947" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A947" s="50"/>
-      <c r="B947" s="49"/>
-      <c r="D947" s="50"/>
+      <c r="A947" s="36"/>
+      <c r="B947" s="35"/>
+      <c r="D947" s="36"/>
     </row>
     <row r="948" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A948" s="50"/>
-      <c r="B948" s="49"/>
-      <c r="D948" s="50"/>
+      <c r="A948" s="36"/>
+      <c r="B948" s="35"/>
+      <c r="D948" s="36"/>
     </row>
     <row r="949" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A949" s="50"/>
-      <c r="B949" s="49"/>
-      <c r="D949" s="50"/>
+      <c r="A949" s="36"/>
+      <c r="B949" s="35"/>
+      <c r="D949" s="36"/>
     </row>
     <row r="950" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A950" s="50"/>
-      <c r="B950" s="49"/>
-      <c r="D950" s="50"/>
+      <c r="A950" s="36"/>
+      <c r="B950" s="35"/>
+      <c r="D950" s="36"/>
     </row>
     <row r="951" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A951" s="50"/>
-      <c r="B951" s="49"/>
-      <c r="D951" s="50"/>
+      <c r="A951" s="36"/>
+      <c r="B951" s="35"/>
+      <c r="D951" s="36"/>
     </row>
     <row r="952" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A952" s="50"/>
-      <c r="B952" s="49"/>
-      <c r="D952" s="50"/>
+      <c r="A952" s="36"/>
+      <c r="B952" s="35"/>
+      <c r="D952" s="36"/>
     </row>
     <row r="953" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A953" s="50"/>
-      <c r="B953" s="49"/>
-      <c r="D953" s="50"/>
+      <c r="A953" s="36"/>
+      <c r="B953" s="35"/>
+      <c r="D953" s="36"/>
     </row>
     <row r="954" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A954" s="50"/>
-      <c r="B954" s="49"/>
-      <c r="D954" s="50"/>
+      <c r="A954" s="36"/>
+      <c r="B954" s="35"/>
+      <c r="D954" s="36"/>
     </row>
     <row r="955" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A955" s="50"/>
-      <c r="B955" s="49"/>
-      <c r="D955" s="50"/>
+      <c r="A955" s="36"/>
+      <c r="B955" s="35"/>
+      <c r="D955" s="36"/>
     </row>
     <row r="956" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A956" s="50"/>
-      <c r="B956" s="49"/>
-      <c r="D956" s="50"/>
+      <c r="A956" s="36"/>
+      <c r="B956" s="35"/>
+      <c r="D956" s="36"/>
     </row>
     <row r="957" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A957" s="50"/>
-      <c r="B957" s="49"/>
-      <c r="D957" s="50"/>
+      <c r="A957" s="36"/>
+      <c r="B957" s="35"/>
+      <c r="D957" s="36"/>
     </row>
     <row r="958" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A958" s="50"/>
-      <c r="B958" s="49"/>
-      <c r="D958" s="50"/>
+      <c r="A958" s="36"/>
+      <c r="B958" s="35"/>
+      <c r="D958" s="36"/>
     </row>
     <row r="959" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A959" s="50"/>
-      <c r="B959" s="49"/>
-      <c r="D959" s="50"/>
+      <c r="A959" s="36"/>
+      <c r="B959" s="35"/>
+      <c r="D959" s="36"/>
     </row>
     <row r="960" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A960" s="50"/>
-      <c r="B960" s="49"/>
-      <c r="D960" s="50"/>
+      <c r="A960" s="36"/>
+      <c r="B960" s="35"/>
+      <c r="D960" s="36"/>
     </row>
     <row r="961" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A961" s="50"/>
-      <c r="B961" s="49"/>
-      <c r="D961" s="50"/>
+      <c r="A961" s="36"/>
+      <c r="B961" s="35"/>
+      <c r="D961" s="36"/>
     </row>
     <row r="962" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A962" s="50"/>
-      <c r="B962" s="49"/>
-      <c r="D962" s="50"/>
+      <c r="A962" s="36"/>
+      <c r="B962" s="35"/>
+      <c r="D962" s="36"/>
     </row>
     <row r="963" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A963" s="50"/>
-      <c r="B963" s="49"/>
-      <c r="D963" s="50"/>
+      <c r="A963" s="36"/>
+      <c r="B963" s="35"/>
+      <c r="D963" s="36"/>
     </row>
     <row r="964" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A964" s="50"/>
-      <c r="B964" s="49"/>
-      <c r="D964" s="50"/>
+      <c r="A964" s="36"/>
+      <c r="B964" s="35"/>
+      <c r="D964" s="36"/>
     </row>
     <row r="965" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A965" s="50"/>
-      <c r="B965" s="49"/>
-      <c r="D965" s="50"/>
+      <c r="A965" s="36"/>
+      <c r="B965" s="35"/>
+      <c r="D965" s="36"/>
     </row>
     <row r="966" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A966" s="50"/>
-      <c r="B966" s="49"/>
-      <c r="D966" s="50"/>
+      <c r="A966" s="36"/>
+      <c r="B966" s="35"/>
+      <c r="D966" s="36"/>
     </row>
     <row r="967" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A967" s="50"/>
-      <c r="B967" s="49"/>
-      <c r="D967" s="50"/>
+      <c r="A967" s="36"/>
+      <c r="B967" s="35"/>
+      <c r="D967" s="36"/>
     </row>
     <row r="968" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A968" s="50"/>
-      <c r="B968" s="49"/>
-      <c r="D968" s="50"/>
+      <c r="A968" s="36"/>
+      <c r="B968" s="35"/>
+      <c r="D968" s="36"/>
     </row>
     <row r="969" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A969" s="50"/>
-      <c r="B969" s="49"/>
-      <c r="D969" s="50"/>
+      <c r="A969" s="36"/>
+      <c r="B969" s="35"/>
+      <c r="D969" s="36"/>
     </row>
     <row r="970" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A970" s="50"/>
-      <c r="B970" s="49"/>
-      <c r="D970" s="50"/>
+      <c r="A970" s="36"/>
+      <c r="B970" s="35"/>
+      <c r="D970" s="36"/>
     </row>
     <row r="971" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A971" s="50"/>
-      <c r="B971" s="49"/>
-      <c r="D971" s="50"/>
+      <c r="A971" s="36"/>
+      <c r="B971" s="35"/>
+      <c r="D971" s="36"/>
     </row>
     <row r="972" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A972" s="50"/>
-      <c r="B972" s="49"/>
-      <c r="D972" s="50"/>
+      <c r="A972" s="36"/>
+      <c r="B972" s="35"/>
+      <c r="D972" s="36"/>
     </row>
     <row r="973" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A973" s="50"/>
-      <c r="B973" s="49"/>
-      <c r="D973" s="50"/>
+      <c r="A973" s="36"/>
+      <c r="B973" s="35"/>
+      <c r="D973" s="36"/>
     </row>
     <row r="974" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A974" s="50"/>
-      <c r="B974" s="49"/>
-      <c r="D974" s="50"/>
+      <c r="A974" s="36"/>
+      <c r="B974" s="35"/>
+      <c r="D974" s="36"/>
     </row>
     <row r="975" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A975" s="50"/>
-      <c r="B975" s="49"/>
-      <c r="D975" s="50"/>
+      <c r="A975" s="36"/>
+      <c r="B975" s="35"/>
+      <c r="D975" s="36"/>
     </row>
     <row r="976" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A976" s="50"/>
-      <c r="B976" s="49"/>
-      <c r="D976" s="50"/>
+      <c r="A976" s="36"/>
+      <c r="B976" s="35"/>
+      <c r="D976" s="36"/>
     </row>
     <row r="977" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A977" s="50"/>
-      <c r="B977" s="49"/>
-      <c r="D977" s="50"/>
+      <c r="A977" s="36"/>
+      <c r="B977" s="35"/>
+      <c r="D977" s="36"/>
     </row>
     <row r="978" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A978" s="50"/>
-      <c r="B978" s="49"/>
-      <c r="D978" s="50"/>
+      <c r="A978" s="36"/>
+      <c r="B978" s="35"/>
+      <c r="D978" s="36"/>
     </row>
     <row r="979" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A979" s="50"/>
-      <c r="B979" s="49"/>
-      <c r="D979" s="50"/>
+      <c r="A979" s="36"/>
+      <c r="B979" s="35"/>
+      <c r="D979" s="36"/>
     </row>
     <row r="980" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A980" s="50"/>
-      <c r="B980" s="49"/>
-      <c r="D980" s="50"/>
+      <c r="A980" s="36"/>
+      <c r="B980" s="35"/>
+      <c r="D980" s="36"/>
     </row>
     <row r="981" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A981" s="50"/>
-      <c r="B981" s="49"/>
-      <c r="D981" s="50"/>
+      <c r="A981" s="36"/>
+      <c r="B981" s="35"/>
+      <c r="D981" s="36"/>
     </row>
     <row r="982" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A982" s="50"/>
-      <c r="B982" s="49"/>
-      <c r="D982" s="50"/>
+      <c r="A982" s="36"/>
+      <c r="B982" s="35"/>
+      <c r="D982" s="36"/>
     </row>
     <row r="983" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A983" s="50"/>
-      <c r="B983" s="49"/>
-      <c r="D983" s="50"/>
+      <c r="A983" s="36"/>
+      <c r="B983" s="35"/>
+      <c r="D983" s="36"/>
     </row>
     <row r="984" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A984" s="50"/>
-      <c r="B984" s="49"/>
-      <c r="D984" s="50"/>
+      <c r="A984" s="36"/>
+      <c r="B984" s="35"/>
+      <c r="D984" s="36"/>
     </row>
     <row r="985" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A985" s="50"/>
-      <c r="B985" s="49"/>
-      <c r="D985" s="50"/>
+      <c r="A985" s="36"/>
+      <c r="B985" s="35"/>
+      <c r="D985" s="36"/>
     </row>
     <row r="986" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A986" s="50"/>
-      <c r="B986" s="49"/>
-      <c r="D986" s="50"/>
+      <c r="A986" s="36"/>
+      <c r="B986" s="35"/>
+      <c r="D986" s="36"/>
     </row>
     <row r="987" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A987" s="50"/>
-      <c r="B987" s="49"/>
-      <c r="D987" s="50"/>
+      <c r="A987" s="36"/>
+      <c r="B987" s="35"/>
+      <c r="D987" s="36"/>
     </row>
     <row r="988" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A988" s="50"/>
-      <c r="B988" s="49"/>
-      <c r="D988" s="50"/>
+      <c r="A988" s="36"/>
+      <c r="B988" s="35"/>
+      <c r="D988" s="36"/>
     </row>
     <row r="989" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A989" s="50"/>
-      <c r="B989" s="49"/>
-      <c r="D989" s="50"/>
+      <c r="A989" s="36"/>
+      <c r="B989" s="35"/>
+      <c r="D989" s="36"/>
     </row>
     <row r="990" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A990" s="50"/>
-      <c r="B990" s="49"/>
-      <c r="D990" s="50"/>
+      <c r="A990" s="36"/>
+      <c r="B990" s="35"/>
+      <c r="D990" s="36"/>
     </row>
     <row r="991" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A991" s="50"/>
-      <c r="B991" s="49"/>
-      <c r="D991" s="50"/>
+      <c r="A991" s="36"/>
+      <c r="B991" s="35"/>
+      <c r="D991" s="36"/>
     </row>
     <row r="992" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A992" s="50"/>
-      <c r="B992" s="49"/>
-      <c r="D992" s="50"/>
+      <c r="A992" s="36"/>
+      <c r="B992" s="35"/>
+      <c r="D992" s="36"/>
     </row>
     <row r="993" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A993" s="50"/>
-      <c r="B993" s="49"/>
-      <c r="D993" s="50"/>
+      <c r="A993" s="36"/>
+      <c r="B993" s="35"/>
+      <c r="D993" s="36"/>
     </row>
     <row r="994" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A994" s="50"/>
-      <c r="B994" s="49"/>
-      <c r="D994" s="50"/>
+      <c r="A994" s="36"/>
+      <c r="B994" s="35"/>
+      <c r="D994" s="36"/>
     </row>
     <row r="995" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A995" s="50"/>
-      <c r="B995" s="49"/>
-      <c r="D995" s="50"/>
+      <c r="A995" s="36"/>
+      <c r="B995" s="35"/>
+      <c r="D995" s="36"/>
     </row>
     <row r="996" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A996" s="50"/>
-      <c r="B996" s="49"/>
-      <c r="D996" s="50"/>
+      <c r="A996" s="36"/>
+      <c r="B996" s="35"/>
+      <c r="D996" s="36"/>
     </row>
     <row r="997" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A997" s="50"/>
-      <c r="B997" s="49"/>
-      <c r="D997" s="50"/>
+      <c r="A997" s="36"/>
+      <c r="B997" s="35"/>
+      <c r="D997" s="36"/>
     </row>
     <row r="998" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A998" s="50"/>
-      <c r="B998" s="49"/>
-      <c r="D998" s="50"/>
+      <c r="A998" s="36"/>
+      <c r="B998" s="35"/>
+      <c r="D998" s="36"/>
     </row>
     <row r="999" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A999" s="50"/>
-      <c r="B999" s="49"/>
-      <c r="D999" s="50"/>
+      <c r="A999" s="36"/>
+      <c r="B999" s="35"/>
+      <c r="D999" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Document/KPI/Digital Appraisal System.xlsx
+++ b/Document/KPI/Digital Appraisal System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\Claude AI\Claude Code Advanced\project-management-system\Document\KPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDAF079C-31FB-4AD8-97A3-B95B98646EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A8E60F-9E05-4C31-8E75-6BD828CEA8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI &amp; Scoring" sheetId="1" r:id="rId1"/>
@@ -1220,24 +1220,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1280,9 +1262,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1294,9 +1273,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1310,14 +1286,8 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1330,6 +1300,36 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1584,7 +1584,7 @@
       <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -1606,7 +1606,7 @@
       <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="66"/>
+      <c r="A3" s="92"/>
       <c r="B3" s="13" t="s">
         <v>7</v>
       </c>
@@ -1626,7 +1626,7 @@
       <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="66"/>
+      <c r="A4" s="92"/>
       <c r="B4" s="13" t="s">
         <v>8</v>
       </c>
@@ -1646,7 +1646,7 @@
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="67"/>
+      <c r="A5" s="93"/>
       <c r="B5" s="13" t="s">
         <v>9</v>
       </c>
@@ -1666,7 +1666,7 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="83" t="s">
+      <c r="A6" s="91" t="s">
         <v>61</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -1688,7 +1688,7 @@
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="66"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="13" t="s">
         <v>55</v>
       </c>
@@ -1703,7 +1703,7 @@
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="67"/>
+      <c r="A8" s="93"/>
       <c r="B8" s="13" t="s">
         <v>56</v>
       </c>
@@ -1718,10 +1718,10 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="83" t="s">
+      <c r="A9" s="91" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="78" t="s">
         <v>50</v>
       </c>
       <c r="C9" s="9">
@@ -1735,7 +1735,7 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="67"/>
+      <c r="A10" s="93"/>
       <c r="B10" s="22" t="s">
         <v>63</v>
       </c>
@@ -1750,10 +1750,10 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="83" t="s">
+      <c r="A11" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="77" t="s">
         <v>57</v>
       </c>
       <c r="C11" s="9">
@@ -1767,8 +1767,8 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="67"/>
-      <c r="B12" s="92" t="s">
+      <c r="A12" s="93"/>
+      <c r="B12" s="82" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="23">
@@ -1782,7 +1782,7 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="94" t="s">
+      <c r="A13" s="75" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="8" t="s">
@@ -1799,10 +1799,10 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="99" t="s">
+      <c r="A14" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="98" t="s">
+      <c r="B14" s="86" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="9">
@@ -1816,10 +1816,10 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="99" t="s">
+      <c r="A15" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="B15" s="97"/>
+      <c r="B15" s="85"/>
       <c r="C15" s="23">
         <v>0.05</v>
       </c>
@@ -1831,10 +1831,10 @@
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="96" t="s">
+      <c r="A16" s="89" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="65"/>
+      <c r="B16" s="90"/>
       <c r="C16" s="25">
         <f>SUM(C2:C15)</f>
         <v>1.0000000000000002</v>
@@ -10763,20 +10763,20 @@
       <c r="D1" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="70" t="s">
+      <c r="E1" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="81" t="s">
+      <c r="F1" s="73" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="82" t="s">
+      <c r="G1" s="74" t="s">
         <v>85</v>
       </c>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
     </row>
     <row r="2" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="94" t="s">
         <v>60</v>
       </c>
       <c r="B2" s="51" t="s">
@@ -10788,20 +10788,20 @@
       <c r="D2" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="71" t="s">
+      <c r="E2" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="74" t="s">
+      <c r="F2" s="66" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="79" t="s">
+      <c r="G2" s="71" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="60"/>
     </row>
     <row r="3" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61"/>
+      <c r="A3" s="95"/>
       <c r="B3" s="54" t="s">
         <v>30</v>
       </c>
@@ -10811,20 +10811,20 @@
       <c r="D3" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="69" t="s">
+      <c r="E3" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="74" t="s">
+      <c r="F3" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="G3" s="80" t="s">
+      <c r="G3" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
     </row>
     <row r="4" spans="1:9" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="61"/>
+      <c r="A4" s="95"/>
       <c r="B4" s="54" t="s">
         <v>33</v>
       </c>
@@ -10834,18 +10834,18 @@
       <c r="D4" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="69" t="s">
+      <c r="E4" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="74" t="s">
+      <c r="F4" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="79"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
+      <c r="G4" s="71"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
     </row>
     <row r="5" spans="1:9" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="62"/>
+      <c r="A5" s="96"/>
       <c r="B5" s="57" t="s">
         <v>36</v>
       </c>
@@ -10855,20 +10855,20 @@
       <c r="D5" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="72" t="s">
+      <c r="E5" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="74" t="s">
+      <c r="F5" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="79" t="s">
+      <c r="G5" s="71" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
     </row>
     <row r="6" spans="1:9" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="60" t="s">
+      <c r="A6" s="94" t="s">
         <v>61</v>
       </c>
       <c r="B6" s="51" t="s">
@@ -10880,18 +10880,18 @@
       <c r="D6" s="53" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="71" t="s">
+      <c r="E6" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="74" t="s">
+      <c r="F6" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="79"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
     </row>
     <row r="7" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="61"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="56" t="s">
         <v>42</v>
       </c>
@@ -10901,18 +10901,18 @@
       <c r="D7" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="69" t="s">
+      <c r="E7" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="74" t="s">
+      <c r="F7" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="79"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
+      <c r="G7" s="71"/>
+      <c r="H7" s="60"/>
+      <c r="I7" s="60"/>
     </row>
     <row r="8" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="61"/>
+      <c r="A8" s="95"/>
       <c r="B8" s="56" t="s">
         <v>44</v>
       </c>
@@ -10922,70 +10922,70 @@
       <c r="D8" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="69" t="s">
+      <c r="E8" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="74" t="s">
+      <c r="F8" s="66" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="97" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="88" t="s">
+      <c r="B9" s="79" t="s">
         <v>50</v>
       </c>
       <c r="C9" s="52">
         <v>0.05</v>
       </c>
-      <c r="D9" s="85" t="s">
+      <c r="D9" s="76" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="71" t="s">
+      <c r="E9" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="74" t="s">
+      <c r="F9" s="66" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="63"/>
-      <c r="B10" s="88" t="s">
+      <c r="A10" s="98"/>
+      <c r="B10" s="79" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="52">
         <v>0.05</v>
       </c>
       <c r="D10" s="53"/>
-      <c r="E10" s="71" t="s">
+      <c r="E10" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="74" t="s">
+      <c r="F10" s="66" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="89" t="s">
+      <c r="A11" s="99" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="90" t="s">
+      <c r="B11" s="80" t="s">
         <v>57</v>
       </c>
       <c r="C11" s="47">
         <v>0.05</v>
       </c>
       <c r="D11" s="48"/>
-      <c r="E11" s="75" t="s">
+      <c r="E11" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="74" t="s">
+      <c r="F11" s="66" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="64"/>
-      <c r="B12" s="91" t="s">
+      <c r="A12" s="100"/>
+      <c r="B12" s="81" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="49">
@@ -10994,10 +10994,10 @@
       <c r="D12" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="76" t="s">
+      <c r="E12" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="74" t="s">
+      <c r="F12" s="66" t="s">
         <v>78</v>
       </c>
     </row>
@@ -11005,7 +11005,7 @@
       <c r="A13" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="93" t="s">
+      <c r="B13" s="83" t="s">
         <v>47</v>
       </c>
       <c r="C13" s="43">
@@ -11014,15 +11014,15 @@
       <c r="D13" s="44" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="77" t="s">
+      <c r="E13" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="74" t="s">
+      <c r="F13" s="66" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="95" t="s">
+      <c r="A14" s="84" t="s">
         <v>67</v>
       </c>
       <c r="B14" s="39" t="s">
@@ -11034,15 +11034,15 @@
       <c r="D14" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="78" t="s">
+      <c r="E14" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="74" t="s">
+      <c r="F14" s="66" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="100" t="s">
+      <c r="A15" s="88" t="s">
         <v>66</v>
       </c>
       <c r="B15" s="45"/>
@@ -11050,8 +11050,8 @@
         <v>0.05</v>
       </c>
       <c r="D15" s="45"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="74" t="s">
+      <c r="E15" s="65"/>
+      <c r="F15" s="66" t="s">
         <v>78</v>
       </c>
     </row>

--- a/Document/KPI/Digital Appraisal System.xlsx
+++ b/Document/KPI/Digital Appraisal System.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\Claude AI\Claude Code Advanced\project-management-system\Document\KPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A8E60F-9E05-4C31-8E75-6BD828CEA8C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC8E2D5-3649-4D13-8B48-05ACDFC7AEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI &amp; Scoring" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="88">
   <si>
     <t>Category</t>
   </si>
@@ -266,22 +266,10 @@
     <t>Collaboration Manual</t>
   </si>
   <si>
-    <t>Work Item in Closed Column / Total Assigned Work Item * 10</t>
-  </si>
-  <si>
-    <t>Work Item complete on or before due date / Total assigned work item * 10</t>
-  </si>
-  <si>
     <t>Work item should be move from in -progress to in -review. If work item is blocked, do not consider it in this calculation.</t>
   </si>
   <si>
     <t>Esimtated hours for work item - Actual hours logged against that work item</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> If work item is blocked, do not consider it in this calculation</t>
-  </si>
-  <si>
-    <t>Work Item in "In QA" Column / Total Assigned Work Item * 10</t>
   </si>
   <si>
     <t>If work item dragged from "In QA" to "In Progress" and time logged against such work item should be treated as rework.</t>
@@ -305,17 +293,6 @@
     <t xml:space="preserve">10 -( (Hours spent on Code Review) / Total Working Hours * 10) </t>
   </si>
   <si>
-    <t>If work item - Bug, Classification = "Code Review"  follow the scoring mentioned in previous column                                   EG: Hours Spend on Code Review - 10, Total Hours worked in month 160, 
-As per formula :
-10 -(10/160*10) = 10 - 0.625 = 9.375</t>
-  </si>
-  <si>
-    <t>If work item - Bug, apart from Classification = "Code Review"  follow the scoring mentioned in previous column
-EG: Hours Spend on Rework + Bug - 20, Total Hours worked in month 160, 
-As per formula :
-10 -(10/160*10) = 10 - 1.25 = 8.75</t>
-  </si>
-  <si>
     <t>Action</t>
   </si>
   <si>
@@ -323,6 +300,118 @@
   </si>
   <si>
     <t>Collaboration -Manual</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Work Item in "In QA" Column / Total Assigned Work Item * 10. Once the score is calculated based on above formula - ensure the score persist - even if the card is moved to "In Closed" column. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Note - If Card move forward from "In-QA",  score should still  persist - track if work-item is moved back to previous column from "In-QA" to "In-Review", or "In-Progress" - in such case recalculate score with the given formula. If work item is blocked, do not consider it in this calculation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ignore Epic in the formula.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Work Item complete on or before due date / Total assigned work item * 10 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Note - check if work item is move in "in-Review" and move forward,  score should still  persist - track if work-item is moved back to previous column from "In-Review" to "In-Progress".in such case recalculate score with the given formula. If work item is blocked, do not consider it in this calculation. Ignore Epic in the formula</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Work Item in Closed Column / Total Assigned Work Item * 10 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Note - Persist score in "Closed" column - track if work item is moved back in any column - recalculate score based on given formula.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If work item - Bug, Classification = "Code Review"  follow the scoring mentioned in previous column                                   EG: Hours Spend on Code Review - 10, Total Hours worked in month 160, 
+As per formula :
+10 -(10/160*10) = 10 - 0.625 = 9.375  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Note - Ensure if Bug Classification = Code Review, check only this specific case for calculation, consider the hours log against this work item.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">If work item - Bug, excluding from Classification = "Code Review"  follow the scoring mentioned in previous column
+EG: Hours Spend on Rework + Bug - 20, Total Hours worked in month 160, 
+As per formula :
+10 -(10/160*10) = 10 - 1.25 = 8.75 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Note - Calculate score if Bug - Classification for work Item is set to other than "Code Review", this specific case should be followed for calculation.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> If work item is blocked and work item type is epic, do not consider it in this calculation</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1301,15 +1390,10 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1331,6 +1415,15 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1584,7 +1677,7 @@
       <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="100" t="s">
         <v>60</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -1606,7 +1699,7 @@
       <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="92"/>
+      <c r="A3" s="101"/>
       <c r="B3" s="13" t="s">
         <v>7</v>
       </c>
@@ -1626,7 +1719,7 @@
       <c r="G3" s="7"/>
     </row>
     <row r="4" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="92"/>
+      <c r="A4" s="101"/>
       <c r="B4" s="13" t="s">
         <v>8</v>
       </c>
@@ -1646,7 +1739,7 @@
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="93"/>
+      <c r="A5" s="102"/>
       <c r="B5" s="13" t="s">
         <v>9</v>
       </c>
@@ -1666,7 +1759,7 @@
       <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="100" t="s">
         <v>61</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -1688,7 +1781,7 @@
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="92"/>
+      <c r="A7" s="101"/>
       <c r="B7" s="13" t="s">
         <v>55</v>
       </c>
@@ -1703,7 +1796,7 @@
       <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="93"/>
+      <c r="A8" s="102"/>
       <c r="B8" s="13" t="s">
         <v>56</v>
       </c>
@@ -1718,7 +1811,7 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="91" t="s">
+      <c r="A9" s="100" t="s">
         <v>62</v>
       </c>
       <c r="B9" s="78" t="s">
@@ -1735,7 +1828,7 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="93"/>
+      <c r="A10" s="102"/>
       <c r="B10" s="22" t="s">
         <v>63</v>
       </c>
@@ -1750,8 +1843,8 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="91" t="s">
-        <v>86</v>
+      <c r="A11" s="100" t="s">
+        <v>80</v>
       </c>
       <c r="B11" s="77" t="s">
         <v>57</v>
@@ -1767,7 +1860,7 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="93"/>
+      <c r="A12" s="102"/>
       <c r="B12" s="82" t="s">
         <v>11</v>
       </c>
@@ -1831,10 +1924,10 @@
       <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="89" t="s">
+      <c r="A16" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="90"/>
+      <c r="B16" s="99"/>
       <c r="C16" s="25">
         <f>SUM(C2:C15)</f>
         <v>1.0000000000000002</v>
@@ -10742,7 +10835,7 @@
   <dimension ref="A1:I999"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.88671875" style="38" customWidth="1"/>
+    <col min="1" max="1" width="26.44140625" style="38" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="54.77734375" customWidth="1"/>
     <col min="5" max="5" width="67" style="38" customWidth="1"/>
@@ -10767,16 +10860,16 @@
         <v>26</v>
       </c>
       <c r="F1" s="73" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="G1" s="74" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H1" s="60"/>
       <c r="I1" s="60"/>
     </row>
-    <row r="2" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="94" t="s">
+    <row r="2" spans="1:9" ht="132" x14ac:dyDescent="0.25">
+      <c r="A2" s="91" t="s">
         <v>60</v>
       </c>
       <c r="B2" s="51" t="s">
@@ -10791,17 +10884,17 @@
       <c r="E2" s="63" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="66" t="s">
-        <v>74</v>
+      <c r="F2" s="89" t="s">
+        <v>82</v>
       </c>
-      <c r="G2" s="71" t="s">
-        <v>73</v>
+      <c r="G2" s="90" t="s">
+        <v>81</v>
       </c>
       <c r="H2" s="60"/>
       <c r="I2" s="60"/>
     </row>
-    <row r="3" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="95"/>
+    <row r="3" spans="1:9" ht="105.6" x14ac:dyDescent="0.25">
+      <c r="A3" s="92"/>
       <c r="B3" s="54" t="s">
         <v>30</v>
       </c>
@@ -10814,17 +10907,17 @@
       <c r="E3" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="66" t="s">
-        <v>70</v>
+      <c r="F3" s="89" t="s">
+        <v>83</v>
       </c>
       <c r="G3" s="72" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H3" s="60"/>
       <c r="I3" s="60"/>
     </row>
     <row r="4" spans="1:9" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="95"/>
+      <c r="A4" s="92"/>
       <c r="B4" s="54" t="s">
         <v>33</v>
       </c>
@@ -10838,14 +10931,14 @@
         <v>35</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G4" s="71"/>
       <c r="H4" s="60"/>
       <c r="I4" s="60"/>
     </row>
-    <row r="5" spans="1:9" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="96"/>
+    <row r="5" spans="1:9" ht="53.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="93"/>
       <c r="B5" s="57" t="s">
         <v>36</v>
       </c>
@@ -10858,17 +10951,17 @@
       <c r="E5" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="66" t="s">
-        <v>69</v>
+      <c r="F5" s="89" t="s">
+        <v>84</v>
       </c>
       <c r="G5" s="71" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="H5" s="60"/>
       <c r="I5" s="60"/>
     </row>
     <row r="6" spans="1:9" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="94" t="s">
+      <c r="A6" s="91" t="s">
         <v>61</v>
       </c>
       <c r="B6" s="51" t="s">
@@ -10884,14 +10977,14 @@
         <v>41</v>
       </c>
       <c r="F6" s="66" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G6" s="71"/>
       <c r="H6" s="60"/>
       <c r="I6" s="60"/>
     </row>
-    <row r="7" spans="1:9" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="95"/>
+    <row r="7" spans="1:9" ht="118.8" x14ac:dyDescent="0.25">
+      <c r="A7" s="92"/>
       <c r="B7" s="56" t="s">
         <v>42</v>
       </c>
@@ -10902,17 +10995,17 @@
         <v>43</v>
       </c>
       <c r="E7" s="61" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
-      <c r="F7" s="66" t="s">
-        <v>82</v>
+      <c r="F7" s="89" t="s">
+        <v>85</v>
       </c>
       <c r="G7" s="71"/>
       <c r="H7" s="60"/>
       <c r="I7" s="60"/>
     </row>
-    <row r="8" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="95"/>
+    <row r="8" spans="1:9" ht="132.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="92"/>
       <c r="B8" s="56" t="s">
         <v>44</v>
       </c>
@@ -10923,14 +11016,14 @@
         <v>43</v>
       </c>
       <c r="E8" s="61" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
-      <c r="F8" s="66" t="s">
-        <v>83</v>
+      <c r="F8" s="89" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="97" t="s">
+    <row r="9" spans="1:9" ht="55.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="94" t="s">
         <v>62</v>
       </c>
       <c r="B9" s="79" t="s">
@@ -10946,11 +11039,11 @@
         <v>52</v>
       </c>
       <c r="F9" s="66" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="98"/>
+      <c r="A10" s="95"/>
       <c r="B10" s="79" t="s">
         <v>63</v>
       </c>
@@ -10962,11 +11055,11 @@
         <v>64</v>
       </c>
       <c r="F10" s="66" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="99" t="s">
+      <c r="A11" s="96" t="s">
         <v>68</v>
       </c>
       <c r="B11" s="80" t="s">
@@ -10980,11 +11073,11 @@
         <v>58</v>
       </c>
       <c r="F11" s="66" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="100"/>
+      <c r="A12" s="97"/>
       <c r="B12" s="81" t="s">
         <v>11</v>
       </c>
@@ -10998,7 +11091,7 @@
         <v>46</v>
       </c>
       <c r="F12" s="66" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -11018,7 +11111,7 @@
         <v>49</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -11038,7 +11131,7 @@
         <v>65</v>
       </c>
       <c r="F14" s="66" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11052,7 +11145,7 @@
       <c r="D15" s="45"/>
       <c r="E15" s="65"/>
       <c r="F15" s="66" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">

--- a/Document/KPI/Digital Appraisal System.xlsx
+++ b/Document/KPI/Digital Appraisal System.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\Claude AI\Claude Code Advanced\project-management-system\Document\KPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC8E2D5-3649-4D13-8B48-05ACDFC7AEA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F750541-ED63-4D39-B689-3AF70C48C401}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KPI &amp; Scoring" sheetId="1" r:id="rId1"/>
@@ -269,9 +269,6 @@
     <t>Work item should be move from in -progress to in -review. If work item is blocked, do not consider it in this calculation.</t>
   </si>
   <si>
-    <t>Esimtated hours for work item - Actual hours logged against that work item</t>
-  </si>
-  <si>
     <t>If work item dragged from "In QA" to "In Progress" and time logged against such work item should be treated as rework.</t>
   </si>
   <si>
@@ -412,6 +409,9 @@
   </si>
   <si>
     <t xml:space="preserve"> If work item is blocked and work item type is epic, do not consider it in this calculation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esimtated hours for work item - Actual hours logged against that work item. To achieve points here Delivery Timeliness should be achieve within due date. </t>
   </si>
 </sst>
 </file>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="11" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="100" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B11" s="77" t="s">
         <v>57</v>
@@ -10860,10 +10860,10 @@
         <v>26</v>
       </c>
       <c r="F1" s="73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G1" s="74" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H1" s="60"/>
       <c r="I1" s="60"/>
@@ -10885,10 +10885,10 @@
         <v>29</v>
       </c>
       <c r="F2" s="89" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G2" s="90" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H2" s="60"/>
       <c r="I2" s="60"/>
@@ -10908,7 +10908,7 @@
         <v>32</v>
       </c>
       <c r="F3" s="89" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G3" s="72" t="s">
         <v>69</v>
@@ -10931,7 +10931,7 @@
         <v>35</v>
       </c>
       <c r="F4" s="66" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="G4" s="71"/>
       <c r="H4" s="60"/>
@@ -10952,10 +10952,10 @@
         <v>38</v>
       </c>
       <c r="F5" s="89" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G5" s="71" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H5" s="60"/>
       <c r="I5" s="60"/>
@@ -10977,7 +10977,7 @@
         <v>41</v>
       </c>
       <c r="F6" s="66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G6" s="71"/>
       <c r="H6" s="60"/>
@@ -10995,10 +10995,10 @@
         <v>43</v>
       </c>
       <c r="E7" s="61" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F7" s="89" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G7" s="71"/>
       <c r="H7" s="60"/>
@@ -11016,10 +11016,10 @@
         <v>43</v>
       </c>
       <c r="E8" s="61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F8" s="89" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="55.8" thickBot="1" x14ac:dyDescent="0.3">
@@ -11039,7 +11039,7 @@
         <v>52</v>
       </c>
       <c r="F9" s="66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -11055,7 +11055,7 @@
         <v>64</v>
       </c>
       <c r="F10" s="66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11073,7 +11073,7 @@
         <v>58</v>
       </c>
       <c r="F11" s="66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="61.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -11091,7 +11091,7 @@
         <v>46</v>
       </c>
       <c r="F12" s="66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -11111,7 +11111,7 @@
         <v>49</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -11131,7 +11131,7 @@
         <v>65</v>
       </c>
       <c r="F14" s="66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -11145,7 +11145,7 @@
       <c r="D15" s="45"/>
       <c r="E15" s="65"/>
       <c r="F15" s="66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="13.8" x14ac:dyDescent="0.25">
